--- a/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix.xlsx
+++ b/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB9633B8-F464-48DD-A649-0D49C97847A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13448522-95BD-4E64-9135-FD8CCBD6EE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -129,7 +129,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -163,12 +163,74 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="8"/>
+      </right>
+      <top style="thin">
+        <color theme="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -177,6 +239,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -621,553 +689,543 @@
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="5">
         <v>7.7261312811500088E-2</v>
       </c>
-      <c r="C3">
-        <v>16770.40234375</v>
-      </c>
-      <c r="D3">
-        <v>7.5164414942264557E-2</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E66" si="0">(B3-D3)^2</f>
-        <v>4.3969806740045109E-6</v>
-      </c>
-      <c r="F3">
-        <v>5.1348115448490717E-6</v>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>14250</v>
-      </c>
-      <c r="I3">
-        <v>18750</v>
-      </c>
-      <c r="J3">
-        <v>0.55166816711425781</v>
-      </c>
-      <c r="K3">
-        <v>0.30433773994445801</v>
-      </c>
-      <c r="L3">
-        <v>3.9008830193124522E-3</v>
-      </c>
-      <c r="M3">
-        <v>7.8017660416662693E-3</v>
-      </c>
-      <c r="N3">
-        <v>2.0968978692355311E-3</v>
-      </c>
-      <c r="O3">
-        <v>215881471.44897291</v>
-      </c>
-      <c r="P3">
-        <v>150</v>
-      </c>
-      <c r="Q3">
-        <v>20000</v>
+      <c r="C3" s="5">
+        <v>16863</v>
+      </c>
+      <c r="D3" s="5">
+        <v>7.7584207057952881E-2</v>
+      </c>
+      <c r="E3" s="5">
+        <v>8.8020700786728412E-5</v>
+      </c>
+      <c r="F3" s="5">
+        <v>8.5422470874618739E-6</v>
+      </c>
+      <c r="G3" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>15500</v>
+      </c>
+      <c r="I3" s="5">
+        <v>17500</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0.54857140779495239</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0.30093061923980707</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1.734735107877096E-3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>3.4694704227149491E-3</v>
+      </c>
+      <c r="N3" s="5">
+        <v>3.2289424645279291E-4</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10000000</v>
+      </c>
+      <c r="P3" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>100000</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S66" si="1">(N3/B3)*100</f>
-        <v>2.7140334443338827</v>
+        <f t="shared" ref="S3:S66" si="0">(N3/B3)*100</f>
+        <v>0.4179248768922435</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>8.7437268462869769E-2</v>
       </c>
-      <c r="C4">
-        <v>14446.8076171875</v>
-      </c>
-      <c r="D4">
-        <v>8.8034152984619141E-2</v>
-      </c>
-      <c r="E4">
+      <c r="C4" s="5">
+        <v>14373</v>
+      </c>
+      <c r="D4" s="5">
+        <v>8.690556138753891E-2</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1.038558093569009E-5</v>
+      </c>
+      <c r="F4" s="5">
+        <v>9.2652926468872465E-6</v>
+      </c>
+      <c r="G4" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>13500</v>
+      </c>
+      <c r="I4" s="5">
+        <v>15500</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0.55228227376937866</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0.3050156831741333</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2.25468294119844E-3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4.509365651756525E-3</v>
+      </c>
+      <c r="N4" s="5">
+        <v>5.3170707533085892E-4</v>
+      </c>
+      <c r="O4" s="5">
+        <v>182012721.6058045</v>
+      </c>
+      <c r="P4" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>60000</v>
+      </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4">
         <f t="shared" si="0"/>
-        <v>3.5627113230397628E-7</v>
-      </c>
-      <c r="F4">
-        <v>1.503678595327074E-5</v>
-      </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>13750</v>
-      </c>
-      <c r="I4">
-        <v>15000</v>
-      </c>
-      <c r="J4">
-        <v>0.55165088176727295</v>
-      </c>
-      <c r="K4">
-        <v>0.30431869626045233</v>
-      </c>
-      <c r="L4">
-        <v>3.9007607934517709E-3</v>
-      </c>
-      <c r="M4">
-        <v>7.8015215694904327E-3</v>
-      </c>
-      <c r="N4">
-        <v>5.9688452174937179E-4</v>
-      </c>
-      <c r="O4">
-        <v>57559347.746496662</v>
-      </c>
-      <c r="P4">
-        <v>150</v>
-      </c>
-      <c r="Q4">
-        <v>20000</v>
-      </c>
-      <c r="R4" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <f t="shared" si="1"/>
-        <v>0.68264314775894308</v>
+        <v>0.60810119606681023</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="8">
         <v>9.8929739735079153E-2</v>
       </c>
-      <c r="C5">
-        <v>12377.0849609375</v>
-      </c>
-      <c r="D5">
-        <v>0.1018834933638573</v>
-      </c>
-      <c r="E5">
+      <c r="C5" s="8">
+        <v>12427</v>
+      </c>
+      <c r="D5" s="8">
+        <v>9.884999692440033E-2</v>
+      </c>
+      <c r="E5" s="8">
+        <v>8.857553439156618E-6</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1.2053801583533639E-5</v>
+      </c>
+      <c r="G5" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8">
+        <v>11500</v>
+      </c>
+      <c r="I5" s="8">
+        <v>13500</v>
+      </c>
+      <c r="J5" s="8">
+        <v>0.54910850524902344</v>
+      </c>
+      <c r="K5" s="8">
+        <v>0.30152013897895807</v>
+      </c>
+      <c r="L5" s="8">
+        <v>1.7364335591574379E-3</v>
+      </c>
+      <c r="M5" s="8">
+        <v>3.472867188975215E-3</v>
+      </c>
+      <c r="N5" s="8">
+        <v>7.9742810678823384E-5</v>
+      </c>
+      <c r="O5" s="8">
+        <v>53770237.375592373</v>
+      </c>
+      <c r="P5" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>100000</v>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5">
         <f t="shared" si="0"/>
-        <v>8.7246604995200541E-6</v>
-      </c>
-      <c r="F5">
-        <v>1.474570581194712E-5</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>11750</v>
-      </c>
-      <c r="I5">
-        <v>13250</v>
-      </c>
-      <c r="J5">
-        <v>0.5475306510925293</v>
-      </c>
-      <c r="K5">
-        <v>0.29978984594345093</v>
-      </c>
-      <c r="L5">
-        <v>3.87162636295013E-3</v>
-      </c>
-      <c r="M5">
-        <v>7.743252906948328E-3</v>
-      </c>
-      <c r="N5">
-        <v>2.9537536287781441E-3</v>
-      </c>
-      <c r="O5">
-        <v>45850570.836959213</v>
-      </c>
-      <c r="P5">
-        <v>150</v>
-      </c>
-      <c r="Q5">
-        <v>20000</v>
-      </c>
-      <c r="R5" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <f t="shared" si="1"/>
-        <v>2.9857084802688334</v>
+        <v>8.0605499309271564E-2</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="8">
         <v>0.1119024130228327</v>
       </c>
-      <c r="C6">
-        <v>10614.443359375</v>
-      </c>
-      <c r="D6">
-        <v>0.11329691112041471</v>
-      </c>
-      <c r="E6">
+      <c r="C6" s="8">
+        <v>10704</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.1120605692267418</v>
+      </c>
+      <c r="E6" s="8">
+        <v>3.2323625873686979E-6</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1.4981729691498909E-5</v>
+      </c>
+      <c r="G6" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8">
+        <v>9500</v>
+      </c>
+      <c r="I6" s="8">
+        <v>11500</v>
+      </c>
+      <c r="J6" s="8">
+        <v>0.54890286922454834</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0.30129438638687128</v>
+      </c>
+      <c r="L6" s="8">
+        <v>1.735783280951114E-3</v>
+      </c>
+      <c r="M6" s="8">
+        <v>3.471566596999764E-3</v>
+      </c>
+      <c r="N6" s="8">
+        <v>1.5815620390913221E-4</v>
+      </c>
+      <c r="O6" s="8">
+        <v>835367082.5790813</v>
+      </c>
+      <c r="P6" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>100000</v>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6">
         <f t="shared" si="0"/>
-        <v>1.9446249441598337E-6</v>
-      </c>
-      <c r="F6">
-        <v>1.1974460903729779E-5</v>
-      </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>10000</v>
-      </c>
-      <c r="I6">
-        <v>11250</v>
-      </c>
-      <c r="J6">
-        <v>0.54931265115737915</v>
-      </c>
-      <c r="K6">
-        <v>0.30174437165260309</v>
-      </c>
-      <c r="L6">
-        <v>3.884227006249432E-3</v>
-      </c>
-      <c r="M6">
-        <v>7.7684540301561364E-3</v>
-      </c>
-      <c r="N6">
-        <v>1.3944980975820059E-3</v>
-      </c>
-      <c r="O6">
-        <v>134672597.50299519</v>
-      </c>
-      <c r="P6">
+        <v>0.14133404243647707</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.12653747766179149</v>
+      </c>
+      <c r="C7" s="5">
+        <v>9137</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.1270018815994263</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1.2833184882765639E-5</v>
+      </c>
+      <c r="F7" s="5">
+        <v>2.491233135515358E-5</v>
+      </c>
+      <c r="G7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>8750</v>
+      </c>
+      <c r="I7" s="5">
+        <v>9500</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0.54802572727203369</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0.30033221840858459</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1.225422779599028E-3</v>
+      </c>
+      <c r="M7" s="5">
+        <v>2.4508456699550152E-3</v>
+      </c>
+      <c r="N7" s="5">
+        <v>4.6440393763474969E-4</v>
+      </c>
+      <c r="O7" s="5">
+        <v>2517626.3915968859</v>
+      </c>
+      <c r="P7" s="5">
         <v>100</v>
       </c>
-      <c r="Q6">
-        <v>20000</v>
-      </c>
-      <c r="R6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="1"/>
-        <v>1.2461733933275156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>0.12653747766179149</v>
-      </c>
-      <c r="C7">
-        <v>9169.5654296875</v>
-      </c>
-      <c r="D7">
-        <v>0.12517066299915311</v>
-      </c>
-      <c r="E7">
+      <c r="Q7" s="6">
+        <v>200000</v>
+      </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7">
         <f t="shared" si="0"/>
-        <v>1.8681823220032757E-6</v>
-      </c>
-      <c r="F7">
-        <v>1.929402424138971E-5</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>7750</v>
-      </c>
-      <c r="I7">
-        <v>9250</v>
-      </c>
-      <c r="J7">
-        <v>0.54851353168487549</v>
-      </c>
-      <c r="K7">
-        <v>0.30086711049079901</v>
-      </c>
-      <c r="L7">
-        <v>3.878576378269577E-3</v>
-      </c>
-      <c r="M7">
-        <v>7.757152896374464E-3</v>
-      </c>
-      <c r="N7">
-        <v>1.366814662638383E-3</v>
-      </c>
-      <c r="O7">
-        <v>41834339.641357012</v>
-      </c>
-      <c r="P7">
-        <v>120</v>
-      </c>
-      <c r="Q7">
-        <v>20000</v>
-      </c>
-      <c r="R7" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="1"/>
-        <v>1.0801658827842262</v>
+        <v>0.36700900493370464</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="8">
         <v>0.14303719980762769</v>
       </c>
-      <c r="C8">
-        <v>7963.41650390625</v>
-      </c>
-      <c r="D8">
-        <v>0.14415986835956571</v>
-      </c>
-      <c r="E8">
+      <c r="C8" s="8">
+        <v>8009</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.1426205039024353</v>
+      </c>
+      <c r="E8" s="8">
+        <v>7.3540354605938774E-6</v>
+      </c>
+      <c r="F8" s="8">
+        <v>2.0959972971468229E-5</v>
+      </c>
+      <c r="G8" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8">
+        <v>7250</v>
+      </c>
+      <c r="I8" s="8">
+        <v>8250</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0.54907357692718506</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0.30148178339004522</v>
+      </c>
+      <c r="L8" s="8">
+        <v>1.227765842658146E-3</v>
+      </c>
+      <c r="M8" s="8">
+        <v>2.455531619489193E-3</v>
+      </c>
+      <c r="N8" s="8">
+        <v>4.1669590519238803E-4</v>
+      </c>
+      <c r="O8" s="8">
+        <v>2222893.248628262</v>
+      </c>
+      <c r="P8" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>200000</v>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8">
         <f t="shared" si="0"/>
-        <v>1.2603846775106027E-6</v>
-      </c>
-      <c r="F8">
-        <v>2.215739004896022E-5</v>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>6750</v>
-      </c>
-      <c r="I8">
-        <v>8250</v>
-      </c>
-      <c r="J8">
-        <v>0.55184644460678101</v>
-      </c>
-      <c r="K8">
-        <v>0.30453449487686157</v>
-      </c>
-      <c r="L8">
-        <v>3.902143631551413E-3</v>
-      </c>
-      <c r="M8">
-        <v>7.8042871318757534E-3</v>
-      </c>
-      <c r="N8">
-        <v>1.1226685519380439E-3</v>
-      </c>
-      <c r="O8">
-        <v>28508704.493796129</v>
-      </c>
-      <c r="P8">
-        <v>120</v>
-      </c>
-      <c r="Q8">
-        <v>20000</v>
-      </c>
-      <c r="R8" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="1"/>
-        <v>0.78487872626696631</v>
+        <v>0.29131995435649394</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="8">
         <v>0.1616254787212342</v>
       </c>
-      <c r="C9">
-        <v>6919.48779296875</v>
-      </c>
-      <c r="D9">
-        <v>0.16161872446537021</v>
-      </c>
-      <c r="E9">
+      <c r="C9" s="8">
+        <v>6909</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.1617928892374039</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2.2656438147805599E-7</v>
+      </c>
+      <c r="F9" s="8">
+        <v>3.1375173421110958E-5</v>
+      </c>
+      <c r="G9" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8">
+        <v>6250</v>
+      </c>
+      <c r="I9" s="8">
+        <v>7250</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0.55034726858139038</v>
+      </c>
+      <c r="K9" s="8">
+        <v>0.30288213491439819</v>
+      </c>
+      <c r="L9" s="8">
+        <v>1.1233916577990449E-3</v>
+      </c>
+      <c r="M9" s="8">
+        <v>2.246783347800374E-3</v>
+      </c>
+      <c r="N9" s="8">
+        <v>1.6741051616966929E-4</v>
+      </c>
+      <c r="O9" s="8">
+        <v>126980707.6534635</v>
+      </c>
+      <c r="P9" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>240000</v>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9">
         <f t="shared" si="0"/>
-        <v>4.5619972276302238E-11</v>
-      </c>
-      <c r="F9">
-        <v>2.9522683689720001E-5</v>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9">
+        <v>0.10357928557688167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8">
+        <v>0.1825493302612313</v>
+      </c>
+      <c r="C10" s="8">
+        <v>5977</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.18354858458042139</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3.2813471761983243E-7</v>
+      </c>
+      <c r="F10" s="8">
+        <v>3.5167820897186168E-5</v>
+      </c>
+      <c r="G10" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8">
+        <v>5250</v>
+      </c>
+      <c r="I10" s="8">
+        <v>6250</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0.54833275079727173</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0.30066877603530878</v>
+      </c>
+      <c r="L10" s="8">
+        <v>7.6040071115991573E-4</v>
+      </c>
+      <c r="M10" s="8">
+        <v>1.520801451988518E-3</v>
+      </c>
+      <c r="N10" s="3">
+        <v>7.2856512355887193E-4</v>
+      </c>
+      <c r="O10" s="8">
+        <v>5053463.1062353067</v>
+      </c>
+      <c r="P10" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>520000</v>
+      </c>
+      <c r="R10" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="0"/>
+        <v>0.39910588689439858</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8">
+        <v>0.20608022489221051</v>
+      </c>
+      <c r="C11" s="8">
+        <v>5238</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0.20641706883907321</v>
+      </c>
+      <c r="E11" s="8">
+        <v>6.6838879320130218E-6</v>
+      </c>
+      <c r="F11" s="8">
+        <v>4.5608339860336862E-5</v>
+      </c>
+      <c r="G11" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8">
+        <v>4750</v>
+      </c>
+      <c r="I11" s="8">
         <v>5750</v>
       </c>
-      <c r="I9">
-        <v>7250</v>
-      </c>
-      <c r="J9">
-        <v>0.54778468608856201</v>
-      </c>
-      <c r="K9">
-        <v>0.30006805062294012</v>
-      </c>
-      <c r="L9">
-        <v>3.8734226616336642E-3</v>
-      </c>
-      <c r="M9">
-        <v>7.7468454837799072E-3</v>
-      </c>
-      <c r="N9">
-        <f>B9-D9</f>
-        <v>6.7542558639943628E-6</v>
-      </c>
-      <c r="O9">
-        <v>16757861.71388893</v>
-      </c>
-      <c r="P9">
-        <v>120</v>
-      </c>
-      <c r="Q9">
-        <v>20000</v>
-      </c>
-      <c r="R9" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="1"/>
-        <v>4.1789549008197282E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>0.1825493302612313</v>
-      </c>
-      <c r="C10">
-        <v>5999.59765625</v>
-      </c>
-      <c r="D10">
-        <v>0.1818207651376724</v>
-      </c>
-      <c r="E10">
+      <c r="J11" s="8">
+        <v>0.5483708381652832</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0.30071058869361877</v>
+      </c>
+      <c r="L11" s="8">
+        <v>1.583010255152335E-3</v>
+      </c>
+      <c r="M11" s="8">
+        <v>3.1660206150263548E-3</v>
+      </c>
+      <c r="N11" s="8">
+        <v>3.3684394686264718E-4</v>
+      </c>
+      <c r="O11" s="8">
+        <v>48074134.203578062</v>
+      </c>
+      <c r="P11" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>120000</v>
+      </c>
+      <c r="R11" t="b">
+        <v>1</v>
+      </c>
+      <c r="S11">
         <f t="shared" si="0"/>
-        <v>5.3080713926639474E-7</v>
-      </c>
-      <c r="F10">
-        <v>3.1045878131408238E-5</v>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>5750</v>
-      </c>
-      <c r="I10">
-        <v>7250</v>
-      </c>
-      <c r="J10">
-        <v>0.54828858375549316</v>
-      </c>
-      <c r="K10">
-        <v>0.30062034726142878</v>
-      </c>
-      <c r="L10">
-        <v>3.876985756206775E-3</v>
-      </c>
-      <c r="M10">
-        <v>7.7539714984595784E-3</v>
-      </c>
-      <c r="N10">
-        <v>7.2856512355887193E-4</v>
-      </c>
-      <c r="O10">
-        <v>12491933.049825611</v>
-      </c>
-      <c r="P10">
-        <v>120</v>
-      </c>
-      <c r="Q10">
-        <v>20000</v>
-      </c>
-      <c r="R10" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="1"/>
-        <v>0.39910588689439858</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>0.20608022489221051</v>
-      </c>
-      <c r="C11">
-        <v>5246.669921875</v>
-      </c>
-      <c r="D11">
-        <v>0.20512519776821139</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>9.1207680757401852E-7</v>
-      </c>
-      <c r="F11">
-        <v>4.5797616621712223E-5</v>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>4750</v>
-      </c>
-      <c r="I11">
-        <v>6250</v>
-      </c>
-      <c r="J11">
-        <v>0.54416519403457642</v>
-      </c>
-      <c r="K11">
-        <v>0.29611572623252869</v>
-      </c>
-      <c r="L11">
-        <v>3.847828987875424E-3</v>
-      </c>
-      <c r="M11">
-        <v>7.6956581324338913E-3</v>
-      </c>
-      <c r="N11">
-        <v>9.5502712399916923E-4</v>
-      </c>
-      <c r="O11">
-        <v>6644748.8053372381</v>
-      </c>
-      <c r="P11">
-        <v>120</v>
-      </c>
-      <c r="Q11">
-        <v>20000</v>
-      </c>
-      <c r="R11" t="b">
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="1"/>
-        <v>0.46342492323011231</v>
+        <v>0.16345282379172099</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -1226,374 +1284,368 @@
         <v>1</v>
       </c>
       <c r="S12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.28548733167222518</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="8">
         <v>0.26217753565747121</v>
       </c>
-      <c r="C13">
-        <v>4005.86962890625</v>
-      </c>
-      <c r="D13">
-        <v>0.2642558217048645</v>
-      </c>
-      <c r="E13">
+      <c r="C13" s="8">
+        <v>4017</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.26168420910835272</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3.8433540794358118E-7</v>
+      </c>
+      <c r="F13" s="8">
+        <v>6.7063774622511119E-5</v>
+      </c>
+      <c r="G13" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8">
+        <v>3250</v>
+      </c>
+      <c r="I13" s="8">
+        <v>4250</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0.54734569787979126</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0.29958733916282648</v>
+      </c>
+      <c r="L13" s="8">
+        <v>1.1669449488213299E-3</v>
+      </c>
+      <c r="M13" s="8">
+        <v>2.3338899482041602E-3</v>
+      </c>
+      <c r="N13" s="8">
+        <v>4.9332654911848905E-4</v>
+      </c>
+      <c r="O13" s="8">
+        <v>6948227.5742930649</v>
+      </c>
+      <c r="P13" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>220000</v>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13">
         <f t="shared" si="0"/>
-        <v>4.3192728947896503E-6</v>
-      </c>
-      <c r="F13">
-        <v>7.178896339610219E-5</v>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13">
+        <v>0.1881650721452385</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0.29541712804948039</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3520</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.29488134384155268</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2.0747364033013579E-5</v>
+      </c>
+      <c r="F14" s="5">
+        <v>8.6557003669440746E-5</v>
+      </c>
+      <c r="G14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5">
+        <v>3250</v>
+      </c>
+      <c r="I14" s="5">
+        <v>4250</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0.54577392339706421</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0.29786917567253107</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1.7258886854609841E-3</v>
+      </c>
+      <c r="M14" s="5">
+        <v>3.4517776221036911E-3</v>
+      </c>
+      <c r="N14" s="5">
+        <v>5.3578420792765868E-4</v>
+      </c>
+      <c r="O14" s="5">
+        <v>4171051.896944467</v>
+      </c>
+      <c r="P14" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>100000</v>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="0"/>
+        <v>0.18136531604149858</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8">
+        <v>0.33260991979033733</v>
+      </c>
+      <c r="C15" s="8">
+        <v>3095</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.33310297131538391</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.608051206858363E-5</v>
+      </c>
+      <c r="F15" s="8">
+        <v>1.109635559259914E-4</v>
+      </c>
+      <c r="G15" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="8">
+        <v>2750</v>
+      </c>
+      <c r="I15" s="8">
         <v>3750</v>
       </c>
-      <c r="I13">
-        <v>5250</v>
-      </c>
-      <c r="J13">
-        <v>0.54493433237075806</v>
-      </c>
-      <c r="K13">
-        <v>0.29695343971252441</v>
-      </c>
-      <c r="L13">
-        <v>3.8532676172072702E-3</v>
-      </c>
-      <c r="M13">
-        <v>7.7065350487828246E-3</v>
-      </c>
-      <c r="N13">
-        <v>2.0782860473933522E-3</v>
-      </c>
-      <c r="O13">
-        <v>2619060.000737112</v>
-      </c>
-      <c r="P13">
-        <v>120</v>
-      </c>
-      <c r="Q13">
-        <v>20000</v>
-      </c>
-      <c r="R13" t="b">
-        <v>1</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="1"/>
-        <v>0.79270180115987665</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>0.29541712804948039</v>
-      </c>
-      <c r="C14">
-        <v>3519.489990234375</v>
-      </c>
-      <c r="D14">
-        <v>0.29931411147117609</v>
-      </c>
-      <c r="E14">
+      <c r="J15" s="8">
+        <v>0.54862445592880249</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0.30098879337310791</v>
+      </c>
+      <c r="L15" s="8">
+        <v>1.1198749811980029E-3</v>
+      </c>
+      <c r="M15" s="8">
+        <v>2.2397499997168779E-3</v>
+      </c>
+      <c r="N15" s="8">
+        <v>4.9305152504663941E-4</v>
+      </c>
+      <c r="O15" s="8">
+        <v>16243112.95374831</v>
+      </c>
+      <c r="P15" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>240000</v>
+      </c>
+      <c r="R15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S15">
         <f t="shared" si="0"/>
-        <v>1.5186479788971117E-5</v>
-      </c>
-      <c r="F14">
-        <v>8.4665764006786048E-5</v>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14">
+        <v>0.14823716783836074</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8">
+        <v>0.37415664623331951</v>
+      </c>
+      <c r="C16" s="8">
+        <v>2735</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.37379944324493408</v>
+      </c>
+      <c r="E16" s="8">
+        <v>5.6602090126034448E-8</v>
+      </c>
+      <c r="F16" s="8">
+        <v>1.470321585657075E-4</v>
+      </c>
+      <c r="G16" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="8">
+        <v>2250</v>
+      </c>
+      <c r="I16" s="8">
+        <v>3250</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0.54861003160476685</v>
+      </c>
+      <c r="K16" s="8">
+        <v>0.30097296833991999</v>
+      </c>
+      <c r="L16" s="8">
+        <v>1.036775507415356E-3</v>
+      </c>
+      <c r="M16" s="8">
+        <v>2.0735510624945159E-3</v>
+      </c>
+      <c r="N16" s="8">
+        <v>3.5720298838537451E-4</v>
+      </c>
+      <c r="O16" s="8">
+        <v>5782096.6497019297</v>
+      </c>
+      <c r="P16" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>280000</v>
+      </c>
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="0"/>
+        <v>9.5468834238648562E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8">
+        <v>0.4204803812220419</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2418</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0.42015156149864202</v>
+      </c>
+      <c r="E17" s="8">
+        <v>4.3501304958226678E-7</v>
+      </c>
+      <c r="F17" s="8">
+        <v>1.793150877347216E-4</v>
+      </c>
+      <c r="G17" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1750</v>
+      </c>
+      <c r="I17" s="8">
         <v>2750</v>
       </c>
-      <c r="I14">
-        <v>4250</v>
-      </c>
-      <c r="J14">
-        <v>0.55061483383178711</v>
-      </c>
-      <c r="K14">
-        <v>0.30317670106887817</v>
-      </c>
-      <c r="L14">
-        <v>3.8934348282436068E-3</v>
-      </c>
-      <c r="M14">
-        <v>7.7868695370852947E-3</v>
-      </c>
-      <c r="N14">
-        <v>3.8969834216956989E-3</v>
-      </c>
-      <c r="O14">
-        <v>1749101.084245757</v>
-      </c>
-      <c r="P14">
-        <v>120</v>
-      </c>
-      <c r="Q14">
-        <v>20000</v>
-      </c>
-      <c r="R14" t="b">
-        <v>1</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="1"/>
-        <v>1.3191460655737537</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>0.33260991979033733</v>
-      </c>
-      <c r="C15">
-        <v>3091.037109375</v>
-      </c>
-      <c r="D15">
-        <v>0.33368292450904852</v>
-      </c>
-      <c r="E15">
+      <c r="J17" s="8">
+        <v>0.54805046319961548</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0.30035927891731262</v>
+      </c>
+      <c r="L17" s="8">
+        <v>7.4580221563057107E-4</v>
+      </c>
+      <c r="M17" s="8">
+        <v>1.4916043728590009E-3</v>
+      </c>
+      <c r="N17" s="8">
+        <v>3.2881972339993132E-4</v>
+      </c>
+      <c r="O17" s="8">
+        <v>5831329.822522331</v>
+      </c>
+      <c r="P17" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>540000</v>
+      </c>
+      <c r="R17" t="b">
+        <v>1</v>
+      </c>
+      <c r="S17">
         <f t="shared" si="0"/>
-        <v>1.1513391263764805E-6</v>
-      </c>
-      <c r="F15">
-        <v>1.1837275815196339E-4</v>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15">
+        <v>7.8200966819018461E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8">
+        <v>0.47202271129371798</v>
+      </c>
+      <c r="C18" s="8">
+        <v>2137</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0.47170323133468628</v>
+      </c>
+      <c r="E18" s="8">
+        <v>5.634854005620582E-6</v>
+      </c>
+      <c r="F18" s="8">
+        <v>2.3557996610179541E-4</v>
+      </c>
+      <c r="G18" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="8">
+        <v>1750</v>
+      </c>
+      <c r="I18" s="8">
         <v>2750</v>
       </c>
-      <c r="I15">
-        <v>4250</v>
-      </c>
-      <c r="J15">
-        <v>0.54738181829452515</v>
-      </c>
-      <c r="K15">
-        <v>0.29962685704231262</v>
-      </c>
-      <c r="L15">
-        <v>3.8705739561428129E-3</v>
-      </c>
-      <c r="M15">
-        <v>7.741148117929697E-3</v>
-      </c>
-      <c r="N15">
-        <v>1.0730047187111902E-3</v>
-      </c>
-      <c r="O15">
-        <v>986897.21214908699</v>
-      </c>
-      <c r="P15">
-        <v>120</v>
-      </c>
-      <c r="Q15">
-        <v>20000</v>
-      </c>
-      <c r="R15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="1"/>
-        <v>0.32260153857935603</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>0.37415664623331951</v>
-      </c>
-      <c r="C16">
-        <v>2726.815673828125</v>
-      </c>
-      <c r="D16">
-        <v>0.37100070714950562</v>
-      </c>
-      <c r="E16">
+      <c r="J18" s="8">
+        <v>0.54796117544174194</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0.30026146769523621</v>
+      </c>
+      <c r="L18" s="8">
+        <v>8.0792467604067213E-4</v>
+      </c>
+      <c r="M18" s="8">
+        <v>1.6158494399860499E-3</v>
+      </c>
+      <c r="N18" s="8">
+        <v>3.1947995903169879E-4</v>
+      </c>
+      <c r="O18" s="8">
+        <v>900934.65870304138</v>
+      </c>
+      <c r="P18" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>460000</v>
+      </c>
+      <c r="R18" t="b">
+        <v>1</v>
+      </c>
+      <c r="S18">
         <f t="shared" si="0"/>
-        <v>9.9599515007440983E-6</v>
-      </c>
-      <c r="F16">
-        <v>1.423599605914205E-4</v>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>2000</v>
-      </c>
-      <c r="I16">
-        <v>3250</v>
-      </c>
-      <c r="J16">
-        <v>0.54629391431808472</v>
-      </c>
-      <c r="K16">
-        <v>0.29843702912330627</v>
-      </c>
-      <c r="L16">
-        <v>3.862881313352605E-3</v>
-      </c>
-      <c r="M16">
-        <v>7.7257626689970493E-3</v>
-      </c>
-      <c r="N16">
-        <v>3.1559390838138968E-3</v>
-      </c>
-      <c r="O16">
-        <v>648484.04729090398</v>
-      </c>
-      <c r="P16">
-        <v>120</v>
-      </c>
-      <c r="Q16">
-        <v>20000</v>
-      </c>
-      <c r="R16" t="b">
-        <v>1</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="1"/>
-        <v>0.8434806960093103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>0.4204803812220419</v>
-      </c>
-      <c r="C17">
-        <v>2410.089111328125</v>
-      </c>
-      <c r="D17">
-        <v>0.42623931169509888</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="0"/>
-        <v>3.3165280193504268E-5</v>
-      </c>
-      <c r="F17">
-        <v>1.8552149413153529E-4</v>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>2000</v>
-      </c>
-      <c r="I17">
-        <v>3250</v>
-      </c>
-      <c r="J17">
-        <v>0.54987722635269165</v>
-      </c>
-      <c r="K17">
-        <v>0.30236497521400452</v>
-      </c>
-      <c r="L17">
-        <v>3.8882191557403842E-3</v>
-      </c>
-      <c r="M17">
-        <v>7.7764382585883141E-3</v>
-      </c>
-      <c r="N17">
-        <v>5.7589304730569779E-3</v>
-      </c>
-      <c r="O17">
-        <v>394011.02694328671</v>
-      </c>
-      <c r="P17">
-        <v>120</v>
-      </c>
-      <c r="Q17">
-        <v>20000</v>
-      </c>
-      <c r="R17" t="b">
-        <v>1</v>
-      </c>
-      <c r="S17">
-        <f t="shared" si="1"/>
-        <v>1.3696074133874692</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>0.47202271129371798</v>
-      </c>
-      <c r="C18">
-        <v>2134.518798828125</v>
-      </c>
-      <c r="D18">
-        <v>0.47369569540023798</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="0"/>
-        <v>2.7988758206685343E-6</v>
-      </c>
-      <c r="F18">
-        <v>2.288785035489127E-4</v>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>2000</v>
-      </c>
-      <c r="I18">
-        <v>3250</v>
-      </c>
-      <c r="J18">
-        <v>0.54985135793685913</v>
-      </c>
-      <c r="K18">
-        <v>0.30233651399612432</v>
-      </c>
-      <c r="L18">
-        <v>3.8880362384178472E-3</v>
-      </c>
-      <c r="M18">
-        <v>7.7760722488164902E-3</v>
-      </c>
-      <c r="N18">
-        <v>1.672984106520059E-3</v>
-      </c>
-      <c r="O18">
-        <v>253433.07240539431</v>
-      </c>
-      <c r="P18">
-        <v>120</v>
-      </c>
-      <c r="Q18">
-        <v>20000</v>
-      </c>
-      <c r="R18" t="b">
-        <v>1</v>
-      </c>
-      <c r="S18">
-        <f t="shared" si="1"/>
-        <v>0.35442873118006352</v>
+        <v>6.7683175276899155E-2</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -1610,7 +1662,7 @@
         <v>0.52636730670928955</v>
       </c>
       <c r="E19">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E18:E66" si="1">(B19-D19)^2</f>
         <v>8.242269720510988E-6</v>
       </c>
       <c r="F19">
@@ -1653,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="S19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.54246558749282658</v>
       </c>
     </row>
@@ -1671,7 +1723,7 @@
         <v>0.59066981077194214</v>
       </c>
       <c r="E20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.6761842597220721E-6</v>
       </c>
       <c r="F20">
@@ -1714,7 +1766,7 @@
         <v>1</v>
       </c>
       <c r="S20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.32355372706388208</v>
       </c>
     </row>
@@ -1732,7 +1784,7 @@
         <v>0.66252553462982178</v>
       </c>
       <c r="E21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3759516974982108E-15</v>
       </c>
       <c r="F21">
@@ -1775,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="S21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.5988521257120927E-6</v>
       </c>
     </row>
@@ -1835,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="S22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4.7767266704893972E-2</v>
       </c>
     </row>
@@ -1853,7 +1905,7 @@
         <v>0.8248019814491272</v>
       </c>
       <c r="E23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.156618265980115E-7</v>
       </c>
       <c r="F23">
@@ -1896,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="S23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.10961782396984278</v>
       </c>
     </row>
@@ -1914,7 +1966,7 @@
         <v>0.92241066694259644</v>
       </c>
       <c r="E24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.9784189166900559E-5</v>
       </c>
       <c r="F24">
@@ -1957,7 +2009,7 @@
         <v>1</v>
       </c>
       <c r="S24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.68851095905452109</v>
       </c>
     </row>
@@ -1975,7 +2027,7 @@
         <v>1.0130019187927251</v>
       </c>
       <c r="E25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.153707170055961E-5</v>
       </c>
       <c r="F25">
@@ -2018,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="S25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.33418254417475352</v>
       </c>
     </row>
@@ -2036,7 +2088,7 @@
         <v>1.123741030693054</v>
       </c>
       <c r="E26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.553026332235015E-6</v>
       </c>
       <c r="F26">
@@ -2079,7 +2131,7 @@
         <v>1</v>
       </c>
       <c r="S26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.11077501433831266</v>
       </c>
     </row>
@@ -2097,7 +2149,7 @@
         <v>1.242001533508301</v>
       </c>
       <c r="E27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.867646055540535E-9</v>
       </c>
       <c r="F27">
@@ -2140,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="S27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.4796876937884459E-3</v>
       </c>
     </row>
@@ -2158,7 +2210,7 @@
         <v>1.368261575698853</v>
       </c>
       <c r="E28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.9545311894184814E-7</v>
       </c>
       <c r="F28">
@@ -2201,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="S28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7.2972306555972713E-2</v>
       </c>
     </row>
@@ -2219,7 +2271,7 @@
         <v>1.5002703666687009</v>
       </c>
       <c r="E29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.8122900967765719E-7</v>
       </c>
       <c r="F29">
@@ -2262,7 +2314,7 @@
         <v>1</v>
       </c>
       <c r="S29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.8367503131860618E-2</v>
       </c>
     </row>
@@ -2280,7 +2332,7 @@
         <v>1.6453398466110229</v>
       </c>
       <c r="E30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2060788203594927E-5</v>
       </c>
       <c r="F30">
@@ -2323,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="S30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.21151923943697956</v>
       </c>
     </row>
@@ -2341,7 +2393,7 @@
         <v>1.7935007810592649</v>
       </c>
       <c r="E31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0947879205780598E-5</v>
       </c>
       <c r="F31">
@@ -2384,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="S31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.18482698573388812</v>
       </c>
     </row>
@@ -2444,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="S32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4.583090426013927E-3</v>
       </c>
     </row>
@@ -2462,7 +2514,7 @@
         <v>2.103854656219482</v>
       </c>
       <c r="E33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.1539668908396683E-6</v>
       </c>
       <c r="F33">
@@ -2505,7 +2557,7 @@
         <v>1</v>
       </c>
       <c r="S33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.1033957365229358E-2</v>
       </c>
     </row>
@@ -2523,7 +2575,7 @@
         <v>2.268501996994019</v>
       </c>
       <c r="E34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.998945255478072E-7</v>
       </c>
       <c r="F34">
@@ -2566,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="S34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.7868430810511803E-2</v>
       </c>
     </row>
@@ -2584,7 +2636,7 @@
         <v>2.4397609233856201</v>
       </c>
       <c r="E35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.338313588623241E-5</v>
       </c>
       <c r="F35">
@@ -2627,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="S35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.15017006328497925</v>
       </c>
     </row>
@@ -2645,7 +2697,7 @@
         <v>2.6028010845184331</v>
       </c>
       <c r="E36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.1766252271953018E-6</v>
       </c>
       <c r="F36">
@@ -2688,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="S36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.6650630776740339E-2</v>
       </c>
     </row>
@@ -2706,7 +2758,7 @@
         <v>2.774096012115479</v>
       </c>
       <c r="E37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.5276902299589098E-6</v>
       </c>
       <c r="F37">
@@ -2749,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="S37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7.6762677254653286E-2</v>
       </c>
     </row>
@@ -2767,7 +2819,7 @@
         <v>2.9404647350311279</v>
       </c>
       <c r="E38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.3921462974435056E-6</v>
       </c>
       <c r="F38">
@@ -2810,7 +2862,7 @@
         <v>1</v>
       </c>
       <c r="S38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.10433243006341508</v>
       </c>
     </row>
@@ -2828,7 +2880,7 @@
         <v>3.09555983543396</v>
       </c>
       <c r="E39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0168525775846671E-5</v>
       </c>
       <c r="F39">
@@ -2871,7 +2923,7 @@
         <v>1</v>
       </c>
       <c r="S39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.10290646188957213</v>
       </c>
     </row>
@@ -2889,7 +2941,7 @@
         <v>3.2546195983886719</v>
       </c>
       <c r="E40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.8375716576251172E-7</v>
       </c>
       <c r="F40">
@@ -2932,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="S40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.3172830744431957E-2</v>
       </c>
     </row>
@@ -2950,7 +3002,7 @@
         <v>3.4018938541412349</v>
       </c>
       <c r="E41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.0765993476111782E-9</v>
       </c>
       <c r="F41">
@@ -2993,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="S41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.6304505520652393E-3</v>
       </c>
     </row>
@@ -3011,7 +3063,7 @@
         <v>3.5418522357940669</v>
       </c>
       <c r="E42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.3096631643562933E-6</v>
       </c>
       <c r="F42">
@@ -3054,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="S42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.1260417969444527E-3</v>
       </c>
     </row>
@@ -3072,7 +3124,7 @@
         <v>3.670695304870605</v>
       </c>
       <c r="E43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.5570068644861231E-6</v>
       </c>
       <c r="F43">
@@ -3115,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="S43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.17717840620584274</v>
       </c>
     </row>
@@ -3133,7 +3185,7 @@
         <v>3.7893028259277339</v>
       </c>
       <c r="E44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.1767391787733612E-5</v>
       </c>
       <c r="F44">
@@ -3176,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="S44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.0592376659295051E-2</v>
       </c>
     </row>
@@ -3194,7 +3246,7 @@
         <v>3.8793566226959229</v>
       </c>
       <c r="E45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4318549446444133E-5</v>
       </c>
       <c r="F45">
@@ -3237,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.6236769772406932E-2</v>
       </c>
     </row>
@@ -3255,7 +3307,7 @@
         <v>3.9724795818328862</v>
       </c>
       <c r="E46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.0759109700624383E-6</v>
       </c>
       <c r="F46">
@@ -3298,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="S46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.13192348415881053</v>
       </c>
     </row>
@@ -3316,7 +3368,7 @@
         <v>4.0410537719726563</v>
       </c>
       <c r="E47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3176900672230462E-6</v>
       </c>
       <c r="F47">
@@ -3359,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="S47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.1021856930743399E-2</v>
       </c>
     </row>
@@ -3377,7 +3429,7 @@
         <v>4.1021084785461426</v>
       </c>
       <c r="E48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.5379726275339526E-5</v>
       </c>
       <c r="F48">
@@ -3420,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="S48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.5186513811953603E-3</v>
       </c>
     </row>
@@ -3438,7 +3490,7 @@
         <v>4.1341972351074219</v>
       </c>
       <c r="E49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.5400278439493646E-7</v>
       </c>
       <c r="F49">
@@ -3481,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="S49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5925153256168001E-2</v>
       </c>
     </row>
@@ -3499,7 +3551,7 @@
         <v>4.161799430847168</v>
       </c>
       <c r="E50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.3552135764089973E-5</v>
       </c>
       <c r="F50">
@@ -3542,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="S50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.6846171329022414E-2</v>
       </c>
     </row>
@@ -3560,7 +3612,7 @@
         <v>4.1563525199890137</v>
       </c>
       <c r="E51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0252806091137026E-5</v>
       </c>
       <c r="F51">
@@ -3603,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="S51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.5710231702699873E-2</v>
       </c>
     </row>
@@ -3621,7 +3673,7 @@
         <v>4.1424875259399414</v>
       </c>
       <c r="E52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0723853017531858E-5</v>
       </c>
       <c r="F52">
@@ -3664,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="S52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.9770525134329854E-3</v>
       </c>
     </row>
@@ -3682,7 +3734,7 @@
         <v>4.1215057373046884</v>
       </c>
       <c r="E53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.4966367850085851E-5</v>
       </c>
       <c r="F53">
@@ -3725,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="S53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.10449365454884546</v>
       </c>
     </row>
@@ -3743,7 +3795,7 @@
         <v>4.0627474784851074</v>
       </c>
       <c r="E54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.8181924270618406E-5</v>
       </c>
       <c r="F54">
@@ -3786,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="S54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.3124394244231933E-2</v>
       </c>
     </row>
@@ -3804,7 +3856,7 @@
         <v>4.0063467025756836</v>
       </c>
       <c r="E55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.1754306527273798E-5</v>
       </c>
       <c r="F55">
@@ -3847,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="S55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4.4944781120918417E-2</v>
       </c>
     </row>
@@ -3865,7 +3917,7 @@
         <v>3.9237735271453862</v>
       </c>
       <c r="E56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.0117339994851722E-7</v>
       </c>
       <c r="F56">
@@ -3908,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="S56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.3988305844643242E-2</v>
       </c>
     </row>
@@ -3926,7 +3978,7 @@
         <v>3.828858613967896</v>
       </c>
       <c r="E57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3100595793617298E-9</v>
       </c>
       <c r="F57">
@@ -3969,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="S57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8.7070167997500308E-2</v>
       </c>
     </row>
@@ -3987,7 +4039,7 @@
         <v>3.7188000679016109</v>
       </c>
       <c r="E58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.9648608678536969E-6</v>
       </c>
       <c r="F58">
@@ -4030,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="S58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.3515386849396565E-2</v>
       </c>
     </row>
@@ -4048,7 +4100,7 @@
         <v>3.603272676467896</v>
       </c>
       <c r="E59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.2705356427097528E-6</v>
       </c>
       <c r="F59">
@@ -4091,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="S59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7.9876025886476978E-2</v>
       </c>
     </row>
@@ -4109,7 +4161,7 @@
         <v>3.4685320854187012</v>
       </c>
       <c r="E60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.0154297856341968E-7</v>
       </c>
       <c r="F60">
@@ -4152,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="S60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5829242883427387E-2</v>
       </c>
     </row>
@@ -4170,7 +4222,7 @@
         <v>3.3293106555938721</v>
       </c>
       <c r="E61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.4630389314315915E-7</v>
       </c>
       <c r="F61">
@@ -4213,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="S61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.5954713427319722E-2</v>
       </c>
     </row>
@@ -4231,7 +4283,7 @@
         <v>3.181837797164917</v>
       </c>
       <c r="E62">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.5792975633841161E-6</v>
       </c>
       <c r="F62">
@@ -4274,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="S62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.0500066620254268E-2</v>
       </c>
     </row>
@@ -4292,7 +4344,7 @@
         <v>3.0251514911651598</v>
       </c>
       <c r="E63">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2705632340071172E-6</v>
       </c>
       <c r="F63">
@@ -4335,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="S63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.7246821978876743E-2</v>
       </c>
     </row>
@@ -4353,7 +4405,7 @@
         <v>2.8730683326721191</v>
       </c>
       <c r="E64">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.0908302838872642E-5</v>
       </c>
       <c r="F64">
@@ -4396,7 +4448,7 @@
         <v>0</v>
       </c>
       <c r="S64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.15940618814755253</v>
       </c>
     </row>
@@ -4414,7 +4466,7 @@
         <v>2.7025988101959229</v>
       </c>
       <c r="E65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.8633811545955397E-5</v>
       </c>
       <c r="F65">
@@ -4457,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="S65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.22945869840941302</v>
       </c>
     </row>
@@ -4475,7 +4527,7 @@
         <v>2.5520672798156738</v>
       </c>
       <c r="E66">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.5431443770434383E-6</v>
       </c>
       <c r="F66">
@@ -4518,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="S66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.11466065890472625</v>
       </c>
     </row>
@@ -6721,7 +6773,7 @@
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="S103">
         <f>AVERAGE(S2:S102)</f>
-        <v>0.25012349277108109</v>
+        <v>0.13100739392912197</v>
       </c>
     </row>
   </sheetData>

--- a/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix.xlsx
+++ b/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13448522-95BD-4E64-9135-FD8CCBD6EE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB3019F-232B-4D82-AD13-A2BEE30C29F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1649,64 +1649,63 @@
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="5">
         <v>0.52923824204825332</v>
       </c>
-      <c r="C19">
-        <v>1887.880981445312</v>
-      </c>
-      <c r="D19">
-        <v>0.52636730670928955</v>
-      </c>
-      <c r="E19">
-        <f t="shared" ref="E18:E66" si="1">(B19-D19)^2</f>
-        <v>8.242269720510988E-6</v>
-      </c>
-      <c r="F19">
-        <v>2.7226036763750022E-4</v>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>1775</v>
-      </c>
-      <c r="I19">
-        <v>1925</v>
-      </c>
-      <c r="J19">
-        <v>0.54893946647644043</v>
-      </c>
-      <c r="K19">
-        <v>0.30133455991745001</v>
-      </c>
-      <c r="L19">
-        <v>3.881588192064165E-3</v>
-      </c>
-      <c r="M19">
-        <v>7.7631762251257896E-3</v>
-      </c>
-      <c r="N19">
-        <v>2.8709353389637648E-3</v>
-      </c>
-      <c r="O19">
-        <v>264805.65005861939</v>
-      </c>
-      <c r="P19">
+      <c r="C19" s="5">
+        <v>1883</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0.52974724769592285</v>
+      </c>
+      <c r="E19" s="5">
+        <v>5.1842616812791684E-6</v>
+      </c>
+      <c r="F19" s="5">
+        <v>3.0343793332576752E-4</v>
+      </c>
+      <c r="G19" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1250</v>
+      </c>
+      <c r="I19" s="5">
+        <v>2250</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0.54753077030181885</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0.29978996515274048</v>
+      </c>
+      <c r="L19" s="5">
+        <v>7.4509500317359873E-4</v>
+      </c>
+      <c r="M19" s="5">
+        <v>1.4901900431141259E-3</v>
+      </c>
+      <c r="N19" s="5">
+        <v>5.0900564766953593E-4</v>
+      </c>
+      <c r="O19" s="5">
+        <v>169699.3904836897</v>
+      </c>
+      <c r="P19" s="5">
         <v>100</v>
       </c>
-      <c r="Q19">
-        <v>20000</v>
+      <c r="Q19" s="6">
+        <v>540000</v>
       </c>
       <c r="R19" t="b">
         <v>1</v>
       </c>
       <c r="S19">
         <f t="shared" si="0"/>
-        <v>0.54246558749282658</v>
+        <v>9.6177034694164693E-2</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -1723,7 +1722,7 @@
         <v>0.59066981077194214</v>
       </c>
       <c r="E20">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E19:E66" si="1">(B20-D20)^2</f>
         <v>3.6761842597220721E-6</v>
       </c>
       <c r="F20">
@@ -6773,7 +6772,7 @@
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="S103">
         <f>AVERAGE(S2:S102)</f>
-        <v>0.13100739392912197</v>
+        <v>0.12658869538656098</v>
       </c>
     </row>
   </sheetData>

--- a/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix.xlsx
+++ b/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB3019F-232B-4D82-AD13-A2BEE30C29F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49926716-DE25-4D19-84C9-446F0DE71A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -230,7 +230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -245,6 +245,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -553,7 +560,8 @@
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -576,7 +584,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -635,7 +643,7 @@
       <c r="B2" s="3">
         <v>6.8255138645384933E-2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="11">
         <v>19798</v>
       </c>
       <c r="D2" s="3">
@@ -695,7 +703,7 @@
       <c r="B3" s="5">
         <v>7.7261312811500088E-2</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="12">
         <v>16863</v>
       </c>
       <c r="D3" s="5">
@@ -755,7 +763,7 @@
       <c r="B4" s="5">
         <v>8.7437268462869769E-2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="12">
         <v>14373</v>
       </c>
       <c r="D4" s="5">
@@ -815,7 +823,7 @@
       <c r="B5" s="8">
         <v>9.8929739735079153E-2</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="13">
         <v>12427</v>
       </c>
       <c r="D5" s="8">
@@ -875,7 +883,7 @@
       <c r="B6" s="8">
         <v>0.1119024130228327</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="13">
         <v>10704</v>
       </c>
       <c r="D6" s="8">
@@ -935,7 +943,7 @@
       <c r="B7" s="5">
         <v>0.12653747766179149</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="12">
         <v>9137</v>
       </c>
       <c r="D7" s="5">
@@ -995,7 +1003,7 @@
       <c r="B8" s="8">
         <v>0.14303719980762769</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="13">
         <v>8009</v>
       </c>
       <c r="D8" s="8">
@@ -1055,7 +1063,7 @@
       <c r="B9" s="8">
         <v>0.1616254787212342</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="13">
         <v>6909</v>
       </c>
       <c r="D9" s="8">
@@ -1115,7 +1123,7 @@
       <c r="B10" s="8">
         <v>0.1825493302612313</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="13">
         <v>5977</v>
       </c>
       <c r="D10" s="8">
@@ -1175,7 +1183,7 @@
       <c r="B11" s="8">
         <v>0.20608022489221051</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="13">
         <v>5238</v>
       </c>
       <c r="D11" s="8">
@@ -1235,7 +1243,7 @@
       <c r="B12" s="3">
         <v>0.23251518669686461</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="11">
         <v>4579.56005859375</v>
       </c>
       <c r="D12" s="3">
@@ -1295,7 +1303,7 @@
       <c r="B13" s="8">
         <v>0.26217753565747121</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="13">
         <v>4017</v>
       </c>
       <c r="D13" s="8">
@@ -1355,7 +1363,7 @@
       <c r="B14" s="5">
         <v>0.29541712804948039</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="12">
         <v>3520</v>
       </c>
       <c r="D14" s="5">
@@ -1415,7 +1423,7 @@
       <c r="B15" s="8">
         <v>0.33260991979033733</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="13">
         <v>3095</v>
       </c>
       <c r="D15" s="8">
@@ -1475,7 +1483,7 @@
       <c r="B16" s="8">
         <v>0.37415664623331951</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="13">
         <v>2735</v>
       </c>
       <c r="D16" s="8">
@@ -1535,7 +1543,7 @@
       <c r="B17" s="8">
         <v>0.4204803812220419</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="13">
         <v>2418</v>
       </c>
       <c r="D17" s="8">
@@ -1595,7 +1603,7 @@
       <c r="B18" s="8">
         <v>0.47202271129371798</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="13">
         <v>2137</v>
       </c>
       <c r="D18" s="8">
@@ -1655,7 +1663,7 @@
       <c r="B19" s="5">
         <v>0.52923824204825332</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="12">
         <v>1883</v>
       </c>
       <c r="D19" s="5">
@@ -1709,125 +1717,123 @@
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="8">
         <v>0.59258714857726547</v>
       </c>
-      <c r="C20">
-        <v>1678.790771484375</v>
-      </c>
-      <c r="D20">
-        <v>0.59066981077194214</v>
-      </c>
-      <c r="E20">
-        <f t="shared" ref="E19:E66" si="1">(B20-D20)^2</f>
-        <v>3.6761842597220721E-6</v>
-      </c>
-      <c r="F20">
-        <v>4.1176131344400352E-4</v>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>1675</v>
-      </c>
-      <c r="I20">
-        <v>1825</v>
-      </c>
-      <c r="J20">
-        <v>0.54675513505935669</v>
-      </c>
-      <c r="K20">
-        <v>0.29894119501113892</v>
-      </c>
-      <c r="L20">
-        <v>3.8661426364903781E-3</v>
-      </c>
-      <c r="M20">
-        <v>7.7322851866483688E-3</v>
-      </c>
-      <c r="N20">
-        <v>1.917337805323327E-3</v>
-      </c>
-      <c r="O20">
-        <v>139657.45136251021</v>
-      </c>
-      <c r="P20">
+      <c r="C20" s="13">
+        <v>1677</v>
+      </c>
+      <c r="D20" s="8">
+        <v>0.59311950206756592</v>
+      </c>
+      <c r="E20" s="8">
+        <v>4.4358569084579358E-7</v>
+      </c>
+      <c r="F20" s="8">
+        <v>3.7227064603939652E-4</v>
+      </c>
+      <c r="G20" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8">
+        <v>1250</v>
+      </c>
+      <c r="I20" s="8">
+        <v>2250</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0.54768466949462891</v>
+      </c>
+      <c r="K20" s="8">
+        <v>0.2999584972858429</v>
+      </c>
+      <c r="L20" s="8">
+        <v>9.1280778249104816E-4</v>
+      </c>
+      <c r="M20" s="8">
+        <v>1.825615530833602E-3</v>
+      </c>
+      <c r="N20" s="8">
+        <v>5.3235349030045231E-4</v>
+      </c>
+      <c r="O20" s="8">
+        <v>1352956.0410496821</v>
+      </c>
+      <c r="P20" s="8">
         <v>100</v>
       </c>
-      <c r="Q20">
-        <v>20000</v>
+      <c r="Q20" s="9">
+        <v>360000</v>
       </c>
       <c r="R20" t="b">
         <v>1</v>
       </c>
       <c r="S20">
         <f t="shared" si="0"/>
-        <v>0.32355372706388208</v>
+        <v>8.9835476786591248E-2</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="5">
         <v>0.66252549753599888</v>
       </c>
-      <c r="C21">
-        <v>1491.0595703125</v>
-      </c>
-      <c r="D21">
-        <v>0.66252553462982178</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="1"/>
-        <v>1.3759516974982108E-15</v>
-      </c>
-      <c r="F21">
-        <v>4.2105832835659379E-4</v>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <v>1475</v>
-      </c>
-      <c r="I21">
-        <v>1625</v>
-      </c>
-      <c r="J21">
-        <v>0.54694944620132446</v>
-      </c>
-      <c r="K21">
-        <v>0.29915368556976318</v>
-      </c>
-      <c r="L21">
-        <v>3.8675166237518328E-3</v>
-      </c>
-      <c r="M21">
-        <v>7.7350330539047718E-3</v>
-      </c>
-      <c r="N21">
-        <v>3.7093822902178892E-8</v>
-      </c>
-      <c r="O21">
-        <v>69927.278854158067</v>
-      </c>
-      <c r="P21">
-        <v>120</v>
-      </c>
-      <c r="Q21">
-        <v>20000</v>
+      <c r="C21" s="12">
+        <v>1495</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.66226661205291748</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1.242995892880572E-7</v>
+      </c>
+      <c r="F21" s="5">
+        <v>4.6213998575694859E-4</v>
+      </c>
+      <c r="G21" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I21" s="5">
+        <v>1750</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0.54668885469436646</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0.29886868596076971</v>
+      </c>
+      <c r="L21" s="5">
+        <v>3.9871382570993741E-4</v>
+      </c>
+      <c r="M21" s="5">
+        <v>7.9742766683921218E-4</v>
+      </c>
+      <c r="N21" s="5">
+        <v>2.588854830813947E-4</v>
+      </c>
+      <c r="O21" s="5">
+        <v>877918.45551437186</v>
+      </c>
+      <c r="P21" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>1880000</v>
       </c>
       <c r="R21" t="b">
         <v>1</v>
       </c>
       <c r="S21">
         <f t="shared" si="0"/>
-        <v>5.5988521257120927E-6</v>
+        <v>3.9075550155309752E-2</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -1837,7 +1843,7 @@
       <c r="B22" s="3">
         <v>0.73949311311490629</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="11">
         <v>1333.859985351562</v>
       </c>
       <c r="D22" s="3">
@@ -1891,247 +1897,244 @@
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="8">
         <v>0.82389884146739789</v>
       </c>
-      <c r="C23">
-        <v>1194.685791015625</v>
-      </c>
-      <c r="D23">
-        <v>0.8248019814491272</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="1"/>
-        <v>8.156618265980115E-7</v>
-      </c>
-      <c r="F23">
-        <v>6.5232557244598866E-4</v>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>1175</v>
-      </c>
-      <c r="I23">
-        <v>1325</v>
-      </c>
-      <c r="J23">
-        <v>0.55029153823852539</v>
-      </c>
-      <c r="K23">
-        <v>0.30282080173492432</v>
-      </c>
-      <c r="L23">
-        <v>3.8911487831803761E-3</v>
-      </c>
-      <c r="M23">
-        <v>7.7822976745665073E-3</v>
-      </c>
-      <c r="N23">
-        <v>9.0313998172930621E-4</v>
-      </c>
-      <c r="O23">
-        <v>29186.4917767765</v>
-      </c>
-      <c r="P23">
-        <v>120</v>
-      </c>
-      <c r="Q23">
-        <v>20000</v>
+      <c r="C23" s="13">
+        <v>1192.400024414062</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0.82346981763839722</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.049324509949656E-6</v>
+      </c>
+      <c r="F23" s="8">
+        <v>6.9150049239397049E-4</v>
+      </c>
+      <c r="G23" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="8">
+        <v>1050</v>
+      </c>
+      <c r="I23" s="8">
+        <v>1250</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0.54686480760574341</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0.299061119556427</v>
+      </c>
+      <c r="L23" s="8">
+        <v>1.729338364223921E-3</v>
+      </c>
+      <c r="M23" s="8">
+        <v>3.458676859736443E-3</v>
+      </c>
+      <c r="N23" s="8">
+        <v>4.2902382900067432E-4</v>
+      </c>
+      <c r="O23" s="8">
+        <v>392117.55382156838</v>
+      </c>
+      <c r="P23" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>100000</v>
       </c>
       <c r="R23" t="b">
         <v>1</v>
       </c>
       <c r="S23">
         <f t="shared" si="0"/>
-        <v>0.10961782396984278</v>
+        <v>5.2072391343161155E-2</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="5">
         <v>0.91610319604160129</v>
       </c>
-      <c r="C24">
-        <v>1072.037353515625</v>
-      </c>
-      <c r="D24">
-        <v>0.92241066694259644</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="1"/>
-        <v>3.9784189166900559E-5</v>
-      </c>
-      <c r="F24">
-        <v>8.9104153448715806E-4</v>
-      </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>1000</v>
-      </c>
-      <c r="I24">
-        <v>1125</v>
-      </c>
-      <c r="J24">
-        <v>0.54445266723632813</v>
-      </c>
-      <c r="K24">
-        <v>0.29642868041992188</v>
-      </c>
-      <c r="L24">
-        <v>3.849861730379104E-3</v>
-      </c>
-      <c r="M24">
-        <v>7.6997233554720879E-3</v>
-      </c>
-      <c r="N24">
-        <v>6.3074709009951491E-3</v>
-      </c>
-      <c r="O24">
-        <v>17282.53078682096</v>
-      </c>
-      <c r="P24">
-        <v>120</v>
-      </c>
-      <c r="Q24">
-        <v>20000</v>
+      <c r="C24" s="12">
+        <v>1072.599975585938</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0.91606009006500244</v>
+      </c>
+      <c r="E24" s="5">
+        <v>7.0510793648281833E-8</v>
+      </c>
+      <c r="F24" s="5">
+        <v>8.8741042418405414E-4</v>
+      </c>
+      <c r="G24" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5">
+        <v>950</v>
+      </c>
+      <c r="I24" s="5">
+        <v>1150</v>
+      </c>
+      <c r="J24" s="5">
+        <v>0.54583948850631714</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0.29794076085090643</v>
+      </c>
+      <c r="L24" s="5">
+        <v>1.2205342011038401E-3</v>
+      </c>
+      <c r="M24" s="5">
+        <v>2.4410684127360578E-3</v>
+      </c>
+      <c r="N24" s="5">
+        <v>4.3105976598845068E-5</v>
+      </c>
+      <c r="O24" s="5">
+        <v>158730.7108206609</v>
+      </c>
+      <c r="P24" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>200000</v>
       </c>
       <c r="R24" t="b">
         <v>1</v>
       </c>
       <c r="S24">
         <f t="shared" si="0"/>
-        <v>0.68851095905452109</v>
+        <v>4.7053625383146874E-3</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="5">
         <v>1.0163985453103981</v>
       </c>
-      <c r="C25">
-        <v>963.1207275390625</v>
-      </c>
-      <c r="D25">
-        <v>1.0130019187927251</v>
-      </c>
-      <c r="E25">
-        <f t="shared" si="1"/>
-        <v>1.153707170055961E-5</v>
-      </c>
-      <c r="F25">
-        <v>1.132820965722203E-3</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>875</v>
-      </c>
-      <c r="I25">
-        <v>1000</v>
-      </c>
-      <c r="J25">
-        <v>0.54170781373977661</v>
-      </c>
-      <c r="K25">
-        <v>0.29344737529754639</v>
-      </c>
-      <c r="L25">
-        <v>3.8304526851713531E-3</v>
-      </c>
-      <c r="M25">
-        <v>7.6609053649008274E-3</v>
-      </c>
-      <c r="N25">
-        <v>3.3966265176734729E-3</v>
-      </c>
-      <c r="O25">
-        <v>11043.449167192961</v>
-      </c>
-      <c r="P25">
-        <v>120</v>
-      </c>
-      <c r="Q25">
-        <v>20000</v>
+      <c r="C25" s="12">
+        <v>963</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1.017299890518188</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1.415448878105963E-5</v>
+      </c>
+      <c r="F25" s="5">
+        <v>1.102049835026264E-3</v>
+      </c>
+      <c r="G25" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5">
+        <v>850</v>
+      </c>
+      <c r="I25" s="5">
+        <v>1050</v>
+      </c>
+      <c r="J25" s="5">
+        <v>0.54618608951568604</v>
+      </c>
+      <c r="K25" s="5">
+        <v>0.2983192503452301</v>
+      </c>
+      <c r="L25" s="5">
+        <v>1.5767034290475521E-3</v>
+      </c>
+      <c r="M25" s="5">
+        <v>3.153407014906406E-3</v>
+      </c>
+      <c r="N25" s="5">
+        <f>D25-B25</f>
+        <v>9.0134520778994975E-4</v>
+      </c>
+      <c r="O25" s="5">
+        <v>205843.68164158051</v>
+      </c>
+      <c r="P25" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>120000</v>
       </c>
       <c r="R25" t="b">
         <v>1</v>
       </c>
       <c r="S25">
         <f t="shared" si="0"/>
-        <v>0.33418254417475352</v>
+        <v>8.8680292976480779E-2</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="5">
         <v>1.1249872354644439</v>
       </c>
-      <c r="C26">
-        <v>869.05377197265625</v>
-      </c>
-      <c r="D26">
-        <v>1.123741030693054</v>
-      </c>
-      <c r="E26">
-        <f t="shared" si="1"/>
-        <v>1.553026332235015E-6</v>
-      </c>
-      <c r="F26">
-        <v>1.241189893335104E-3</v>
-      </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>775</v>
-      </c>
-      <c r="I26">
-        <v>925</v>
-      </c>
-      <c r="J26">
-        <v>0.53987449407577515</v>
-      </c>
-      <c r="K26">
-        <v>0.29146444797515869</v>
-      </c>
-      <c r="L26">
-        <v>3.817489157506372E-3</v>
-      </c>
-      <c r="M26">
-        <v>7.6349782757461071E-3</v>
-      </c>
-      <c r="N26">
-        <v>1.2462047713899249E-3</v>
-      </c>
-      <c r="O26">
-        <v>6581.8904722017478</v>
-      </c>
-      <c r="P26">
-        <v>130</v>
-      </c>
-      <c r="Q26">
-        <v>20000</v>
+      <c r="C26" s="5">
+        <v>869.20001220703125</v>
+      </c>
+      <c r="D26" s="5">
+        <v>1.125318646430969</v>
+      </c>
+      <c r="E26" s="5">
+        <v>2.5101382561842911E-5</v>
+      </c>
+      <c r="F26" s="5">
+        <v>1.315595000050962E-3</v>
+      </c>
+      <c r="G26" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="5">
+        <v>750</v>
+      </c>
+      <c r="I26" s="5">
+        <v>950</v>
+      </c>
+      <c r="J26" s="5">
+        <v>0.54351019859313965</v>
+      </c>
+      <c r="K26" s="5">
+        <v>0.29540336132049561</v>
+      </c>
+      <c r="L26" s="5">
+        <v>1.0271377289319821E-3</v>
+      </c>
+      <c r="M26" s="5">
+        <v>2.0542754791676998E-3</v>
+      </c>
+      <c r="N26" s="5">
+        <v>3.314109665248921E-4</v>
+      </c>
+      <c r="O26" s="5">
+        <v>72221.347046929703</v>
+      </c>
+      <c r="P26" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>280000</v>
       </c>
       <c r="R26" t="b">
         <v>1</v>
       </c>
       <c r="S26">
         <f t="shared" si="0"/>
-        <v>0.11077501433831266</v>
+        <v>2.9459086830267114E-2</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -2141,14 +2144,14 @@
       <c r="B27">
         <v>1.2419583172375741</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="14">
         <v>786.5404052734375</v>
       </c>
       <c r="D27">
         <v>1.242001533508301</v>
       </c>
       <c r="E27">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E27:E48" si="1">(B27-D27)^2</f>
         <v>1.867646055540535E-9</v>
       </c>
       <c r="F27">
@@ -2196,64 +2199,63 @@
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="A28" s="4">
         <v>27</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="5">
         <v>1.3672638517295399</v>
       </c>
-      <c r="C28">
-        <v>714.41259765625</v>
-      </c>
-      <c r="D28">
-        <v>1.368261575698853</v>
-      </c>
-      <c r="E28">
-        <f t="shared" si="1"/>
-        <v>9.9545311894184814E-7</v>
-      </c>
-      <c r="F28">
-        <v>1.888558035716414E-3</v>
-      </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28">
-        <v>675</v>
-      </c>
-      <c r="I28">
-        <v>825</v>
-      </c>
-      <c r="J28">
-        <v>0.53980171680450439</v>
-      </c>
-      <c r="K28">
-        <v>0.29138591885566711</v>
-      </c>
-      <c r="L28">
-        <v>3.8169745444860538E-3</v>
-      </c>
-      <c r="M28">
-        <v>7.633949164301157E-3</v>
-      </c>
-      <c r="N28">
-        <v>9.9772396931308016E-4</v>
-      </c>
-      <c r="O28">
-        <v>2928.525918896622</v>
-      </c>
-      <c r="P28">
-        <v>130</v>
-      </c>
-      <c r="Q28">
-        <v>20000</v>
+      <c r="C28" s="5">
+        <v>714.0999755859375</v>
+      </c>
+      <c r="D28" s="5">
+        <v>1.36687183380127</v>
+      </c>
+      <c r="E28" s="5">
+        <v>8.8824714339352795E-7</v>
+      </c>
+      <c r="F28" s="5">
+        <v>1.9155516056343911E-3</v>
+      </c>
+      <c r="G28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="5">
+        <v>650</v>
+      </c>
+      <c r="I28" s="5">
+        <v>850</v>
+      </c>
+      <c r="J28" s="5">
+        <v>0.54211878776550293</v>
+      </c>
+      <c r="K28" s="5">
+        <v>0.29389277100563049</v>
+      </c>
+      <c r="L28" s="5">
+        <v>1.1558011390144041E-3</v>
+      </c>
+      <c r="M28" s="5">
+        <v>2.3116022348403931E-3</v>
+      </c>
+      <c r="N28" s="5">
+        <v>3.9201792827081578E-4</v>
+      </c>
+      <c r="O28" s="5">
+        <v>17033.04541203364</v>
+      </c>
+      <c r="P28" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>220000</v>
       </c>
       <c r="R28" t="b">
         <v>1</v>
       </c>
       <c r="S28">
         <f t="shared" si="0"/>
-        <v>7.2972306555972713E-2</v>
+        <v>2.8671710129316085E-2</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -2263,7 +2265,7 @@
       <c r="B29">
         <v>1.500696076675252</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="14">
         <v>651.10205078125</v>
       </c>
       <c r="D29">
@@ -2318,125 +2320,123 @@
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="A30" s="4">
         <v>29</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="5">
         <v>1.641866982058007</v>
       </c>
-      <c r="C30">
-        <v>595.3984375</v>
-      </c>
-      <c r="D30">
-        <v>1.6453398466110229</v>
-      </c>
-      <c r="E30">
-        <f t="shared" si="1"/>
-        <v>1.2060788203594927E-5</v>
-      </c>
-      <c r="F30">
-        <v>2.7098171412944789E-3</v>
-      </c>
-      <c r="G30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30">
-        <v>475</v>
-      </c>
-      <c r="I30">
-        <v>625</v>
-      </c>
-      <c r="J30">
-        <v>0.53746223449707031</v>
-      </c>
-      <c r="K30">
-        <v>0.28886568546295172</v>
-      </c>
-      <c r="L30">
-        <v>3.800431906445528E-3</v>
-      </c>
-      <c r="M30">
-        <v>7.6008639298379421E-3</v>
-      </c>
-      <c r="N30">
-        <v>3.4728645530159863E-3</v>
-      </c>
-      <c r="O30">
-        <v>1415.364006326673</v>
-      </c>
-      <c r="P30">
-        <v>130</v>
-      </c>
-      <c r="Q30">
-        <v>20000</v>
+      <c r="C30" s="5">
+        <v>595.4000244140625</v>
+      </c>
+      <c r="D30" s="5">
+        <v>1.6419694423675539</v>
+      </c>
+      <c r="E30" s="5">
+        <v>3.7988812096045883E-8</v>
+      </c>
+      <c r="F30" s="5">
+        <v>2.767425030469894E-3</v>
+      </c>
+      <c r="G30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="5">
+        <v>450</v>
+      </c>
+      <c r="I30" s="5">
+        <v>650</v>
+      </c>
+      <c r="J30" s="5">
+        <v>0.54004651308059692</v>
+      </c>
+      <c r="K30" s="5">
+        <v>0.29165023565292358</v>
+      </c>
+      <c r="L30" s="5">
+        <v>6.4547904280521024E-4</v>
+      </c>
+      <c r="M30" s="5">
+        <v>1.290958025492728E-3</v>
+      </c>
+      <c r="N30" s="5">
+        <v>1.0246030954674799E-4</v>
+      </c>
+      <c r="O30" s="5">
+        <v>16321.432890700011</v>
+      </c>
+      <c r="P30" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>700000</v>
       </c>
       <c r="R30" t="b">
         <v>1</v>
       </c>
       <c r="S30">
         <f t="shared" si="0"/>
-        <v>0.21151923943697956</v>
+        <v>6.2404756698571633E-3</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="5">
         <v>1.7901920231041131</v>
       </c>
-      <c r="C31">
-        <v>546.5574951171875</v>
-      </c>
-      <c r="D31">
-        <v>1.7935007810592649</v>
-      </c>
-      <c r="E31">
-        <f t="shared" si="1"/>
-        <v>1.0947879205780598E-5</v>
-      </c>
-      <c r="F31">
-        <v>3.2354868017137051E-3</v>
-      </c>
-      <c r="G31" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31">
-        <v>475</v>
-      </c>
-      <c r="I31">
-        <v>625</v>
-      </c>
-      <c r="J31">
-        <v>0.53987753391265869</v>
-      </c>
-      <c r="K31">
-        <v>0.29146775603294373</v>
-      </c>
-      <c r="L31">
-        <v>3.8175106523991118E-3</v>
-      </c>
-      <c r="M31">
-        <v>7.6350211165845394E-3</v>
-      </c>
-      <c r="N31">
-        <v>3.308757955151842E-3</v>
-      </c>
-      <c r="O31">
-        <v>1246.3936174374251</v>
-      </c>
-      <c r="P31">
-        <v>120</v>
-      </c>
-      <c r="Q31">
-        <v>20000</v>
+      <c r="C31" s="5">
+        <v>547.0999755859375</v>
+      </c>
+      <c r="D31" s="5">
+        <v>1.7905030250549321</v>
+      </c>
+      <c r="E31" s="5">
+        <v>8.0293162341149582E-8</v>
+      </c>
+      <c r="F31" s="5">
+        <v>3.2203758601099248E-3</v>
+      </c>
+      <c r="G31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="5">
+        <v>450</v>
+      </c>
+      <c r="I31" s="5">
+        <v>650</v>
+      </c>
+      <c r="J31" s="5">
+        <v>0.53896313905715942</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0.29048123955726618</v>
+      </c>
+      <c r="L31" s="5">
+        <v>7.9465779517971433E-4</v>
+      </c>
+      <c r="M31" s="5">
+        <v>1.5893157105892901E-3</v>
+      </c>
+      <c r="N31" s="5">
+        <v>3.1100195081879001E-4</v>
+      </c>
+      <c r="O31" s="5">
+        <v>12053.0480520694</v>
+      </c>
+      <c r="P31" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>460000</v>
       </c>
       <c r="R31" t="b">
         <v>1</v>
       </c>
       <c r="S31">
         <f t="shared" si="0"/>
-        <v>0.18482698573388812</v>
+        <v>1.7372547011997433E-2</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
@@ -2446,7 +2446,7 @@
       <c r="B32" s="3">
         <v>1.9448797373273861</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="11">
         <v>503.97000122070313</v>
       </c>
       <c r="D32" s="3">
@@ -2500,491 +2500,483 @@
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="5">
         <v>2.104928884729083</v>
       </c>
-      <c r="C33">
-        <v>466.61209106445313</v>
-      </c>
-      <c r="D33">
-        <v>2.103854656219482</v>
-      </c>
-      <c r="E33">
-        <f t="shared" si="1"/>
-        <v>1.1539668908396683E-6</v>
-      </c>
-      <c r="F33">
-        <v>4.4323964975774288E-3</v>
-      </c>
-      <c r="G33" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33">
-        <v>375</v>
-      </c>
-      <c r="I33">
-        <v>525</v>
-      </c>
-      <c r="J33">
-        <v>0.53829467296600342</v>
-      </c>
-      <c r="K33">
-        <v>0.28976118564605707</v>
-      </c>
-      <c r="L33">
-        <v>3.806318135308559E-3</v>
-      </c>
-      <c r="M33">
-        <v>7.6126363128423691E-3</v>
-      </c>
-      <c r="N33">
-        <v>1.074228509601038E-3</v>
-      </c>
-      <c r="O33">
-        <v>658.08292991339147</v>
-      </c>
-      <c r="P33">
-        <v>120</v>
-      </c>
-      <c r="Q33">
-        <v>20000</v>
+      <c r="C33" s="5">
+        <v>466.6300048828125</v>
+      </c>
+      <c r="D33" s="5">
+        <v>2.1047952175140381</v>
+      </c>
+      <c r="E33" s="5">
+        <v>2.668564775376581E-5</v>
+      </c>
+      <c r="F33" s="5">
+        <v>4.4279671274125576E-3</v>
+      </c>
+      <c r="G33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="5">
+        <v>400</v>
+      </c>
+      <c r="I33" s="5">
+        <v>550</v>
+      </c>
+      <c r="J33" s="5">
+        <v>0.54028064012527466</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0.29190313816070562</v>
+      </c>
+      <c r="L33" s="5">
+        <v>1.3507016003131869E-3</v>
+      </c>
+      <c r="M33" s="5">
+        <v>2.7014031074941158E-3</v>
+      </c>
+      <c r="N33" s="5">
+        <v>1.336672150453744E-4</v>
+      </c>
+      <c r="O33" s="5">
+        <v>10200.49434702924</v>
+      </c>
+      <c r="P33" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>160000</v>
       </c>
       <c r="R33" t="b">
         <v>1</v>
       </c>
       <c r="S33">
         <f t="shared" si="0"/>
-        <v>5.1033957365229358E-2</v>
+        <v>6.3502009980056012E-3</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="A34" s="4">
         <v>33</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="5">
         <v>2.2691343691356791</v>
       </c>
-      <c r="C34">
-        <v>433.90231323242188</v>
-      </c>
-      <c r="D34">
-        <v>2.268501996994019</v>
-      </c>
-      <c r="E34">
-        <f t="shared" si="1"/>
-        <v>3.998945255478072E-7</v>
-      </c>
-      <c r="F34">
-        <v>5.0777299329638481E-3</v>
-      </c>
-      <c r="G34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34">
-        <v>375</v>
-      </c>
-      <c r="I34">
-        <v>525</v>
-      </c>
-      <c r="J34">
-        <v>0.53862494230270386</v>
-      </c>
-      <c r="K34">
-        <v>0.2901168167591095</v>
-      </c>
-      <c r="L34">
-        <v>3.8086534921845478E-3</v>
-      </c>
-      <c r="M34">
-        <v>7.6173068955540657E-3</v>
-      </c>
-      <c r="N34">
-        <v>6.3237214166012023E-4</v>
-      </c>
-      <c r="O34">
-        <v>1885.6632454459341</v>
-      </c>
-      <c r="P34">
-        <v>60</v>
-      </c>
-      <c r="Q34">
-        <v>20000</v>
+      <c r="C34" s="5">
+        <v>433.69000244140619</v>
+      </c>
+      <c r="D34" s="5">
+        <v>2.268783330917358</v>
+      </c>
+      <c r="E34" s="5">
+        <v>5.2947962103644386E-7</v>
+      </c>
+      <c r="F34" s="5">
+        <v>5.1063201390206814E-3</v>
+      </c>
+      <c r="G34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5">
+        <v>400</v>
+      </c>
+      <c r="I34" s="5">
+        <v>550</v>
+      </c>
+      <c r="J34" s="5">
+        <v>0.53960871696472168</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0.29117757081985468</v>
+      </c>
+      <c r="L34" s="5">
+        <v>1.7063925908896609E-3</v>
+      </c>
+      <c r="M34" s="5">
+        <v>3.4127852413803339E-3</v>
+      </c>
+      <c r="N34" s="5">
+        <v>3.5103821832027648E-4</v>
+      </c>
+      <c r="O34" s="5">
+        <v>599.24434933559655</v>
+      </c>
+      <c r="P34" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>100000</v>
       </c>
       <c r="R34" t="b">
         <v>1</v>
       </c>
       <c r="S34">
         <f t="shared" si="0"/>
-        <v>2.7868430810511803E-2</v>
+        <v>1.5470138000421197E-2</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="5">
         <v>2.436102626529673</v>
       </c>
-      <c r="C35">
-        <v>404.86004638671881</v>
-      </c>
-      <c r="D35">
-        <v>2.4397609233856201</v>
-      </c>
-      <c r="E35">
-        <f t="shared" si="1"/>
-        <v>1.338313588623241E-5</v>
-      </c>
-      <c r="F35">
-        <v>5.7611754164099693E-3</v>
-      </c>
-      <c r="G35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35">
-        <v>375</v>
-      </c>
-      <c r="I35">
-        <v>525</v>
-      </c>
-      <c r="J35">
-        <v>0.54821658134460449</v>
-      </c>
-      <c r="K35">
-        <v>0.30054143071174622</v>
-      </c>
-      <c r="L35">
-        <v>3.8764766222767642E-3</v>
-      </c>
-      <c r="M35">
-        <v>7.7529530972242364E-3</v>
-      </c>
-      <c r="N35">
-        <v>3.6582968559466522E-3</v>
-      </c>
-      <c r="O35">
-        <v>1441.955651108341</v>
-      </c>
-      <c r="P35">
-        <v>60</v>
-      </c>
-      <c r="Q35">
-        <v>20000</v>
+      <c r="C35" s="5">
+        <v>404.75</v>
+      </c>
+      <c r="D35" s="5">
+        <v>2.4367704391479492</v>
+      </c>
+      <c r="E35" s="5">
+        <v>5.8791192714124918E-7</v>
+      </c>
+      <c r="F35" s="5">
+        <v>5.738699808716774E-3</v>
+      </c>
+      <c r="G35" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="5">
+        <v>400</v>
+      </c>
+      <c r="I35" s="5">
+        <v>550</v>
+      </c>
+      <c r="J35" s="5">
+        <v>0.54559206962585449</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0.29767072200775152</v>
+      </c>
+      <c r="L35" s="5">
+        <v>1.4581561410577581E-3</v>
+      </c>
+      <c r="M35" s="5">
+        <v>2.9163123108446598E-3</v>
+      </c>
+      <c r="N35" s="5">
+        <v>6.6781261827575378E-4</v>
+      </c>
+      <c r="O35" s="5">
+        <v>474.4527969668971</v>
+      </c>
+      <c r="P35" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>140000</v>
       </c>
       <c r="R35" t="b">
         <v>1</v>
       </c>
       <c r="S35">
         <f t="shared" si="0"/>
-        <v>0.15017006328497925</v>
+        <v>2.7413156202991333E-2</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="A36" s="4">
         <v>35</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="5">
         <v>2.6042764235395381</v>
       </c>
-      <c r="C36">
-        <v>379.60751342773438</v>
-      </c>
-      <c r="D36">
-        <v>2.6028010845184331</v>
-      </c>
-      <c r="E36">
-        <f t="shared" si="1"/>
-        <v>2.1766252271953018E-6</v>
-      </c>
-      <c r="F36">
-        <v>6.6780243068933487E-3</v>
-      </c>
-      <c r="G36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36">
-        <v>275</v>
-      </c>
-      <c r="I36">
-        <v>425</v>
-      </c>
-      <c r="J36">
-        <v>0.54927808046340942</v>
-      </c>
-      <c r="K36">
-        <v>0.30170640349388123</v>
-      </c>
-      <c r="L36">
-        <v>3.8839825545280691E-3</v>
-      </c>
-      <c r="M36">
-        <v>7.7679650858044624E-3</v>
-      </c>
-      <c r="N36">
-        <v>1.4753390211050821E-3</v>
-      </c>
-      <c r="O36">
-        <v>1088.508959820696</v>
-      </c>
-      <c r="P36">
-        <v>60</v>
-      </c>
-      <c r="Q36">
-        <v>20000</v>
+      <c r="C36" s="5">
+        <v>379.52999877929688</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2.604678869247437</v>
+      </c>
+      <c r="E36" s="5">
+        <v>3.8091113765403861E-6</v>
+      </c>
+      <c r="F36" s="5">
+        <v>6.7103966139256954E-3</v>
+      </c>
+      <c r="G36" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="5">
+        <v>250</v>
+      </c>
+      <c r="I36" s="5">
+        <v>450</v>
+      </c>
+      <c r="J36" s="5">
+        <v>0.54911023378372192</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0.30152204632759089</v>
+      </c>
+      <c r="L36" s="5">
+        <v>1.227847809881204E-3</v>
+      </c>
+      <c r="M36" s="5">
+        <v>2.4556955322623249E-3</v>
+      </c>
+      <c r="N36" s="5">
+        <v>4.0244570789882422E-4</v>
+      </c>
+      <c r="O36" s="5">
+        <v>1110.385098986133</v>
+      </c>
+      <c r="P36" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>200000</v>
       </c>
       <c r="R36" t="b">
         <v>1</v>
       </c>
       <c r="S36">
         <f t="shared" si="0"/>
-        <v>5.6650630776740339E-2</v>
+        <v>1.5453263880177898E-2</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="5">
         <v>2.771968175131601</v>
       </c>
-      <c r="C37">
-        <v>357.34356689453119</v>
-      </c>
-      <c r="D37">
-        <v>2.774096012115479</v>
-      </c>
-      <c r="E37">
-        <f t="shared" si="1"/>
-        <v>4.5276902299589098E-6</v>
-      </c>
-      <c r="F37">
-        <v>7.5398175977170467E-3</v>
-      </c>
-      <c r="G37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37">
-        <v>275</v>
-      </c>
-      <c r="I37">
-        <v>425</v>
-      </c>
-      <c r="J37">
-        <v>0.55053693056106567</v>
-      </c>
-      <c r="K37">
-        <v>0.30309092998504639</v>
-      </c>
-      <c r="L37">
-        <v>3.892883968933569E-3</v>
-      </c>
-      <c r="M37">
-        <v>7.7857677824795246E-3</v>
-      </c>
-      <c r="N37">
-        <v>2.1278369838779732E-3</v>
-      </c>
-      <c r="O37">
-        <v>850.97508118272538</v>
-      </c>
-      <c r="P37">
-        <v>60</v>
-      </c>
-      <c r="Q37">
-        <v>20000</v>
+      <c r="C37" s="5">
+        <v>357.6099853515625</v>
+      </c>
+      <c r="D37" s="5">
+        <v>2.7717258930206299</v>
+      </c>
+      <c r="E37" s="5">
+        <v>3.8734175177523873E-5</v>
+      </c>
+      <c r="F37" s="5">
+        <v>7.5418823398649693E-3</v>
+      </c>
+      <c r="G37" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="5">
+        <v>250</v>
+      </c>
+      <c r="I37" s="5">
+        <v>450</v>
+      </c>
+      <c r="J37" s="5">
+        <v>0.55216401815414429</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0.30488511919975281</v>
+      </c>
+      <c r="L37" s="5">
+        <v>1.3804100453853609E-3</v>
+      </c>
+      <c r="M37" s="5">
+        <v>2.760820090770721E-3</v>
+      </c>
+      <c r="N37" s="5">
+        <v>2.4228211097110369E-4</v>
+      </c>
+      <c r="O37" s="5">
+        <v>4395.2188351561836</v>
+      </c>
+      <c r="P37" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>160000</v>
       </c>
       <c r="R37" t="b">
         <v>1</v>
       </c>
       <c r="S37">
         <f t="shared" si="0"/>
-        <v>7.6762677254653286E-2</v>
+        <v>8.7404362411051557E-3</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="A38" s="4">
         <v>37</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="5">
         <v>2.937400074153079</v>
       </c>
-      <c r="C38">
-        <v>338.44384765625</v>
-      </c>
-      <c r="D38">
-        <v>2.9404647350311279</v>
-      </c>
-      <c r="E38">
-        <f t="shared" si="1"/>
-        <v>9.3921462974435056E-6</v>
-      </c>
-      <c r="F38">
-        <v>8.2908682525157928E-3</v>
-      </c>
-      <c r="G38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <v>275</v>
-      </c>
-      <c r="I38">
-        <v>425</v>
-      </c>
-      <c r="J38">
-        <v>0.56024092435836792</v>
-      </c>
-      <c r="K38">
-        <v>0.31386986374855042</v>
-      </c>
-      <c r="L38">
-        <v>3.9615015671202146E-3</v>
-      </c>
-      <c r="M38">
-        <v>7.9230032861232758E-3</v>
-      </c>
-      <c r="N38">
-        <v>3.0646608780484641E-3</v>
-      </c>
-      <c r="O38">
-        <v>36.134739581451782</v>
-      </c>
-      <c r="P38">
-        <v>60</v>
-      </c>
-      <c r="Q38">
-        <v>20000</v>
+      <c r="C38" s="5">
+        <v>338.16000366210938</v>
+      </c>
+      <c r="D38" s="5">
+        <v>2.9371383190155029</v>
+      </c>
+      <c r="E38" s="5">
+        <v>2.1526125237869559E-7</v>
+      </c>
+      <c r="F38" s="5">
+        <v>8.3334473893046379E-3</v>
+      </c>
+      <c r="G38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="5">
+        <v>250</v>
+      </c>
+      <c r="I38" s="5">
+        <v>450</v>
+      </c>
+      <c r="J38" s="5">
+        <v>0.55657583475112915</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0.30977663397789001</v>
+      </c>
+      <c r="L38" s="5">
+        <v>1.7600473284230631E-3</v>
+      </c>
+      <c r="M38" s="5">
+        <v>3.52009478956461E-3</v>
+      </c>
+      <c r="N38" s="5">
+        <v>2.617551375765359E-4</v>
+      </c>
+      <c r="O38" s="5">
+        <v>1799.9507288319389</v>
+      </c>
+      <c r="P38" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>100000</v>
       </c>
       <c r="R38" t="b">
         <v>1</v>
       </c>
       <c r="S38">
         <f t="shared" si="0"/>
-        <v>0.10433243006341508</v>
+        <v>8.9111163262977043E-3</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="5">
         <v>3.0987486480304991</v>
       </c>
-      <c r="C39">
-        <v>321.81817626953119</v>
-      </c>
-      <c r="D39">
-        <v>3.09555983543396</v>
-      </c>
-      <c r="E39">
-        <f t="shared" si="1"/>
-        <v>1.0168525775846671E-5</v>
-      </c>
-      <c r="F39">
-        <v>8.7563665583729744E-3</v>
-      </c>
-      <c r="G39" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39">
-        <v>275</v>
-      </c>
-      <c r="I39">
-        <v>425</v>
-      </c>
-      <c r="J39">
-        <v>0.55584269762039185</v>
-      </c>
-      <c r="K39">
-        <v>0.30896109342575068</v>
-      </c>
-      <c r="L39">
-        <v>3.930401407604027E-3</v>
-      </c>
-      <c r="M39">
-        <v>7.8608030453324318E-3</v>
-      </c>
-      <c r="N39">
-        <v>3.1888125965391367E-3</v>
-      </c>
-      <c r="O39">
-        <v>586.35080806401174</v>
-      </c>
-      <c r="P39">
-        <v>60</v>
-      </c>
-      <c r="Q39">
-        <v>20000</v>
+      <c r="C39" s="5">
+        <v>321.6300048828125</v>
+      </c>
+      <c r="D39" s="5">
+        <v>3.0990738868713379</v>
+      </c>
+      <c r="E39" s="5">
+        <v>1.447017621103441E-5</v>
+      </c>
+      <c r="F39" s="5">
+        <v>9.0668704360723495E-3</v>
+      </c>
+      <c r="G39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" s="5">
+        <v>250</v>
+      </c>
+      <c r="I39" s="5">
+        <v>450</v>
+      </c>
+      <c r="J39" s="5">
+        <v>0.55993026494979858</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0.31352192163467407</v>
+      </c>
+      <c r="L39" s="5">
+        <v>1.399825662374497E-3</v>
+      </c>
+      <c r="M39" s="5">
+        <v>2.7996513526886702E-3</v>
+      </c>
+      <c r="N39" s="5">
+        <v>3.2523884083879301E-4</v>
+      </c>
+      <c r="O39" s="5">
+        <v>608.21228045489568</v>
+      </c>
+      <c r="P39" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>160000</v>
       </c>
       <c r="R39" t="b">
         <v>1</v>
       </c>
       <c r="S39">
         <f t="shared" si="0"/>
-        <v>0.10290646188957213</v>
+        <v>1.049581227072122E-2</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40">
+      <c r="A40" s="4">
         <v>39</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="5">
         <v>3.2541909293254512</v>
       </c>
-      <c r="C40">
-        <v>307.497802734375</v>
-      </c>
-      <c r="D40">
-        <v>3.2546195983886719</v>
-      </c>
-      <c r="E40">
-        <f t="shared" si="1"/>
-        <v>1.8375716576251172E-7</v>
-      </c>
-      <c r="F40">
-        <v>9.5292897894978523E-3</v>
-      </c>
-      <c r="G40" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40">
-        <v>287.5</v>
-      </c>
-      <c r="I40">
-        <v>362.5</v>
-      </c>
-      <c r="J40">
-        <v>0.55876147747039795</v>
-      </c>
-      <c r="K40">
-        <v>0.31221437454223627</v>
-      </c>
-      <c r="L40">
-        <v>3.9510402978513263E-3</v>
-      </c>
-      <c r="M40">
-        <v>7.9020801931619644E-3</v>
-      </c>
-      <c r="N40">
-        <v>4.2866906322069909E-4</v>
-      </c>
-      <c r="O40">
-        <v>200.1094119002035</v>
-      </c>
-      <c r="P40">
+      <c r="C40" s="5">
+        <v>307.48001098632813</v>
+      </c>
+      <c r="D40" s="5">
+        <v>3.254597663879395</v>
+      </c>
+      <c r="E40" s="5">
+        <v>1.091004833142506E-6</v>
+      </c>
+      <c r="F40" s="5">
+        <v>9.5614735037088394E-3</v>
+      </c>
+      <c r="G40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="5">
+        <v>250</v>
+      </c>
+      <c r="I40" s="5">
+        <v>450</v>
+      </c>
+      <c r="J40" s="5">
+        <v>0.55850476026535034</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0.31192755699157709</v>
+      </c>
+      <c r="L40" s="5">
+        <v>1.3962619006633759E-3</v>
+      </c>
+      <c r="M40" s="5">
+        <v>2.7925237081944938E-3</v>
+      </c>
+      <c r="N40" s="5">
+        <v>4.0673455394335528E-4</v>
+      </c>
+      <c r="O40" s="5">
+        <v>683.64456515644645</v>
+      </c>
+      <c r="P40" s="5">
         <v>100</v>
       </c>
-      <c r="Q40">
-        <v>20000</v>
+      <c r="Q40" s="6">
+        <v>160000</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40">
         <f t="shared" si="0"/>
-        <v>1.3172830744431957E-2</v>
+        <v>1.249879195095863E-2</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -2994,7 +2986,7 @@
       <c r="B41">
         <v>3.4019493212427241</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="14">
         <v>295.44149780273438</v>
       </c>
       <c r="D41">
@@ -3055,7 +3047,7 @@
       <c r="B42">
         <v>3.540332478193541</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="14">
         <v>285.37942504882813</v>
       </c>
       <c r="D42">
@@ -3110,308 +3102,303 @@
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="A43" s="4">
         <v>42</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="5">
         <v>3.6677700686639909</v>
       </c>
-      <c r="C43">
-        <v>276.92678833007813</v>
-      </c>
-      <c r="D43">
-        <v>3.670695304870605</v>
-      </c>
-      <c r="E43">
-        <f t="shared" si="1"/>
-        <v>8.5570068644861231E-6</v>
-      </c>
-      <c r="F43">
-        <v>1.175930723547935E-2</v>
-      </c>
-      <c r="G43" t="b">
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <v>237.5</v>
-      </c>
-      <c r="I43">
-        <v>312.5</v>
-      </c>
-      <c r="J43">
-        <v>0.56040960550308228</v>
-      </c>
-      <c r="K43">
-        <v>0.31405889987945562</v>
-      </c>
-      <c r="L43">
-        <v>3.9626943229330736E-3</v>
-      </c>
-      <c r="M43">
-        <v>7.925388403236866E-3</v>
-      </c>
-      <c r="N43">
-        <v>6.4984965509538029E-3</v>
-      </c>
-      <c r="O43">
-        <v>238.18624850034689</v>
-      </c>
-      <c r="P43">
-        <v>70</v>
-      </c>
-      <c r="Q43">
-        <v>20000</v>
+      <c r="C43" s="5">
+        <v>277.04998779296881</v>
+      </c>
+      <c r="D43" s="5">
+        <v>3.6680006980896001</v>
+      </c>
+      <c r="E43" s="5">
+        <v>8.2948190538445488E-9</v>
+      </c>
+      <c r="F43" s="5">
+        <v>1.2039560824632639E-2</v>
+      </c>
+      <c r="G43" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" s="5">
+        <v>200</v>
+      </c>
+      <c r="I43" s="5">
+        <v>350</v>
+      </c>
+      <c r="J43" s="5">
+        <v>0.55924546718597412</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0.31275546550750732</v>
+      </c>
+      <c r="L43" s="5">
+        <v>9.8861565548760276E-4</v>
+      </c>
+      <c r="M43" s="5">
+        <v>1.977231353521347E-3</v>
+      </c>
+      <c r="N43" s="5">
+        <v>2.3062942560869709E-4</v>
+      </c>
+      <c r="O43" s="5">
+        <v>862.36023601301861</v>
+      </c>
+      <c r="P43" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>320000</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43">
         <f t="shared" si="0"/>
-        <v>0.17717840620584274</v>
+        <v>6.2880011912171303E-3</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A44">
+      <c r="A44" s="4">
         <v>43</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="5">
         <v>3.782840056259261</v>
       </c>
-      <c r="C44">
-        <v>269.969482421875</v>
-      </c>
-      <c r="D44">
-        <v>3.7893028259277339</v>
-      </c>
-      <c r="E44">
-        <f t="shared" si="1"/>
-        <v>4.1767391787733612E-5</v>
-      </c>
-      <c r="F44">
-        <v>1.2099321000278E-2</v>
-      </c>
-      <c r="G44" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <v>250</v>
-      </c>
-      <c r="I44">
-        <v>281.25</v>
-      </c>
-      <c r="J44">
-        <v>0.55725699663162231</v>
-      </c>
-      <c r="K44">
-        <v>0.31053537130355829</v>
-      </c>
-      <c r="L44">
-        <v>3.9404020118186918E-3</v>
-      </c>
-      <c r="M44">
-        <v>7.8808041289448738E-3</v>
-      </c>
-      <c r="N44">
-        <v>1.9138286896813741E-3</v>
-      </c>
-      <c r="O44">
-        <v>227.79657611348469</v>
-      </c>
-      <c r="P44">
-        <v>70</v>
-      </c>
-      <c r="Q44">
-        <v>20000</v>
+      <c r="C44" s="5">
+        <v>270.04000854492188</v>
+      </c>
+      <c r="D44" s="5">
+        <v>3.7836558818817139</v>
+      </c>
+      <c r="E44" s="5">
+        <v>1.271824658033438E-5</v>
+      </c>
+      <c r="F44" s="5">
+        <v>1.2431502342224119E-2</v>
+      </c>
+      <c r="G44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="5">
+        <v>200</v>
+      </c>
+      <c r="I44" s="5">
+        <v>350</v>
+      </c>
+      <c r="J44" s="5">
+        <v>0.55891507863998413</v>
+      </c>
+      <c r="K44" s="5">
+        <v>0.31238606572151179</v>
+      </c>
+      <c r="L44" s="5">
+        <v>1.096122650933279E-3</v>
+      </c>
+      <c r="M44" s="5">
+        <v>2.1922453306615348E-3</v>
+      </c>
+      <c r="N44" s="5">
+        <v>8.1582562245241519E-4</v>
+      </c>
+      <c r="O44" s="5">
+        <v>1213.260447624541</v>
+      </c>
+      <c r="P44" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>260000</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44">
         <f t="shared" si="0"/>
-        <v>5.0592376659295051E-2</v>
+        <v>2.1566484713053426E-2</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="A45" s="4">
         <v>44</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="5">
         <v>3.884288006826818</v>
       </c>
-      <c r="C45">
-        <v>264.39816284179688</v>
-      </c>
-      <c r="D45">
-        <v>3.8793566226959229</v>
-      </c>
-      <c r="E45">
-        <f t="shared" si="1"/>
-        <v>2.4318549446444133E-5</v>
-      </c>
-      <c r="F45">
-        <v>1.220888737589121E-2</v>
-      </c>
-      <c r="G45" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <v>250</v>
-      </c>
-      <c r="I45">
-        <v>281.25</v>
-      </c>
-      <c r="J45">
-        <v>0.55823439359664917</v>
-      </c>
-      <c r="K45">
-        <v>0.31162562966346741</v>
-      </c>
-      <c r="L45">
-        <v>3.9473132520375081E-3</v>
-      </c>
-      <c r="M45">
-        <v>7.8946268185973167E-3</v>
-      </c>
-      <c r="N45">
-        <v>6.3068290096568447E-4</v>
-      </c>
-      <c r="O45">
-        <v>214.11407350566569</v>
-      </c>
-      <c r="P45">
-        <v>70</v>
-      </c>
-      <c r="Q45">
-        <v>20000</v>
+      <c r="C45" s="5">
+        <v>264.29000854492188</v>
+      </c>
+      <c r="D45" s="5">
+        <v>3.8846390247344971</v>
+      </c>
+      <c r="E45" s="5">
+        <v>5.1706228987313807E-7</v>
+      </c>
+      <c r="F45" s="5">
+        <v>1.280318014323711E-2</v>
+      </c>
+      <c r="G45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="5">
+        <v>200</v>
+      </c>
+      <c r="I45" s="5">
+        <v>350</v>
+      </c>
+      <c r="J45" s="5">
+        <v>0.56204813718795776</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0.31589809060096741</v>
+      </c>
+      <c r="L45" s="5">
+        <v>1.256777841379401E-3</v>
+      </c>
+      <c r="M45" s="5">
+        <v>2.5135558098554611E-3</v>
+      </c>
+      <c r="N45" s="5">
+        <v>3.5101790767955171E-4</v>
+      </c>
+      <c r="O45" s="5">
+        <v>762.56049174356963</v>
+      </c>
+      <c r="P45" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>200000</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45">
         <f t="shared" si="0"/>
-        <v>1.6236769772406932E-2</v>
+        <v>9.0368661402713008E-3</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A46">
+      <c r="A46" s="4">
         <v>45</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="5">
         <v>3.9710387796361699</v>
       </c>
-      <c r="C46">
-        <v>259.77481079101563</v>
-      </c>
-      <c r="D46">
-        <v>3.9724795818328862</v>
-      </c>
-      <c r="E46">
-        <f t="shared" si="1"/>
-        <v>2.0759109700624383E-6</v>
-      </c>
-      <c r="F46">
-        <v>1.242890488356352E-2</v>
-      </c>
-      <c r="G46" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46">
-        <v>250</v>
-      </c>
-      <c r="I46">
-        <v>281.25</v>
-      </c>
-      <c r="J46">
-        <v>0.56026208400726318</v>
-      </c>
-      <c r="K46">
-        <v>0.31389358639717102</v>
-      </c>
-      <c r="L46">
-        <v>3.9616511884324286E-3</v>
-      </c>
-      <c r="M46">
-        <v>7.9233022406697273E-3</v>
-      </c>
-      <c r="N46">
-        <v>5.2387327153935459E-3</v>
-      </c>
-      <c r="O46">
-        <v>1.7214841243503229</v>
-      </c>
-      <c r="P46">
-        <v>70</v>
-      </c>
-      <c r="Q46">
-        <v>20000</v>
+      <c r="C46" s="5">
+        <v>259.79998779296881</v>
+      </c>
+      <c r="D46" s="5">
+        <v>3.9706728458404541</v>
+      </c>
+      <c r="E46" s="5">
+        <v>2.7646749458654089E-6</v>
+      </c>
+      <c r="F46" s="5">
+        <v>1.386785786598921E-2</v>
+      </c>
+      <c r="G46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" s="5">
+        <v>150</v>
+      </c>
+      <c r="I46" s="5">
+        <v>350</v>
+      </c>
+      <c r="J46" s="5">
+        <v>0.56199496984481812</v>
+      </c>
+      <c r="K46" s="5">
+        <v>0.31583836674690252</v>
+      </c>
+      <c r="L46" s="5">
+        <v>1.147167428442186E-3</v>
+      </c>
+      <c r="M46" s="5">
+        <v>2.2943348158150911E-3</v>
+      </c>
+      <c r="N46" s="5">
+        <v>3.6593379571581147E-4</v>
+      </c>
+      <c r="O46" s="5">
+        <v>1299.933826459541</v>
+      </c>
+      <c r="P46" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>240000</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46">
         <f t="shared" si="0"/>
-        <v>0.13192348415881053</v>
+        <v>9.2150647732868185E-3</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A47">
+      <c r="A47" s="4">
         <v>46</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="5">
         <v>4.0422016787925781</v>
       </c>
-      <c r="C47">
-        <v>256.16012573242188</v>
-      </c>
-      <c r="D47">
-        <v>4.0410537719726563</v>
-      </c>
-      <c r="E47">
-        <f t="shared" si="1"/>
-        <v>1.3176900672230462E-6</v>
-      </c>
-      <c r="F47">
-        <v>1.2485102750360969E-2</v>
-      </c>
-      <c r="G47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H47">
-        <v>250</v>
-      </c>
-      <c r="I47">
-        <v>281.25</v>
-      </c>
-      <c r="J47">
-        <v>0.56421679258346558</v>
-      </c>
-      <c r="K47">
-        <v>0.31834056973457342</v>
-      </c>
-      <c r="L47">
-        <v>3.9896152009509227E-3</v>
-      </c>
-      <c r="M47">
-        <v>7.979230023920536E-3</v>
-      </c>
-      <c r="N47">
-        <v>4.4552568588862579E-4</v>
-      </c>
-      <c r="O47">
-        <v>7.2476845494983699</v>
-      </c>
-      <c r="P47">
-        <v>70</v>
-      </c>
-      <c r="Q47">
-        <v>20000</v>
+      <c r="C47" s="5">
+        <v>256.17999267578119</v>
+      </c>
+      <c r="D47" s="5">
+        <v>4.0414037704467773</v>
+      </c>
+      <c r="E47" s="5">
+        <v>4.4219859773875208E-8</v>
+      </c>
+      <c r="F47" s="5">
+        <v>1.4250532723963261E-2</v>
+      </c>
+      <c r="G47" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" s="5">
+        <v>150</v>
+      </c>
+      <c r="I47" s="5">
+        <v>350</v>
+      </c>
+      <c r="J47" s="5">
+        <v>0.56292015314102173</v>
+      </c>
+      <c r="K47" s="5">
+        <v>0.31687912344932562</v>
+      </c>
+      <c r="L47" s="5">
+        <v>1.0638190951410989E-3</v>
+      </c>
+      <c r="M47" s="5">
+        <v>2.127638086676598E-3</v>
+      </c>
+      <c r="N47" s="5">
+        <v>7.9790834580073522E-4</v>
+      </c>
+      <c r="O47" s="5">
+        <v>9.6176249992013592</v>
+      </c>
+      <c r="P47" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>280000</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47">
         <f t="shared" si="0"/>
-        <v>1.1021856930743399E-2</v>
+        <v>1.973944917164731E-2</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
@@ -3421,7 +3408,7 @@
       <c r="B48">
         <v>4.097070649025869</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="14">
         <v>253.69715881347659</v>
       </c>
       <c r="D48">
@@ -3476,1345 +3463,1323 @@
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49">
+      <c r="A49" s="4">
         <v>48</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="5">
         <v>4.1351213578181021</v>
       </c>
-      <c r="C49">
-        <v>252.0335693359375</v>
-      </c>
-      <c r="D49">
-        <v>4.1341972351074219</v>
-      </c>
-      <c r="E49">
-        <f t="shared" si="1"/>
-        <v>8.5400278439493646E-7</v>
-      </c>
-      <c r="F49">
-        <v>1.27271106466651E-2</v>
-      </c>
-      <c r="G49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H49">
-        <v>243.75</v>
-      </c>
-      <c r="I49">
-        <v>281.25</v>
-      </c>
-      <c r="J49">
-        <v>0.56852781772613525</v>
-      </c>
-      <c r="K49">
-        <v>0.32322388887405401</v>
-      </c>
-      <c r="L49">
-        <v>4.0200987520733972E-3</v>
-      </c>
-      <c r="M49">
-        <v>8.0401971936225891E-3</v>
-      </c>
-      <c r="N49">
-        <v>6.5852441356106795E-4</v>
-      </c>
-      <c r="O49">
-        <v>181.2332213438458</v>
-      </c>
-      <c r="P49">
-        <v>70</v>
-      </c>
-      <c r="Q49">
-        <v>20000</v>
+      <c r="C49" s="5">
+        <v>251.94000244140619</v>
+      </c>
+      <c r="D49" s="5">
+        <v>4.1354131698608398</v>
+      </c>
+      <c r="E49" s="5">
+        <v>7.0491805672645569E-6</v>
+      </c>
+      <c r="F49" s="5">
+        <v>1.448707282543182E-2</v>
+      </c>
+      <c r="G49" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H49" s="5">
+        <v>150</v>
+      </c>
+      <c r="I49" s="5">
+        <v>350</v>
+      </c>
+      <c r="J49" s="5">
+        <v>0.56571424007415771</v>
+      </c>
+      <c r="K49" s="5">
+        <v>0.32003259658813482</v>
+      </c>
+      <c r="L49" s="5">
+        <v>1.0000509384255789E-3</v>
+      </c>
+      <c r="M49" s="5">
+        <v>2.0001018419861789E-3</v>
+      </c>
+      <c r="N49" s="5">
+        <v>2.9181204273776018E-4</v>
+      </c>
+      <c r="O49" s="5">
+        <v>1191.183645507849</v>
+      </c>
+      <c r="P49" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>320000</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49">
         <f t="shared" si="0"/>
-        <v>1.5925153256168001E-2</v>
+        <v>7.0569160488130117E-3</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50">
+      <c r="A50" s="4">
         <v>49</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="5">
         <v>4.15600701030269</v>
       </c>
-      <c r="C50">
-        <v>250.99427795410159</v>
-      </c>
-      <c r="D50">
-        <v>4.161799430847168</v>
-      </c>
-      <c r="E50">
-        <f t="shared" si="1"/>
-        <v>3.3552135764089973E-5</v>
-      </c>
-      <c r="F50">
-        <v>1.271851267665625E-2</v>
-      </c>
-      <c r="G50" t="b">
-        <v>1</v>
-      </c>
-      <c r="H50">
-        <v>243.75</v>
-      </c>
-      <c r="I50">
-        <v>281.25</v>
-      </c>
-      <c r="J50">
-        <v>0.57330280542373657</v>
-      </c>
-      <c r="K50">
-        <v>0.32867607474327087</v>
-      </c>
-      <c r="L50">
-        <v>4.0538630138839604E-3</v>
-      </c>
-      <c r="M50">
-        <v>8.1077264621853828E-3</v>
-      </c>
-      <c r="N50">
-        <v>2.3625308655228494E-3</v>
-      </c>
-      <c r="O50">
-        <v>179.5375436949052</v>
-      </c>
-      <c r="P50">
-        <v>70</v>
-      </c>
-      <c r="Q50">
-        <v>20000</v>
+      <c r="C50" s="5">
+        <v>250.9100036621094</v>
+      </c>
+      <c r="D50" s="5">
+        <v>4.1561617851257324</v>
+      </c>
+      <c r="E50" s="5">
+        <v>3.2832758734002709E-10</v>
+      </c>
+      <c r="F50" s="5">
+        <v>1.4582906849682329E-2</v>
+      </c>
+      <c r="G50" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H50" s="5">
+        <v>150</v>
+      </c>
+      <c r="I50" s="5">
+        <v>350</v>
+      </c>
+      <c r="J50" s="5">
+        <v>0.56741124391555786</v>
+      </c>
+      <c r="K50" s="5">
+        <v>0.32195550203323359</v>
+      </c>
+      <c r="L50" s="5">
+        <v>8.9715595038125987E-4</v>
+      </c>
+      <c r="M50" s="5">
+        <v>1.7943120328709481E-3</v>
+      </c>
+      <c r="N50" s="5">
+        <v>1.5477482304238069E-4</v>
+      </c>
+      <c r="O50" s="5">
+        <v>587.78948086663559</v>
+      </c>
+      <c r="P50" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>400000</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50">
         <f t="shared" si="0"/>
-        <v>5.6846171329022414E-2</v>
+        <v>3.7241232427831766E-3</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A51">
+      <c r="A51" s="4">
         <v>50</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="5">
         <v>4.1595545203155497</v>
       </c>
-      <c r="C51">
-        <v>250.8698425292969</v>
-      </c>
-      <c r="D51">
-        <v>4.1563525199890137</v>
-      </c>
-      <c r="E51">
-        <f t="shared" si="1"/>
-        <v>1.0252806091137026E-5</v>
-      </c>
-      <c r="F51">
-        <v>1.274037826806307E-2</v>
-      </c>
-      <c r="G51" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51">
-        <v>243.75</v>
-      </c>
-      <c r="I51">
-        <v>281.25</v>
-      </c>
-      <c r="J51">
-        <v>0.57071340084075928</v>
-      </c>
-      <c r="K51">
-        <v>0.32571378350257868</v>
-      </c>
-      <c r="L51">
-        <v>4.0355531584853714E-3</v>
-      </c>
-      <c r="M51">
-        <v>8.0711059272289276E-3</v>
-      </c>
-      <c r="N51">
-        <v>1.485386557004809E-3</v>
-      </c>
-      <c r="O51">
-        <v>178.92382938229639</v>
-      </c>
-      <c r="P51">
-        <v>70</v>
-      </c>
-      <c r="Q51">
-        <v>20000</v>
+      <c r="C51" s="5">
+        <v>250.78999328613281</v>
+      </c>
+      <c r="D51" s="5">
+        <v>4.1590938568115234</v>
+      </c>
+      <c r="E51" s="5">
+        <v>2.1217510948190471E-7</v>
+      </c>
+      <c r="F51" s="5">
+        <v>1.455566193908453E-2</v>
+      </c>
+      <c r="G51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="5">
+        <v>150</v>
+      </c>
+      <c r="I51" s="5">
+        <v>350</v>
+      </c>
+      <c r="J51" s="5">
+        <v>0.56645774841308594</v>
+      </c>
+      <c r="K51" s="5">
+        <v>0.32087439298629761</v>
+      </c>
+      <c r="L51" s="5">
+        <v>6.9726128828962505E-4</v>
+      </c>
+      <c r="M51" s="5">
+        <v>1.3945224927738311E-3</v>
+      </c>
+      <c r="N51" s="5">
+        <v>4.6066350402629302E-4</v>
+      </c>
+      <c r="O51" s="5">
+        <v>884.98793764202674</v>
+      </c>
+      <c r="P51" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>660000</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51">
         <f t="shared" si="0"/>
-        <v>3.5710231702699873E-2</v>
+        <v>1.1074827887851472E-2</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A52">
+      <c r="A52" s="4">
         <v>51</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="5">
         <v>4.1457622553970923</v>
       </c>
-      <c r="C52">
-        <v>251.53941345214841</v>
-      </c>
-      <c r="D52">
-        <v>4.1424875259399414</v>
-      </c>
-      <c r="E52">
-        <f t="shared" si="1"/>
-        <v>1.0723853017531858E-5</v>
-      </c>
-      <c r="F52">
-        <v>1.293047517538071E-2</v>
-      </c>
-      <c r="G52" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52">
-        <v>243.75</v>
-      </c>
-      <c r="I52">
-        <v>281.25</v>
-      </c>
-      <c r="J52">
-        <v>0.56968891620635986</v>
-      </c>
-      <c r="K52">
-        <v>0.3245454728603363</v>
-      </c>
-      <c r="L52">
-        <v>4.0283089581633191E-3</v>
-      </c>
-      <c r="M52">
-        <v>8.0566182732582092E-3</v>
-      </c>
-      <c r="N52">
-        <v>2.8925200964113884E-4</v>
-      </c>
-      <c r="O52">
-        <v>177.46833628837209</v>
-      </c>
-      <c r="P52">
-        <v>70</v>
-      </c>
-      <c r="Q52">
-        <v>20000</v>
+      <c r="C52" s="5">
+        <v>251.50999450683591</v>
+      </c>
+      <c r="D52" s="5">
+        <v>4.1459274291992188</v>
+      </c>
+      <c r="E52" s="5">
+        <v>2.2418134904000911E-8</v>
+      </c>
+      <c r="F52" s="5">
+        <v>1.4572064392268659E-2</v>
+      </c>
+      <c r="G52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="5">
+        <v>150</v>
+      </c>
+      <c r="I52" s="5">
+        <v>350</v>
+      </c>
+      <c r="J52" s="5">
+        <v>0.56673741340637207</v>
+      </c>
+      <c r="K52" s="5">
+        <v>0.32119128108024603</v>
+      </c>
+      <c r="L52" s="5">
+        <v>8.1801499547500282E-4</v>
+      </c>
+      <c r="M52" s="5">
+        <v>1.6360300360247491E-3</v>
+      </c>
+      <c r="N52" s="5">
+        <v>1.6517380212643931E-4</v>
+      </c>
+      <c r="O52" s="5">
+        <v>588.66450491450598</v>
+      </c>
+      <c r="P52" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>480000</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52">
         <f t="shared" si="0"/>
-        <v>6.9770525134329854E-3</v>
+        <v>3.9841600157223319E-3</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A53">
+      <c r="A53" s="4">
         <v>52</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="5">
         <v>4.1148000406331944</v>
       </c>
-      <c r="C53">
-        <v>252.98548889160159</v>
-      </c>
-      <c r="D53">
-        <v>4.1215057373046884</v>
-      </c>
-      <c r="E53">
-        <f t="shared" si="1"/>
-        <v>4.4966367850085851E-5</v>
-      </c>
-      <c r="F53">
-        <v>1.295876502990723E-2</v>
-      </c>
-      <c r="G53" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53">
-        <v>243.75</v>
-      </c>
-      <c r="I53">
-        <v>281.25</v>
-      </c>
-      <c r="J53">
-        <v>0.56890952587127686</v>
-      </c>
-      <c r="K53">
-        <v>0.3236580491065979</v>
-      </c>
-      <c r="L53">
-        <v>4.0227978362520336E-3</v>
-      </c>
-      <c r="M53">
-        <v>8.045596070587635E-3</v>
-      </c>
-      <c r="N53">
-        <v>4.2997049398350029E-3</v>
-      </c>
-      <c r="O53">
-        <v>179.75586245188671</v>
-      </c>
-      <c r="P53">
-        <v>70</v>
-      </c>
-      <c r="Q53">
-        <v>20000</v>
+      <c r="C53" s="5">
+        <v>252.80000305175781</v>
+      </c>
+      <c r="D53" s="5">
+        <v>4.1145315170288086</v>
+      </c>
+      <c r="E53" s="5">
+        <v>3.7849531508982182E-8</v>
+      </c>
+      <c r="F53" s="5">
+        <v>1.4434087090194231E-2</v>
+      </c>
+      <c r="G53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="5">
+        <v>150</v>
+      </c>
+      <c r="I53" s="5">
+        <v>350</v>
+      </c>
+      <c r="J53" s="5">
+        <v>0.56644052267074585</v>
+      </c>
+      <c r="K53" s="5">
+        <v>0.32085487246513372</v>
+      </c>
+      <c r="L53" s="5">
+        <v>8.0106786943867333E-4</v>
+      </c>
+      <c r="M53" s="5">
+        <v>1.602135715074837E-3</v>
+      </c>
+      <c r="N53" s="5">
+        <v>2.6852360438578421E-4</v>
+      </c>
+      <c r="O53" s="5">
+        <v>599.97253529058389</v>
+      </c>
+      <c r="P53" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>500000</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
       <c r="S53">
         <f t="shared" si="0"/>
-        <v>0.10449365454884546</v>
+        <v>6.5257995949777239E-3</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A54">
+      <c r="A54" s="4">
         <v>53</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="5">
         <v>4.067011505252216</v>
       </c>
-      <c r="C54">
-        <v>254.99934387207031</v>
-      </c>
-      <c r="D54">
-        <v>4.0627474784851074</v>
-      </c>
-      <c r="E54">
-        <f t="shared" si="1"/>
-        <v>1.8181924270618406E-5</v>
-      </c>
-      <c r="F54">
-        <v>1.273172348737717E-2</v>
-      </c>
-      <c r="G54" t="b">
-        <v>1</v>
-      </c>
-      <c r="H54">
-        <v>243.75</v>
-      </c>
-      <c r="I54">
-        <v>281.25</v>
-      </c>
-      <c r="J54">
-        <v>0.56720024347305298</v>
-      </c>
-      <c r="K54">
-        <v>0.32171612977981567</v>
-      </c>
-      <c r="L54">
-        <v>4.0107113845045646E-3</v>
-      </c>
-      <c r="M54">
-        <v>8.0214226618409157E-3</v>
-      </c>
-      <c r="N54">
-        <v>9.4047177443279395E-4</v>
-      </c>
-      <c r="O54">
-        <v>187.28636017131859</v>
-      </c>
-      <c r="P54">
-        <v>70</v>
-      </c>
-      <c r="Q54">
-        <v>20000</v>
+      <c r="C54" s="5">
+        <v>255.1499938964844</v>
+      </c>
+      <c r="D54" s="5">
+        <v>4.0666408538818359</v>
+      </c>
+      <c r="E54" s="5">
+        <v>1.743356051520095E-6</v>
+      </c>
+      <c r="F54" s="5">
+        <v>1.426623295992613E-2</v>
+      </c>
+      <c r="G54" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H54" s="5">
+        <v>150</v>
+      </c>
+      <c r="I54" s="5">
+        <v>350</v>
+      </c>
+      <c r="J54" s="5">
+        <v>0.56381362676620483</v>
+      </c>
+      <c r="K54" s="5">
+        <v>0.31788578629493708</v>
+      </c>
+      <c r="L54" s="5">
+        <v>1.1057294941963071E-3</v>
+      </c>
+      <c r="M54" s="5">
+        <v>2.2114589810371399E-3</v>
+      </c>
+      <c r="N54" s="5">
+        <v>3.7065137038005957E-4</v>
+      </c>
+      <c r="O54" s="5">
+        <v>307.08697351592332</v>
+      </c>
+      <c r="P54" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>260000</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54">
         <f t="shared" si="0"/>
-        <v>2.3124394244231933E-2</v>
+        <v>9.1136051594984026E-3</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A55">
+      <c r="A55" s="4">
         <v>54</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="5">
         <v>4.0029182471614666</v>
       </c>
-      <c r="C55">
-        <v>258.19088745117188</v>
-      </c>
-      <c r="D55">
-        <v>4.0063467025756836</v>
-      </c>
-      <c r="E55">
-        <f t="shared" si="1"/>
-        <v>1.1754306527273798E-5</v>
-      </c>
-      <c r="F55">
-        <v>1.252659130841494E-2</v>
-      </c>
-      <c r="G55" t="b">
-        <v>1</v>
-      </c>
-      <c r="H55">
-        <v>243.75</v>
-      </c>
-      <c r="I55">
-        <v>281.25</v>
-      </c>
-      <c r="J55">
-        <v>0.56848174333572388</v>
-      </c>
-      <c r="K55">
-        <v>0.32317152619361877</v>
-      </c>
-      <c r="L55">
-        <v>4.019772956934408E-3</v>
-      </c>
-      <c r="M55">
-        <v>8.0395461991429329E-3</v>
-      </c>
-      <c r="N55">
-        <v>1.7991028446360251E-3</v>
-      </c>
-      <c r="O55">
-        <v>196.49784867557051</v>
-      </c>
-      <c r="P55">
-        <v>70</v>
-      </c>
-      <c r="Q55">
-        <v>20000</v>
+      <c r="C55" s="5">
+        <v>258.05999755859381</v>
+      </c>
+      <c r="D55" s="5">
+        <v>4.0022702217102051</v>
+      </c>
+      <c r="E55" s="5">
+        <v>3.8651542126899594E-6</v>
+      </c>
+      <c r="F55" s="5">
+        <v>1.398136280477047E-2</v>
+      </c>
+      <c r="G55" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H55" s="5">
+        <v>150</v>
+      </c>
+      <c r="I55" s="5">
+        <v>350</v>
+      </c>
+      <c r="J55" s="5">
+        <v>0.56255006790161133</v>
+      </c>
+      <c r="K55" s="5">
+        <v>0.31646260619163508</v>
+      </c>
+      <c r="L55" s="5">
+        <v>1.1032514513858701E-3</v>
+      </c>
+      <c r="M55" s="5">
+        <v>2.2065029479563241E-3</v>
+      </c>
+      <c r="N55" s="5">
+        <v>6.4802545126241284E-4</v>
+      </c>
+      <c r="O55" s="5">
+        <v>4.9957538585157222</v>
+      </c>
+      <c r="P55" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>260000</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
       <c r="S55">
         <f t="shared" si="0"/>
-        <v>4.4944781120918417E-2</v>
+        <v>1.6188825533020517E-2</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A56">
+      <c r="A56" s="4">
         <v>55</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="5">
         <v>3.9232247344705549</v>
       </c>
-      <c r="C56">
-        <v>262.25241088867188</v>
-      </c>
-      <c r="D56">
-        <v>3.9237735271453862</v>
-      </c>
-      <c r="E56">
-        <f t="shared" si="1"/>
-        <v>3.0117339994851722E-7</v>
-      </c>
-      <c r="F56">
-        <v>1.2412853538990021E-2</v>
-      </c>
-      <c r="G56" t="b">
-        <v>1</v>
-      </c>
-      <c r="H56">
-        <v>243.75</v>
-      </c>
-      <c r="I56">
-        <v>281.25</v>
-      </c>
-      <c r="J56">
-        <v>0.56167358160018921</v>
-      </c>
-      <c r="K56">
-        <v>0.31547722220420837</v>
-      </c>
-      <c r="L56">
-        <v>3.971631983628294E-3</v>
-      </c>
-      <c r="M56">
-        <v>7.9432642087340355E-3</v>
-      </c>
-      <c r="N56">
-        <v>5.4879267483043392E-4</v>
-      </c>
-      <c r="O56">
-        <v>206.4363373013482</v>
-      </c>
-      <c r="P56">
-        <v>70</v>
-      </c>
-      <c r="Q56">
-        <v>20000</v>
+      <c r="C56" s="5">
+        <v>262.20001220703119</v>
+      </c>
+      <c r="D56" s="5">
+        <v>3.9232628345489502</v>
+      </c>
+      <c r="E56" s="5">
+        <v>2.4686016786290569E-8</v>
+      </c>
+      <c r="F56" s="5">
+        <v>1.3700198382139209E-2</v>
+      </c>
+      <c r="G56" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H56" s="5">
+        <v>150</v>
+      </c>
+      <c r="I56" s="5">
+        <v>350</v>
+      </c>
+      <c r="J56" s="5">
+        <v>0.56107932329177856</v>
+      </c>
+      <c r="K56" s="5">
+        <v>0.31480997800827032</v>
+      </c>
+      <c r="L56" s="5">
+        <v>1.060340253721754E-3</v>
+      </c>
+      <c r="M56" s="5">
+        <v>2.120680408552289E-3</v>
+      </c>
+      <c r="N56" s="5">
+        <v>3.8100078394887049E-5</v>
+      </c>
+      <c r="O56" s="5">
+        <v>665.97250768075253</v>
+      </c>
+      <c r="P56" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q56" s="6">
+        <v>280000</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56">
         <f t="shared" si="0"/>
-        <v>1.3988305844643242E-2</v>
+        <v>9.7114187877459716E-4</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A57">
+      <c r="A57" s="4">
         <v>56</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="5">
         <v>3.8288224192227061</v>
       </c>
-      <c r="C57">
-        <v>267.4197998046875</v>
-      </c>
-      <c r="D57">
-        <v>3.828858613967896</v>
-      </c>
-      <c r="E57">
-        <f t="shared" si="1"/>
-        <v>1.3100595793617298E-9</v>
-      </c>
-      <c r="F57">
-        <v>1.2247589416801929E-2</v>
-      </c>
-      <c r="G57" t="b">
-        <v>1</v>
-      </c>
-      <c r="H57">
-        <v>243.75</v>
-      </c>
-      <c r="I57">
-        <v>281.25</v>
-      </c>
-      <c r="J57">
-        <v>0.5634920597076416</v>
-      </c>
-      <c r="K57">
-        <v>0.3175233006477356</v>
-      </c>
-      <c r="L57">
-        <v>3.9844905656404826E-3</v>
-      </c>
-      <c r="M57">
-        <v>7.9689808189868927E-3</v>
-      </c>
-      <c r="N57">
-        <v>3.333762112743166E-3</v>
-      </c>
-      <c r="O57">
-        <v>219.66612145933709</v>
-      </c>
-      <c r="P57">
-        <v>70</v>
-      </c>
-      <c r="Q57">
-        <v>20000</v>
+      <c r="C57" s="5">
+        <v>267.23001098632813</v>
+      </c>
+      <c r="D57" s="5">
+        <v>3.827543973922729</v>
+      </c>
+      <c r="E57" s="5">
+        <v>2.5768990781216421E-6</v>
+      </c>
+      <c r="F57" s="5">
+        <v>1.326256711035967E-2</v>
+      </c>
+      <c r="G57" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H57" s="5">
+        <v>150</v>
+      </c>
+      <c r="I57" s="5">
+        <v>350</v>
+      </c>
+      <c r="J57" s="5">
+        <v>0.56022447347640991</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0.31385144591331482</v>
+      </c>
+      <c r="L57" s="5">
+        <v>1.2527000053522809E-3</v>
+      </c>
+      <c r="M57" s="5">
+        <v>2.5053999852389102E-3</v>
+      </c>
+      <c r="N57" s="5">
+        <v>1.278445299976561E-3</v>
+      </c>
+      <c r="O57" s="5">
+        <v>1065.9727016822189</v>
+      </c>
+      <c r="P57" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q57" s="6">
+        <v>200000</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57">
         <f t="shared" si="0"/>
-        <v>8.7070167997500308E-2</v>
+        <v>3.3390039025003926E-2</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A58">
+      <c r="A58" s="4">
         <v>57</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="5">
         <v>3.72079126374026</v>
       </c>
-      <c r="C58">
-        <v>273.67919921875</v>
-      </c>
-      <c r="D58">
-        <v>3.7188000679016109</v>
-      </c>
-      <c r="E58">
-        <f t="shared" si="1"/>
-        <v>3.9648608678536969E-6</v>
-      </c>
-      <c r="F58">
-        <v>1.1986366473138331E-2</v>
-      </c>
-      <c r="G58" t="b">
-        <v>1</v>
-      </c>
-      <c r="H58">
-        <v>243.75</v>
-      </c>
-      <c r="I58">
-        <v>281.25</v>
-      </c>
-      <c r="J58">
-        <v>0.55222922563552856</v>
-      </c>
-      <c r="K58">
-        <v>0.30495712161064148</v>
-      </c>
-      <c r="L58">
-        <v>3.9048503021627832E-3</v>
-      </c>
-      <c r="M58">
-        <v>7.8097004443407059E-3</v>
-      </c>
-      <c r="N58">
-        <v>1.9911958386491513E-3</v>
-      </c>
-      <c r="O58">
-        <v>241.15485667158779</v>
-      </c>
-      <c r="P58">
-        <v>70</v>
-      </c>
-      <c r="Q58">
-        <v>20000</v>
+      <c r="C58" s="5">
+        <v>273.60000610351563</v>
+      </c>
+      <c r="D58" s="5">
+        <v>3.7211899757385249</v>
+      </c>
+      <c r="E58" s="5">
+        <v>1.0618171017995339E-6</v>
+      </c>
+      <c r="F58" s="5">
+        <v>1.2790507636964319E-2</v>
+      </c>
+      <c r="G58" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" s="5">
+        <v>150</v>
+      </c>
+      <c r="I58" s="5">
+        <v>350</v>
+      </c>
+      <c r="J58" s="5">
+        <v>0.55959314107894897</v>
+      </c>
+      <c r="K58" s="5">
+        <v>0.31314447522163391</v>
+      </c>
+      <c r="L58" s="5">
+        <v>1.021672621313704E-3</v>
+      </c>
+      <c r="M58" s="5">
+        <v>2.0433452446013689E-3</v>
+      </c>
+      <c r="N58" s="5">
+        <v>3.9871199826491122E-4</v>
+      </c>
+      <c r="O58" s="5">
+        <v>764.07229097612867</v>
+      </c>
+      <c r="P58" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>300000</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58">
         <f t="shared" si="0"/>
-        <v>5.3515386849396565E-2</v>
+        <v>1.0715785165118695E-2</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A59">
+      <c r="A59" s="4">
         <v>58</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="5">
         <v>3.6003968225698841</v>
       </c>
-      <c r="C59">
-        <v>281.34915161132813</v>
-      </c>
-      <c r="D59">
-        <v>3.603272676467896</v>
-      </c>
-      <c r="E59">
-        <f t="shared" si="1"/>
-        <v>8.2705356427097528E-6</v>
-      </c>
-      <c r="F59">
-        <v>1.15339457988739E-2</v>
-      </c>
-      <c r="G59" t="b">
-        <v>1</v>
-      </c>
-      <c r="H59">
-        <v>237.5</v>
-      </c>
-      <c r="I59">
-        <v>312.5</v>
-      </c>
-      <c r="J59">
-        <v>0.55614835023880005</v>
-      </c>
-      <c r="K59">
-        <v>0.3093009889125824</v>
-      </c>
-      <c r="L59">
-        <v>3.9325626979956653E-3</v>
-      </c>
-      <c r="M59">
-        <v>7.8651253134012222E-3</v>
-      </c>
-      <c r="N59">
-        <v>2.8758538980118153E-3</v>
-      </c>
-      <c r="O59">
-        <v>263.79435852576103</v>
-      </c>
-      <c r="P59">
-        <v>70</v>
-      </c>
-      <c r="Q59">
-        <v>20000</v>
+      <c r="C59" s="5">
+        <v>281.260009765625</v>
+      </c>
+      <c r="D59" s="5">
+        <v>3.6008837223052979</v>
+      </c>
+      <c r="E59" s="5">
+        <v>1.222234004671918E-6</v>
+      </c>
+      <c r="F59" s="5">
+        <v>1.2174877338111401E-2</v>
+      </c>
+      <c r="G59" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H59" s="5">
+        <v>150</v>
+      </c>
+      <c r="I59" s="5">
+        <v>350</v>
+      </c>
+      <c r="J59" s="5">
+        <v>0.56012874841690063</v>
+      </c>
+      <c r="K59" s="5">
+        <v>0.31374424695968628</v>
+      </c>
+      <c r="L59" s="5">
+        <v>1.1941985041385469E-3</v>
+      </c>
+      <c r="M59" s="5">
+        <v>2.388396998867393E-3</v>
+      </c>
+      <c r="N59" s="5">
+        <v>4.8689973541371501E-4</v>
+      </c>
+      <c r="O59" s="5">
+        <v>1264.9462831585199</v>
+      </c>
+      <c r="P59" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q59" s="6">
+        <v>220000</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59">
         <f t="shared" si="0"/>
-        <v>7.9876025886476978E-2</v>
+        <v>1.3523501975156635E-2</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A60">
+      <c r="A60" s="4">
         <v>59</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="5">
         <v>3.469081214710001</v>
       </c>
-      <c r="C60">
-        <v>290.4407958984375</v>
-      </c>
-      <c r="D60">
-        <v>3.4685320854187012</v>
-      </c>
-      <c r="E60">
-        <f t="shared" si="1"/>
-        <v>3.0154297856341968E-7</v>
-      </c>
-      <c r="F60">
-        <v>1.0762457735836509E-2</v>
-      </c>
-      <c r="G60" t="b">
-        <v>1</v>
-      </c>
-      <c r="H60">
-        <v>268.75</v>
-      </c>
-      <c r="I60">
-        <v>306.25</v>
-      </c>
-      <c r="J60">
-        <v>0.56472533941268921</v>
-      </c>
-      <c r="K60">
-        <v>0.3189147412776947</v>
-      </c>
-      <c r="L60">
-        <v>3.993211170065872E-3</v>
-      </c>
-      <c r="M60">
-        <v>7.9864226281642914E-3</v>
-      </c>
-      <c r="N60">
-        <v>5.4912929129979915E-4</v>
-      </c>
-      <c r="O60">
-        <v>380.63942514661818</v>
-      </c>
-      <c r="P60">
-        <v>60</v>
-      </c>
-      <c r="Q60">
-        <v>20000</v>
+      <c r="C60" s="5">
+        <v>290.45001220703119</v>
+      </c>
+      <c r="D60" s="5">
+        <v>3.469589471817017</v>
+      </c>
+      <c r="E60" s="5">
+        <v>2.38835150412342E-6</v>
+      </c>
+      <c r="F60" s="5">
+        <v>1.1456123553216461E-2</v>
+      </c>
+      <c r="G60" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" s="5">
+        <v>150</v>
+      </c>
+      <c r="I60" s="5">
+        <v>350</v>
+      </c>
+      <c r="J60" s="5">
+        <v>0.55808240175247192</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0.31145599484443659</v>
+      </c>
+      <c r="L60" s="5">
+        <v>1.189835678390866E-3</v>
+      </c>
+      <c r="M60" s="5">
+        <v>2.3796714376658201E-3</v>
+      </c>
+      <c r="N60" s="5">
+        <v>5.0825710701607463E-4</v>
+      </c>
+      <c r="O60" s="5">
+        <v>59.52709003722272</v>
+      </c>
+      <c r="P60" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>220000</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60">
         <f t="shared" si="0"/>
-        <v>1.5829242883427387E-2</v>
+        <v>1.4651058178197264E-2</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A61">
+      <c r="A61" s="4">
         <v>60</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="5">
         <v>3.328446766773975</v>
       </c>
-      <c r="C61">
-        <v>301.4334716796875</v>
-      </c>
-      <c r="D61">
-        <v>3.3293106555938721</v>
-      </c>
-      <c r="E61">
-        <f t="shared" si="1"/>
-        <v>7.4630389314315915E-7</v>
-      </c>
-      <c r="F61">
-        <v>9.7767766565084457E-3</v>
-      </c>
-      <c r="G61" t="b">
-        <v>1</v>
-      </c>
-      <c r="H61">
-        <v>293.75</v>
-      </c>
-      <c r="I61">
-        <v>331.25</v>
-      </c>
-      <c r="J61">
-        <v>0.56311213970184326</v>
-      </c>
-      <c r="K61">
-        <v>0.3170953094959259</v>
-      </c>
-      <c r="L61">
-        <v>3.9818041255163987E-3</v>
-      </c>
-      <c r="M61">
-        <v>7.963608019053936E-3</v>
-      </c>
-      <c r="N61">
-        <v>8.63888819897074E-4</v>
-      </c>
-      <c r="O61">
-        <v>364.13734732479082</v>
-      </c>
-      <c r="P61">
-        <v>70</v>
-      </c>
-      <c r="Q61">
-        <v>20000</v>
+      <c r="C61" s="5">
+        <v>301.29998779296881</v>
+      </c>
+      <c r="D61" s="5">
+        <v>3.3281962871551509</v>
+      </c>
+      <c r="E61" s="5">
+        <v>6.5479275690449867E-7</v>
+      </c>
+      <c r="F61" s="5">
+        <v>9.5997462049126625E-3</v>
+      </c>
+      <c r="G61" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" s="5">
+        <v>250</v>
+      </c>
+      <c r="I61" s="5">
+        <v>450</v>
+      </c>
+      <c r="J61" s="5">
+        <v>0.55857229232788086</v>
+      </c>
+      <c r="K61" s="5">
+        <v>0.31200301647186279</v>
+      </c>
+      <c r="L61" s="5">
+        <v>9.5794357834039418E-4</v>
+      </c>
+      <c r="M61" s="5">
+        <v>1.915887114591897E-3</v>
+      </c>
+      <c r="N61" s="5">
+        <v>2.5047961882362912E-4</v>
+      </c>
+      <c r="O61" s="5">
+        <v>2034.6127849799509</v>
+      </c>
+      <c r="P61" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>340000</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61">
         <f t="shared" si="0"/>
-        <v>2.5954713427319722E-2</v>
+        <v>7.5254206053113806E-3</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A62">
+      <c r="A62" s="4">
         <v>61</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="5">
         <v>3.1802317779983489</v>
       </c>
-      <c r="C62">
-        <v>314.10568237304688</v>
-      </c>
-      <c r="D62">
-        <v>3.181837797164917</v>
-      </c>
-      <c r="E62">
-        <f t="shared" si="1"/>
-        <v>2.5792975633841161E-6</v>
-      </c>
-      <c r="F62">
-        <v>9.2242155224084854E-3</v>
-      </c>
-      <c r="G62" t="b">
-        <v>1</v>
-      </c>
-      <c r="H62">
-        <v>287.5</v>
-      </c>
-      <c r="I62">
-        <v>362.5</v>
-      </c>
-      <c r="J62">
-        <v>0.55942076444625854</v>
-      </c>
-      <c r="K62">
-        <v>0.31295162439346308</v>
-      </c>
-      <c r="L62">
-        <v>3.9557021607651167E-3</v>
-      </c>
-      <c r="M62">
-        <v>7.9114045947790146E-3</v>
-      </c>
-      <c r="N62">
-        <v>1.6060191665676631E-3</v>
-      </c>
-      <c r="O62">
-        <v>422.76318571851141</v>
-      </c>
-      <c r="P62">
-        <v>70</v>
-      </c>
-      <c r="Q62">
-        <v>20000</v>
+      <c r="C62" s="5">
+        <v>314.1099853515625</v>
+      </c>
+      <c r="D62" s="5">
+        <v>3.1814558506011958</v>
+      </c>
+      <c r="E62" s="5">
+        <v>5.7607671806181324E-6</v>
+      </c>
+      <c r="F62" s="5">
+        <v>9.1216601431369781E-3</v>
+      </c>
+      <c r="G62" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" s="5">
+        <v>250</v>
+      </c>
+      <c r="I62" s="5">
+        <v>450</v>
+      </c>
+      <c r="J62" s="5">
+        <v>0.55801725387573242</v>
+      </c>
+      <c r="K62" s="5">
+        <v>0.31138324737548828</v>
+      </c>
+      <c r="L62" s="5">
+        <v>1.247764512283896E-3</v>
+      </c>
+      <c r="M62" s="5">
+        <v>2.4955291301012039E-3</v>
+      </c>
+      <c r="N62" s="5">
+        <v>1.2240726028469599E-3</v>
+      </c>
+      <c r="O62" s="5">
+        <v>1.467108664723638</v>
+      </c>
+      <c r="P62" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>200000</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62">
         <f t="shared" si="0"/>
-        <v>5.0500066620254268E-2</v>
+        <v>3.849004375452774E-2</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63">
+      <c r="A63" s="4">
         <v>62</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="5">
         <v>3.0262786837990991</v>
       </c>
-      <c r="C63">
-        <v>328.86175537109381</v>
-      </c>
-      <c r="D63">
-        <v>3.0251514911651598</v>
-      </c>
-      <c r="E63">
-        <f t="shared" si="1"/>
-        <v>1.2705632340071172E-6</v>
-      </c>
-      <c r="F63">
-        <v>8.8695427402853966E-3</v>
-      </c>
-      <c r="G63" t="b">
-        <v>1</v>
-      </c>
-      <c r="H63">
-        <v>287.5</v>
-      </c>
-      <c r="I63">
-        <v>362.5</v>
-      </c>
-      <c r="J63">
-        <v>0.55888545513153076</v>
-      </c>
-      <c r="K63">
-        <v>0.31235295534133911</v>
-      </c>
-      <c r="L63">
-        <v>3.9519169523003529E-3</v>
-      </c>
-      <c r="M63">
-        <v>7.9038338735699654E-3</v>
-      </c>
-      <c r="N63">
-        <v>1.1271926339393445E-3</v>
-      </c>
-      <c r="O63">
-        <v>485.54007470391292</v>
-      </c>
-      <c r="P63">
-        <v>70</v>
-      </c>
-      <c r="Q63">
-        <v>20000</v>
+      <c r="C63" s="5">
+        <v>328.85000610351563</v>
+      </c>
+      <c r="D63" s="5">
+        <v>3.0265834331512451</v>
+      </c>
+      <c r="E63" s="5">
+        <v>2.115143615810666E-10</v>
+      </c>
+      <c r="F63" s="5">
+        <v>8.6211152374744415E-3</v>
+      </c>
+      <c r="G63" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" s="5">
+        <v>250</v>
+      </c>
+      <c r="I63" s="5">
+        <v>450</v>
+      </c>
+      <c r="J63" s="5">
+        <v>0.55909621715545654</v>
+      </c>
+      <c r="K63" s="5">
+        <v>0.31258857250213617</v>
+      </c>
+      <c r="L63" s="5">
+        <v>9.8835181621592465E-4</v>
+      </c>
+      <c r="M63" s="5">
+        <v>1.9767035264521842E-3</v>
+      </c>
+      <c r="N63" s="5">
+        <v>3.047493521459721E-4</v>
+      </c>
+      <c r="O63" s="5">
+        <v>672.73357594753872</v>
+      </c>
+      <c r="P63" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>320000</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63">
         <f t="shared" si="0"/>
-        <v>3.7246821978876743E-2</v>
+        <v>1.0070102062226435E-2</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A64">
+      <c r="A64" s="4">
         <v>63</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="5">
         <v>2.8684957729033602</v>
       </c>
-      <c r="C64">
-        <v>345.71453857421881</v>
-      </c>
-      <c r="D64">
-        <v>2.8730683326721191</v>
-      </c>
-      <c r="E64">
-        <f t="shared" si="1"/>
-        <v>2.0908302838872642E-5</v>
-      </c>
-      <c r="F64">
-        <v>8.0108987167477608E-3</v>
-      </c>
-      <c r="G64" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64">
-        <v>287.5</v>
-      </c>
-      <c r="I64">
-        <v>362.5</v>
-      </c>
-      <c r="J64">
-        <v>0.55314689874649048</v>
-      </c>
-      <c r="K64">
-        <v>0.30597147345542908</v>
-      </c>
-      <c r="L64">
-        <v>3.9113392309595204E-3</v>
-      </c>
-      <c r="M64">
-        <v>7.8226784244179726E-3</v>
-      </c>
-      <c r="N64">
-        <v>4.5725597687589215E-3</v>
-      </c>
-      <c r="O64">
-        <v>598.34887648509323</v>
-      </c>
-      <c r="P64">
-        <v>70</v>
-      </c>
-      <c r="Q64">
-        <v>20000</v>
+      <c r="C64" s="5">
+        <v>345.75</v>
+      </c>
+      <c r="D64" s="5">
+        <v>2.8683044910430908</v>
+      </c>
+      <c r="E64" s="5">
+        <v>3.3912883736775261E-6</v>
+      </c>
+      <c r="F64" s="5">
+        <v>8.0162491649389267E-3</v>
+      </c>
+      <c r="G64" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" s="5">
+        <v>250</v>
+      </c>
+      <c r="I64" s="5">
+        <v>450</v>
+      </c>
+      <c r="J64" s="5">
+        <v>0.55621474981307983</v>
+      </c>
+      <c r="K64" s="5">
+        <v>0.30937483906745911</v>
+      </c>
+      <c r="L64" s="5">
+        <v>1.135368603709876E-3</v>
+      </c>
+      <c r="M64" s="5">
+        <v>2.2707371972501278E-3</v>
+      </c>
+      <c r="N64" s="5">
+        <v>1.912818602689548E-4</v>
+      </c>
+      <c r="O64" s="5">
+        <v>243.15186816145689</v>
+      </c>
+      <c r="P64" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>240000</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64">
         <f t="shared" si="0"/>
-        <v>0.15940618814755253</v>
+        <v>6.6683682115155438E-3</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A65">
+      <c r="A65" s="4">
         <v>64</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="5">
         <v>2.708814420507546</v>
       </c>
-      <c r="C65">
-        <v>365.6883544921875</v>
-      </c>
-      <c r="D65">
-        <v>2.7025988101959229</v>
-      </c>
-      <c r="E65">
-        <f t="shared" si="1"/>
-        <v>3.8633811545955397E-5</v>
-      </c>
-      <c r="F65">
-        <v>7.1754790842533112E-3</v>
-      </c>
-      <c r="G65" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65">
-        <v>337.5</v>
-      </c>
-      <c r="I65">
-        <v>412.5</v>
-      </c>
-      <c r="J65">
-        <v>0.55504179000854492</v>
-      </c>
-      <c r="K65">
-        <v>0.30807137489318848</v>
-      </c>
-      <c r="L65">
-        <v>3.9247381355696194E-3</v>
-      </c>
-      <c r="M65">
-        <v>7.8494763001799583E-3</v>
-      </c>
-      <c r="N65">
-        <v>6.2156103116230987E-3</v>
-      </c>
-      <c r="O65">
-        <v>749.09127881087397</v>
-      </c>
-      <c r="P65">
-        <v>70</v>
-      </c>
-      <c r="Q65">
-        <v>20000</v>
+      <c r="C65" s="5">
+        <v>365.32000732421881</v>
+      </c>
+      <c r="D65" s="5">
+        <v>2.7095685005187988</v>
+      </c>
+      <c r="E65" s="5">
+        <v>9.4007418738328852E-8</v>
+      </c>
+      <c r="F65" s="5">
+        <v>7.1941041387617588E-3</v>
+      </c>
+      <c r="G65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" s="5">
+        <v>250</v>
+      </c>
+      <c r="I65" s="5">
+        <v>450</v>
+      </c>
+      <c r="J65" s="5">
+        <v>0.55195343494415283</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0.30465260148048401</v>
+      </c>
+      <c r="L65" s="5">
+        <v>9.465923315747001E-4</v>
+      </c>
+      <c r="M65" s="5">
+        <v>1.8931846134364601E-3</v>
+      </c>
+      <c r="N65" s="5">
+        <v>7.5408001125243374E-4</v>
+      </c>
+      <c r="O65" s="5">
+        <v>9.4344504375109732</v>
+      </c>
+      <c r="P65" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q65" s="6">
+        <v>340000</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65">
         <f t="shared" si="0"/>
-        <v>0.22945869840941302</v>
+        <v>2.7838009335137213E-2</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A66">
+      <c r="A66" s="4">
         <v>65</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="5">
         <v>2.5491444140341089</v>
       </c>
-      <c r="C66">
-        <v>387.21563720703119</v>
-      </c>
-      <c r="D66">
-        <v>2.5520672798156738</v>
-      </c>
-      <c r="E66">
-        <f t="shared" si="1"/>
-        <v>8.5431443770434383E-6</v>
-      </c>
-      <c r="F66">
-        <v>6.4726513810455799E-3</v>
-      </c>
-      <c r="G66" t="b">
-        <v>1</v>
-      </c>
-      <c r="H66">
-        <v>337.5</v>
-      </c>
-      <c r="I66">
-        <v>412.5</v>
-      </c>
-      <c r="J66">
-        <v>0.54844218492507935</v>
-      </c>
-      <c r="K66">
-        <v>0.30078881978988647</v>
-      </c>
-      <c r="L66">
-        <v>3.8780718804929011E-3</v>
-      </c>
-      <c r="M66">
-        <v>7.7561438083648682E-3</v>
-      </c>
-      <c r="N66">
-        <v>2.922865781564532E-3</v>
-      </c>
-      <c r="O66">
-        <v>937.7197287256713</v>
-      </c>
-      <c r="P66">
-        <v>70</v>
-      </c>
-      <c r="Q66">
-        <v>20000</v>
+      <c r="C66" s="5">
+        <v>387.45999145507813</v>
+      </c>
+      <c r="D66" s="5">
+        <v>2.5488102436065669</v>
+      </c>
+      <c r="E66" s="5">
+        <v>4.7607704800611828E-7</v>
+      </c>
+      <c r="F66" s="5">
+        <v>6.418637465685606E-3</v>
+      </c>
+      <c r="G66" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" s="5">
+        <v>250</v>
+      </c>
+      <c r="I66" s="5">
+        <v>450</v>
+      </c>
+      <c r="J66" s="5">
+        <v>0.54821419715881348</v>
+      </c>
+      <c r="K66" s="5">
+        <v>0.30053877830505371</v>
+      </c>
+      <c r="L66" s="5">
+        <v>9.6911494088433982E-4</v>
+      </c>
+      <c r="M66" s="5">
+        <v>1.9382298924028869E-3</v>
+      </c>
+      <c r="N66" s="5">
+        <v>3.3417042754191328E-4</v>
+      </c>
+      <c r="O66" s="5">
+        <v>3034.0610797066929</v>
+      </c>
+      <c r="P66" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q66" s="6">
+        <v>320000</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66">
         <f t="shared" si="0"/>
-        <v>0.11466065890472625</v>
+        <v>1.3109121072237608E-2</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A67">
+      <c r="A67" s="4">
         <v>66</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="5">
         <v>2.3913302718645761</v>
       </c>
-      <c r="C67">
-        <v>412.17422485351563</v>
-      </c>
-      <c r="D67">
-        <v>2.3920919895172119</v>
-      </c>
-      <c r="E67">
-        <f t="shared" ref="E67:E102" si="2">(B67-D67)^2</f>
-        <v>5.802137823369534E-7</v>
-      </c>
-      <c r="F67">
-        <v>5.6412206031382084E-3</v>
-      </c>
-      <c r="G67" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67">
-        <v>387.5</v>
-      </c>
-      <c r="I67">
-        <v>462.5</v>
-      </c>
-      <c r="J67">
-        <v>0.54330539703369141</v>
-      </c>
-      <c r="K67">
-        <v>0.29518076777458191</v>
-      </c>
-      <c r="L67">
-        <v>3.8417493049777269E-3</v>
-      </c>
-      <c r="M67">
-        <v>7.6834987848997116E-3</v>
-      </c>
-      <c r="N67">
-        <v>7.6171765263621793E-4</v>
-      </c>
-      <c r="O67">
-        <v>1222.6212578089151</v>
-      </c>
-      <c r="P67">
-        <v>70</v>
-      </c>
-      <c r="Q67">
-        <v>20000</v>
+      <c r="C67" s="5">
+        <v>412.23001098632813</v>
+      </c>
+      <c r="D67" s="5">
+        <v>2.3920819759368901</v>
+      </c>
+      <c r="E67" s="5">
+        <v>1.1644190180959411E-6</v>
+      </c>
+      <c r="F67" s="5">
+        <v>5.5512646213173866E-3</v>
+      </c>
+      <c r="G67" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" s="5">
+        <v>350</v>
+      </c>
+      <c r="I67" s="5">
+        <v>550</v>
+      </c>
+      <c r="J67" s="5">
+        <v>0.5442470908164978</v>
+      </c>
+      <c r="K67" s="5">
+        <v>0.29620492458343511</v>
+      </c>
+      <c r="L67" s="5">
+        <v>1.216973491622191E-3</v>
+      </c>
+      <c r="M67" s="5">
+        <v>2.433947054669261E-3</v>
+      </c>
+      <c r="N67" s="5">
+        <v>7.5170407231395231E-4</v>
+      </c>
+      <c r="O67" s="5">
+        <v>3.9611947633833799</v>
+      </c>
+      <c r="P67" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q67" s="6">
+        <v>200000</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67">
-        <f t="shared" ref="S67:S102" si="3">(N67/B67)*100</f>
-        <v>3.1853301971638104E-2</v>
+        <f t="shared" ref="S67:S102" si="2">(N67/B67)*100</f>
+        <v>3.1434556788671061E-2</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A68">
+      <c r="A68" s="4">
         <v>67</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="5">
         <v>2.237111438067684</v>
       </c>
-      <c r="C68">
-        <v>439.60955810546881</v>
-      </c>
-      <c r="D68">
-        <v>2.2350010871887211</v>
-      </c>
-      <c r="E68">
-        <f t="shared" si="2"/>
-        <v>4.4535808323391892E-6</v>
-      </c>
-      <c r="F68">
-        <v>4.909150768071413E-3</v>
-      </c>
-      <c r="G68" t="b">
-        <v>1</v>
-      </c>
-      <c r="H68">
-        <v>387.5</v>
-      </c>
-      <c r="I68">
-        <v>462.5</v>
-      </c>
-      <c r="J68">
-        <v>0.54306560754776001</v>
-      </c>
-      <c r="K68">
-        <v>0.29492026567459112</v>
-      </c>
-      <c r="L68">
-        <v>3.8400537372621341E-3</v>
-      </c>
-      <c r="M68">
-        <v>7.6801073737442493E-3</v>
-      </c>
-      <c r="N68">
-        <v>2.1103508789632741E-3</v>
-      </c>
-      <c r="O68">
-        <v>1605.3234229548329</v>
-      </c>
-      <c r="P68">
-        <v>70</v>
-      </c>
-      <c r="Q68">
-        <v>20000</v>
+      <c r="C68" s="5">
+        <v>439.60000610351563</v>
+      </c>
+      <c r="D68" s="5">
+        <v>2.2379336357116699</v>
+      </c>
+      <c r="E68" s="5">
+        <v>4.2837898945435882E-5</v>
+      </c>
+      <c r="F68" s="5">
+        <v>4.971642978489399E-3</v>
+      </c>
+      <c r="G68" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" s="5">
+        <v>350</v>
+      </c>
+      <c r="I68" s="5">
+        <v>550</v>
+      </c>
+      <c r="J68" s="5">
+        <v>0.54126918315887451</v>
+      </c>
+      <c r="K68" s="5">
+        <v>0.29297235608100891</v>
+      </c>
+      <c r="L68" s="5">
+        <v>1.2103146876690279E-3</v>
+      </c>
+      <c r="M68" s="5">
+        <v>2.4206293746829029E-3</v>
+      </c>
+      <c r="N68" s="5">
+        <v>8.2219764398594464E-4</v>
+      </c>
+      <c r="O68" s="5">
+        <v>10114.400379717819</v>
+      </c>
+      <c r="P68" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q68" s="6">
+        <v>200000</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68">
-        <f t="shared" si="3"/>
-        <v>9.4333739618536847E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.6752645844773918E-2</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A69">
+      <c r="A69" s="4">
         <v>68</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="5">
         <v>2.0880888840362379</v>
       </c>
-      <c r="C69">
-        <v>470.37222290039063</v>
-      </c>
-      <c r="D69">
-        <v>2.0926554203033452</v>
-      </c>
-      <c r="E69">
+      <c r="C69" s="5">
+        <v>470.20999145507813</v>
+      </c>
+      <c r="D69" s="5">
+        <v>2.0883610248565669</v>
+      </c>
+      <c r="E69" s="5">
+        <v>2.4536404907848919E-6</v>
+      </c>
+      <c r="F69" s="5">
+        <v>4.4020856730639926E-3</v>
+      </c>
+      <c r="G69" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H69" s="5">
+        <v>350</v>
+      </c>
+      <c r="I69" s="5">
+        <v>550</v>
+      </c>
+      <c r="J69" s="5">
+        <v>0.53947025537490845</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0.29102817177772522</v>
+      </c>
+      <c r="L69" s="5">
+        <v>1.1501544489847461E-3</v>
+      </c>
+      <c r="M69" s="5">
+        <v>2.3003090173006062E-3</v>
+      </c>
+      <c r="N69" s="5">
+        <v>2.7214082032944731E-4</v>
+      </c>
+      <c r="O69" s="5">
+        <v>2418.935564078341</v>
+      </c>
+      <c r="P69" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>220000</v>
+      </c>
+      <c r="R69" t="b">
+        <v>1</v>
+      </c>
+      <c r="S69">
         <f t="shared" si="2"/>
-        <v>2.0853253478805682E-5</v>
-      </c>
-      <c r="F69">
-        <v>4.2354296892881393E-3</v>
-      </c>
-      <c r="G69" t="b">
-        <v>1</v>
-      </c>
-      <c r="H69">
-        <v>437.5</v>
-      </c>
-      <c r="I69">
-        <v>512.5</v>
-      </c>
-      <c r="J69">
-        <v>0.54389458894729614</v>
-      </c>
-      <c r="K69">
-        <v>0.29582133889198298</v>
-      </c>
-      <c r="L69">
-        <v>3.8459155209530291E-3</v>
-      </c>
-      <c r="M69">
-        <v>7.691830862313509E-3</v>
-      </c>
-      <c r="N69">
-        <v>4.5665362671072351E-3</v>
-      </c>
-      <c r="O69">
-        <v>2135.741614379609</v>
-      </c>
-      <c r="P69">
-        <v>70</v>
-      </c>
-      <c r="Q69">
-        <v>20000</v>
-      </c>
-      <c r="R69" t="b">
-        <v>1</v>
-      </c>
-      <c r="S69">
-        <f t="shared" si="3"/>
-        <v>0.21869453460621863</v>
+        <v>1.3033009390069834E-2</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A70">
+      <c r="A70" s="4">
         <v>69</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="5">
         <v>1.9457000227727641</v>
       </c>
-      <c r="C70">
-        <v>504.11795043945313</v>
-      </c>
-      <c r="D70">
-        <v>1.9442896842956541</v>
-      </c>
-      <c r="E70">
+      <c r="C70" s="5">
+        <v>503.95999145507813</v>
+      </c>
+      <c r="D70" s="5">
+        <v>1.9455780982971189</v>
+      </c>
+      <c r="E70" s="5">
+        <v>1.688408701738808E-5</v>
+      </c>
+      <c r="F70" s="5">
+        <v>3.7427872885018591E-3</v>
+      </c>
+      <c r="G70" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" s="5">
+        <v>450</v>
+      </c>
+      <c r="I70" s="5">
+        <v>650</v>
+      </c>
+      <c r="J70" s="5">
+        <v>0.53915929794311523</v>
+      </c>
+      <c r="K70" s="5">
+        <v>0.29069274663925171</v>
+      </c>
+      <c r="L70" s="5">
+        <v>1.2055968409018681E-3</v>
+      </c>
+      <c r="M70" s="5">
+        <v>2.411193680018187E-3</v>
+      </c>
+      <c r="N70" s="5">
+        <v>1.2192447564451919E-4</v>
+      </c>
+      <c r="O70" s="5">
+        <v>17846.362778315081</v>
+      </c>
+      <c r="P70" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q70" s="6">
+        <v>200000</v>
+      </c>
+      <c r="R70" t="b">
+        <v>1</v>
+      </c>
+      <c r="S70">
         <f t="shared" si="2"/>
-        <v>1.9890546200170362E-6</v>
-      </c>
-      <c r="F70">
-        <v>3.8252212107181549E-3</v>
-      </c>
-      <c r="G70" t="b">
-        <v>1</v>
-      </c>
-      <c r="H70">
-        <v>487.5</v>
-      </c>
-      <c r="I70">
-        <v>562.5</v>
-      </c>
-      <c r="J70">
-        <v>0.53931951522827148</v>
-      </c>
-      <c r="K70">
-        <v>0.29086551070213318</v>
-      </c>
-      <c r="L70">
-        <v>3.813564864441522E-3</v>
-      </c>
-      <c r="M70">
-        <v>7.6271295547485352E-3</v>
-      </c>
-      <c r="N70">
-        <v>1.4103384771100291E-3</v>
-      </c>
-      <c r="O70">
-        <v>2723.5529688558731</v>
-      </c>
-      <c r="P70">
-        <v>70</v>
-      </c>
-      <c r="Q70">
-        <v>20000</v>
-      </c>
-      <c r="R70" t="b">
-        <v>1</v>
-      </c>
-      <c r="S70">
-        <f t="shared" si="3"/>
-        <v>7.2484887732087E-2</v>
+        <v>6.2663552560773446E-3</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
@@ -4824,14 +4789,14 @@
       <c r="B71">
         <v>1.8112030457153261</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="14">
         <v>540.6864013671875</v>
       </c>
       <c r="D71">
         <v>1.8118607997894289</v>
       </c>
       <c r="E71">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="E69:E102" si="3">(B71-D71)^2</f>
         <v>4.3264042199889138E-7</v>
       </c>
       <c r="F71">
@@ -4874,7 +4839,7 @@
         <v>1</v>
       </c>
       <c r="S71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.6315866167430412E-2</v>
       </c>
     </row>
@@ -4885,14 +4850,14 @@
       <c r="B72">
         <v>1.685670945847273</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="14">
         <v>580.4493408203125</v>
       </c>
       <c r="D72">
         <v>1.6866112947463989</v>
       </c>
       <c r="E72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.8425605208743432E-7</v>
       </c>
       <c r="F72">
@@ -4935,7 +4900,7 @@
         <v>1</v>
       </c>
       <c r="S72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.5784843503565627E-2</v>
       </c>
     </row>
@@ -4946,14 +4911,14 @@
       <c r="B73">
         <v>1.569994708318921</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="14">
         <v>622.60028076171875</v>
       </c>
       <c r="D73">
         <v>1.5696079730987551</v>
       </c>
       <c r="E73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.4956413051673382E-7</v>
       </c>
       <c r="F73">
@@ -4996,7 +4961,7 @@
         <v>1</v>
       </c>
       <c r="S73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.4632899596200256E-2</v>
       </c>
     </row>
@@ -5007,14 +4972,14 @@
       <c r="B74">
         <v>1.464894518558977</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="14">
         <v>666.988525390625</v>
       </c>
       <c r="D74">
         <v>1.467909097671509</v>
       </c>
       <c r="E74">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.0876872257142266E-6</v>
       </c>
       <c r="F74">
@@ -5057,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="S74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.20578813520971007</v>
       </c>
     </row>
@@ -5068,14 +5033,14 @@
       <c r="B75">
         <v>1.3709374080230179</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="14">
         <v>713.0126953125</v>
       </c>
       <c r="D75">
         <v>1.370973587036133</v>
       </c>
       <c r="E75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.308920989985845E-9</v>
       </c>
       <c r="F75">
@@ -5118,7 +5083,7 @@
         <v>1</v>
       </c>
       <c r="S75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.638998170390261E-3</v>
       </c>
     </row>
@@ -5129,14 +5094,14 @@
       <c r="B76">
         <v>1.2885595404939401</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="14">
         <v>757.803466796875</v>
       </c>
       <c r="D76">
         <v>1.28432309627533</v>
       </c>
       <c r="E76">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.7947459617394304E-5</v>
       </c>
       <c r="F76">
@@ -5179,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="S76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.32877364882854404</v>
       </c>
     </row>
@@ -5190,14 +5155,14 @@
       <c r="B77">
         <v>1.218091315853705</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="14">
         <v>803.16265869140625</v>
       </c>
       <c r="D77">
         <v>1.217975258827209</v>
       </c>
       <c r="E77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.3469233399087403E-8</v>
       </c>
       <c r="F77">
@@ -5240,7 +5205,7 @@
         <v>1</v>
       </c>
       <c r="S77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>9.5277771858975607E-3</v>
       </c>
     </row>
@@ -5251,14 +5216,14 @@
       <c r="B78">
         <v>1.159783590634661</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="14">
         <v>843.139892578125</v>
       </c>
       <c r="D78">
         <v>1.1640465259552</v>
       </c>
       <c r="E78">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.817261754709901E-5</v>
       </c>
       <c r="F78">
@@ -5301,7 +5266,7 @@
         <v>1</v>
       </c>
       <c r="S78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.36756299666269882</v>
       </c>
     </row>
@@ -5312,14 +5277,14 @@
       <c r="B79">
         <v>1.113833533176569</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="14">
         <v>878.2418212890625</v>
       </c>
       <c r="D79">
         <v>1.112043499946594</v>
       </c>
       <c r="E79">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.2042189644145599E-6</v>
       </c>
       <c r="F79">
@@ -5362,7 +5327,7 @@
         <v>1</v>
       </c>
       <c r="S79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.16070922419350533</v>
       </c>
     </row>
@@ -5373,14 +5338,14 @@
       <c r="B80">
         <v>1.0804088945786661</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="14">
         <v>905.79388427734375</v>
       </c>
       <c r="D80">
         <v>1.079329252243042</v>
       </c>
       <c r="E80">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1656275728718097E-6</v>
       </c>
       <c r="F80">
@@ -5423,7 +5388,7 @@
         <v>1</v>
       </c>
       <c r="S80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.25405908032896901</v>
       </c>
     </row>
@@ -5434,14 +5399,14 @@
       <c r="B81">
         <v>1.059669741704262</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="14">
         <v>924.84893798828125</v>
       </c>
       <c r="D81">
         <v>1.0567318201065059</v>
       </c>
       <c r="E81">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.6313833145616196E-6</v>
       </c>
       <c r="F81">
@@ -5484,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="S81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.2772487957456472</v>
       </c>
     </row>
@@ -5495,14 +5460,14 @@
       <c r="B82">
         <v>1.051786933968325</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="14">
         <v>930.06939697265625</v>
       </c>
       <c r="D82">
         <v>1.050126314163208</v>
       </c>
       <c r="E82">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.7576581371468327E-6</v>
       </c>
       <c r="F82">
@@ -5545,7 +5510,7 @@
         <v>1</v>
       </c>
       <c r="S82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.1578855708781067</v>
       </c>
     </row>
@@ -5556,14 +5521,14 @@
       <c r="B83">
         <v>1.056956812851094</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="14">
         <v>925.05218505859375</v>
       </c>
       <c r="D83">
         <v>1.057095050811768</v>
       </c>
       <c r="E83">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.910973377131351E-8</v>
       </c>
       <c r="F83">
@@ -5606,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="S83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1.3078865568827636E-2</v>
       </c>
     </row>
@@ -5617,14 +5582,14 @@
       <c r="B84">
         <v>1.0754117048643399</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="14">
         <v>910.02313232421875</v>
       </c>
       <c r="D84">
         <v>1.0754169225692749</v>
       </c>
       <c r="E84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.722444478873448E-11</v>
       </c>
       <c r="F84">
@@ -5667,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="S84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>4.8518208527954083E-4</v>
       </c>
     </row>
@@ -5678,14 +5643,14 @@
       <c r="B85">
         <v>1.107425917291978</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="14">
         <v>883.05816650390625</v>
       </c>
       <c r="D85">
         <v>1.109120845794678</v>
       </c>
       <c r="E85">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.8727826292645985E-6</v>
       </c>
       <c r="F85">
@@ -5728,7 +5693,7 @@
         <v>1</v>
       </c>
       <c r="S85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.15305118619984814</v>
       </c>
     </row>
@@ -5739,14 +5704,14 @@
       <c r="B86">
         <v>1.153316940821536</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="14">
         <v>848.11285400390625</v>
       </c>
       <c r="D86">
         <v>1.1526093482971189</v>
       </c>
       <c r="E86">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.0068718061096424E-7</v>
       </c>
       <c r="F86">
@@ -5789,7 +5754,7 @@
         <v>1</v>
       </c>
       <c r="S86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>6.1352825001691591E-2</v>
       </c>
     </row>
@@ -5800,14 +5765,14 @@
       <c r="B87">
         <v>1.2134415787506809</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="14">
         <v>805.17840576171875</v>
       </c>
       <c r="D87">
         <v>1.2129890918731689</v>
       </c>
       <c r="E87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.0474437432054313E-7</v>
       </c>
       <c r="F87">
@@ -5850,7 +5815,7 @@
         <v>1</v>
       </c>
       <c r="S87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.19686704170715899</v>
       </c>
     </row>
@@ -5861,14 +5826,14 @@
       <c r="B88">
         <v>1.288186717062378</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="14">
         <v>759.5911865234375</v>
       </c>
       <c r="D88">
         <v>1.28356409072876</v>
       </c>
       <c r="E88">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.1368674220258456E-5</v>
       </c>
       <c r="F88">
@@ -5911,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="S88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.35884753913314782</v>
       </c>
     </row>
@@ -5922,14 +5887,14 @@
       <c r="B89">
         <v>1.3779544541977089</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="14">
         <v>709.41546630859375</v>
       </c>
       <c r="D89">
         <v>1.375151634216309</v>
       </c>
       <c r="E89">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.8557998481343247E-6</v>
       </c>
       <c r="F89">
@@ -5972,7 +5937,7 @@
         <v>1</v>
       </c>
       <c r="S89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.20340439938797872</v>
       </c>
     </row>
@@ -5983,14 +5948,14 @@
       <c r="B90">
         <v>1.4831413464062131</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="14">
         <v>658.56390380859375</v>
       </c>
       <c r="D90">
         <v>1.4825431108474729</v>
       </c>
       <c r="E90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.578857837411607E-7</v>
       </c>
       <c r="F90">
@@ -6033,7 +5998,7 @@
         <v>1</v>
       </c>
       <c r="S90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>4.033570773207322E-2</v>
       </c>
     </row>
@@ -6044,14 +6009,14 @@
       <c r="B91">
         <v>1.60411161733039</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="14">
         <v>609.16339111328125</v>
       </c>
       <c r="D91">
         <v>1.605581402778625</v>
       </c>
       <c r="E91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.1602692638435405E-6</v>
       </c>
       <c r="F91">
@@ -6094,7 +6059,7 @@
         <v>1</v>
       </c>
       <c r="S91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>9.1626133266282397E-2</v>
       </c>
     </row>
@@ -6105,14 +6070,14 @@
       <c r="B92">
         <v>1.741164351173744</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="14">
         <v>561.83294677734375</v>
       </c>
       <c r="D92">
         <v>1.7451074123382571</v>
       </c>
       <c r="E92">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.5547731347090929E-5</v>
       </c>
       <c r="F92">
@@ -6155,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="S92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.22646117018505263</v>
       </c>
     </row>
@@ -6166,14 +6131,14 @@
       <c r="B93">
         <v>1.8944949560389981</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="14">
         <v>517.19720458984375</v>
       </c>
       <c r="D93">
         <v>1.89471447467804</v>
       </c>
       <c r="E93">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8188432886810005E-8</v>
       </c>
       <c r="F93">
@@ -6216,7 +6181,7 @@
         <v>1</v>
       </c>
       <c r="S93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1.1587185193719029E-2</v>
       </c>
     </row>
@@ -6227,14 +6192,14 @@
       <c r="B94">
         <v>2.0641515592264712</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="14">
         <v>475.73391723632813</v>
       </c>
       <c r="D94">
         <v>2.0646834373474121</v>
       </c>
       <c r="E94">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.8289433553563284E-7</v>
       </c>
       <c r="F94">
@@ -6277,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="S94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.5767396709022273E-2</v>
       </c>
     </row>
@@ -6288,14 +6253,14 @@
       <c r="B95">
         <v>2.2499874789877352</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="14">
         <v>437.32403564453119</v>
       </c>
       <c r="D95">
         <v>2.2502238750457759</v>
       </c>
       <c r="E95">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.5883096257187184E-8</v>
       </c>
       <c r="F95">
@@ -6338,7 +6303,7 @@
         <v>1</v>
       </c>
       <c r="S95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1.0506549936336051E-2</v>
       </c>
     </row>
@@ -6349,14 +6314,14 @@
       <c r="B96">
         <v>2.451611489865392</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="14">
         <v>402.53265380859381</v>
       </c>
       <c r="D96">
         <v>2.4533123970031738</v>
       </c>
       <c r="E96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.893085091357127E-6</v>
       </c>
       <c r="F96">
@@ -6399,7 +6364,7 @@
         <v>1</v>
       </c>
       <c r="S96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>6.9379146933073191E-2</v>
       </c>
     </row>
@@ -6410,14 +6375,14 @@
       <c r="B97">
         <v>2.668338221910707</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="14">
         <v>370.69317626953119</v>
       </c>
       <c r="D97">
         <v>2.6640868186950679</v>
       </c>
       <c r="E97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.8074429301946517E-5</v>
       </c>
       <c r="F97">
@@ -6460,7 +6425,7 @@
         <v>1</v>
       </c>
       <c r="S97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.15932774866127636</v>
       </c>
     </row>
@@ -6471,14 +6436,14 @@
       <c r="B98">
         <v>2.8991416438778361</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="14">
         <v>342.44683837890619</v>
       </c>
       <c r="D98">
         <v>2.8974988460540771</v>
       </c>
       <c r="E98">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.6987846897472378E-6</v>
       </c>
       <c r="F98">
@@ -6521,7 +6486,7 @@
         <v>1</v>
       </c>
       <c r="S98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6664972793849432E-2</v>
       </c>
     </row>
@@ -6532,14 +6497,14 @@
       <c r="B99">
         <v>3.1426150900261072</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="14">
         <v>317.7115478515625</v>
       </c>
       <c r="D99">
         <v>3.148351669311523</v>
       </c>
       <c r="E99">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.29083418978619E-5</v>
       </c>
       <c r="F99">
@@ -6582,7 +6547,7 @@
         <v>1</v>
       </c>
       <c r="S99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.18254158148806601</v>
       </c>
     </row>
@@ -6593,14 +6558,14 @@
       <c r="B100">
         <v>3.396941596840962</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="14">
         <v>295.99356079101563</v>
       </c>
       <c r="D100">
         <v>3.395908117294312</v>
       </c>
       <c r="E100">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0680799733439037E-6</v>
       </c>
       <c r="F100">
@@ -6643,7 +6608,7 @@
         <v>0</v>
       </c>
       <c r="S100">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.0423824407552577E-2</v>
       </c>
     </row>
@@ -6654,14 +6619,14 @@
       <c r="B101">
         <v>3.65987831595602</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="14">
         <v>277.44094848632813</v>
       </c>
       <c r="D101">
         <v>3.663387537002563</v>
       </c>
       <c r="E101">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.2314632353500727E-5</v>
       </c>
       <c r="F101">
@@ -6704,7 +6669,7 @@
         <v>0</v>
       </c>
       <c r="S101">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>9.5883544303629317E-2</v>
       </c>
     </row>
@@ -6715,14 +6680,14 @@
       <c r="B102">
         <v>3.9287583783681899</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="14">
         <v>262.08700561523438</v>
       </c>
       <c r="D102">
         <v>3.9297914505004878</v>
       </c>
       <c r="E102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0672380305306829E-6</v>
       </c>
       <c r="F102">
@@ -6765,14 +6730,14 @@
         <v>0</v>
       </c>
       <c r="S102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.6295130237229319E-2</v>
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="S103">
         <f>AVERAGE(S2:S102)</f>
-        <v>0.12658869538656098</v>
+        <v>8.9664837333458189E-2</v>
       </c>
     </row>
   </sheetData>

--- a/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix.xlsx
+++ b/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49926716-DE25-4D19-84C9-446F0DE71A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D4D485-FD28-483A-8954-B4ED99DFD04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4783,125 +4783,123 @@
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A71">
+      <c r="A71" s="4">
         <v>70</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="5">
         <v>1.8112030457153261</v>
       </c>
-      <c r="C71" s="14">
-        <v>540.6864013671875</v>
-      </c>
-      <c r="D71">
-        <v>1.8118607997894289</v>
-      </c>
-      <c r="E71">
-        <f t="shared" ref="E69:E102" si="3">(B71-D71)^2</f>
-        <v>4.3264042199889138E-7</v>
-      </c>
-      <c r="F71">
-        <v>3.368385368958116E-3</v>
-      </c>
-      <c r="G71" t="b">
-        <v>1</v>
-      </c>
-      <c r="H71">
-        <v>487.5</v>
-      </c>
-      <c r="I71">
-        <v>562.5</v>
-      </c>
-      <c r="J71">
-        <v>0.53773772716522217</v>
-      </c>
-      <c r="K71">
-        <v>0.28916186094284058</v>
-      </c>
-      <c r="L71">
-        <v>3.8023799337837008E-3</v>
-      </c>
-      <c r="M71">
-        <v>7.6047596521675587E-3</v>
-      </c>
-      <c r="N71">
-        <v>6.5775407410240128E-4</v>
-      </c>
-      <c r="O71">
-        <v>3569.3414662619512</v>
-      </c>
-      <c r="P71">
-        <v>70</v>
-      </c>
-      <c r="Q71">
-        <v>20000</v>
+      <c r="C71" s="5">
+        <v>540.70001220703125</v>
+      </c>
+      <c r="D71" s="5">
+        <v>1.810828328132629</v>
+      </c>
+      <c r="E71" s="5">
+        <v>1.9454660105111539E-9</v>
+      </c>
+      <c r="F71" s="5">
+        <v>3.306543687358499E-3</v>
+      </c>
+      <c r="G71" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" s="5">
+        <v>450</v>
+      </c>
+      <c r="I71" s="5">
+        <v>650</v>
+      </c>
+      <c r="J71" s="5">
+        <v>0.53949302434921265</v>
+      </c>
+      <c r="K71" s="5">
+        <v>0.29105272889137268</v>
+      </c>
+      <c r="L71" s="5">
+        <v>7.4814221617162642E-4</v>
+      </c>
+      <c r="M71" s="5">
+        <v>1.496284501627088E-3</v>
+      </c>
+      <c r="N71" s="5">
+        <v>3.7471758269691508E-4</v>
+      </c>
+      <c r="O71" s="5">
+        <v>11433.033676115991</v>
+      </c>
+      <c r="P71" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>520000</v>
       </c>
       <c r="R71" t="b">
         <v>1</v>
       </c>
       <c r="S71">
         <f t="shared" si="2"/>
-        <v>3.6315866167430412E-2</v>
+        <v>2.0688877681790899E-2</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A72">
+      <c r="A72" s="4">
         <v>71</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="5">
         <v>1.685670945847273</v>
       </c>
-      <c r="C72" s="14">
-        <v>580.4493408203125</v>
-      </c>
-      <c r="D72">
-        <v>1.6866112947463989</v>
-      </c>
-      <c r="E72">
-        <f t="shared" si="3"/>
-        <v>8.8425605208743432E-7</v>
-      </c>
-      <c r="F72">
-        <v>2.8544520027935501E-3</v>
-      </c>
-      <c r="G72" t="b">
-        <v>1</v>
-      </c>
-      <c r="H72">
-        <v>537.5</v>
-      </c>
-      <c r="I72">
-        <v>612.5</v>
-      </c>
-      <c r="J72">
-        <v>0.53801071643829346</v>
-      </c>
-      <c r="K72">
-        <v>0.28945553302764893</v>
-      </c>
-      <c r="L72">
-        <v>3.8043102594454998E-3</v>
-      </c>
-      <c r="M72">
-        <v>7.6086204499006271E-3</v>
-      </c>
-      <c r="N72">
-        <v>9.4034889912597563E-4</v>
-      </c>
-      <c r="O72">
-        <v>4862.6812418954169</v>
-      </c>
-      <c r="P72">
-        <v>70</v>
-      </c>
-      <c r="Q72">
-        <v>20000</v>
+      <c r="C72" s="5">
+        <v>580.20001220703125</v>
+      </c>
+      <c r="D72" s="5">
+        <v>1.686196565628052</v>
+      </c>
+      <c r="E72" s="5">
+        <v>1.790922965483333E-7</v>
+      </c>
+      <c r="F72" s="5">
+        <v>2.928940579295158E-3</v>
+      </c>
+      <c r="G72" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" s="5">
+        <v>450</v>
+      </c>
+      <c r="I72" s="5">
+        <v>650</v>
+      </c>
+      <c r="J72" s="5">
+        <v>0.53905421495437622</v>
+      </c>
+      <c r="K72" s="5">
+        <v>0.29057943820953369</v>
+      </c>
+      <c r="L72" s="5">
+        <v>8.9842369159062708E-4</v>
+      </c>
+      <c r="M72" s="5">
+        <v>1.7968473257496951E-3</v>
+      </c>
+      <c r="N72" s="5">
+        <v>5.2561978077836358E-4</v>
+      </c>
+      <c r="O72" s="5">
+        <v>227.67163003585921</v>
+      </c>
+      <c r="P72" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q72" s="6">
+        <v>360000</v>
       </c>
       <c r="R72" t="b">
         <v>1</v>
       </c>
       <c r="S72">
-        <f t="shared" si="2"/>
-        <v>5.5784843503565627E-2</v>
+        <f>(N72/B72)*100</f>
+        <v>3.1181636135643898E-2</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
@@ -4918,7 +4916,7 @@
         <v>1.5696079730987551</v>
       </c>
       <c r="E73">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E73:E102" si="3">(B73-D73)^2</f>
         <v>1.4956413051673382E-7</v>
       </c>
       <c r="F73">
@@ -4966,64 +4964,63 @@
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A74">
+      <c r="A74" s="4">
         <v>73</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="5">
         <v>1.464894518558977</v>
       </c>
-      <c r="C74" s="14">
-        <v>666.988525390625</v>
-      </c>
-      <c r="D74">
-        <v>1.467909097671509</v>
-      </c>
-      <c r="E74">
-        <f t="shared" si="3"/>
-        <v>9.0876872257142266E-6</v>
-      </c>
-      <c r="F74">
-        <v>2.236041240394115E-3</v>
-      </c>
-      <c r="G74" t="b">
-        <v>1</v>
-      </c>
-      <c r="H74">
-        <v>637.5</v>
-      </c>
-      <c r="I74">
-        <v>712.5</v>
-      </c>
-      <c r="J74">
-        <v>0.54003262519836426</v>
-      </c>
-      <c r="K74">
-        <v>0.29163524508476257</v>
-      </c>
-      <c r="L74">
-        <v>3.8186073133973661E-3</v>
-      </c>
-      <c r="M74">
-        <v>7.6372148469090462E-3</v>
-      </c>
-      <c r="N74">
-        <v>3.0145791125317789E-3</v>
-      </c>
-      <c r="O74">
-        <v>8219.6179559373759</v>
-      </c>
-      <c r="P74">
-        <v>70</v>
-      </c>
-      <c r="Q74">
-        <v>20000</v>
+      <c r="C74" s="5">
+        <v>667.0999755859375</v>
+      </c>
+      <c r="D74" s="5">
+        <v>1.464526891708374</v>
+      </c>
+      <c r="E74" s="5">
+        <v>3.0004832751728832E-7</v>
+      </c>
+      <c r="F74" s="5">
+        <v>2.1619985345751051E-3</v>
+      </c>
+      <c r="G74" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" s="5">
+        <v>550</v>
+      </c>
+      <c r="I74" s="5">
+        <v>750</v>
+      </c>
+      <c r="J74" s="5">
+        <v>0.54070091247558594</v>
+      </c>
+      <c r="K74" s="5">
+        <v>0.29235747456550598</v>
+      </c>
+      <c r="L74" s="5">
+        <v>6.5569616882490901E-4</v>
+      </c>
+      <c r="M74" s="5">
+        <v>1.311392290517688E-3</v>
+      </c>
+      <c r="N74" s="5">
+        <v>3.6762685060298672E-4</v>
+      </c>
+      <c r="O74" s="5">
+        <v>40113.493043784641</v>
+      </c>
+      <c r="P74" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q74" s="6">
+        <v>680000</v>
       </c>
       <c r="R74" t="b">
         <v>1</v>
       </c>
       <c r="S74">
         <f t="shared" si="2"/>
-        <v>0.20578813520971007</v>
+        <v>2.5095789897870795E-2</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
@@ -5088,64 +5085,63 @@
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A76">
+      <c r="A76" s="4">
         <v>75</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="5">
         <v>1.2885595404939401</v>
       </c>
-      <c r="C76" s="14">
-        <v>757.803466796875</v>
-      </c>
-      <c r="D76">
-        <v>1.28432309627533</v>
-      </c>
-      <c r="E76">
-        <f t="shared" si="3"/>
-        <v>1.7947459617394304E-5</v>
-      </c>
-      <c r="F76">
-        <v>1.793277799151838E-3</v>
-      </c>
-      <c r="G76" t="b">
-        <v>0</v>
-      </c>
-      <c r="H76">
-        <v>737.5</v>
-      </c>
-      <c r="I76">
-        <v>812.5</v>
-      </c>
-      <c r="J76">
-        <v>0.5430106520652771</v>
-      </c>
-      <c r="K76">
-        <v>0.29486054182052612</v>
-      </c>
-      <c r="L76">
-        <v>3.8396651433188641E-3</v>
-      </c>
-      <c r="M76">
-        <v>7.6793301850557327E-3</v>
-      </c>
-      <c r="N76">
-        <v>4.2364442186102469E-3</v>
-      </c>
-      <c r="O76">
-        <v>47.641607365220523</v>
-      </c>
-      <c r="P76">
-        <v>70</v>
-      </c>
-      <c r="Q76">
-        <v>20000</v>
+      <c r="C76" s="5">
+        <v>758.29998779296875</v>
+      </c>
+      <c r="D76" s="5">
+        <v>1.287978053092957</v>
+      </c>
+      <c r="E76" s="5">
+        <v>9.0268628127887496E-7</v>
+      </c>
+      <c r="F76" s="5">
+        <v>1.749545917846262E-3</v>
+      </c>
+      <c r="G76" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" s="5">
+        <v>650</v>
+      </c>
+      <c r="I76" s="5">
+        <v>850</v>
+      </c>
+      <c r="J76" s="5">
+        <v>0.54204308986663818</v>
+      </c>
+      <c r="K76" s="5">
+        <v>0.29381069540977478</v>
+      </c>
+      <c r="L76" s="5">
+        <v>9.2959622998402226E-4</v>
+      </c>
+      <c r="M76" s="5">
+        <v>1.859192387200892E-3</v>
+      </c>
+      <c r="N76" s="5">
+        <v>5.8148740098329377E-4</v>
+      </c>
+      <c r="O76" s="5">
+        <v>61256.274678696478</v>
+      </c>
+      <c r="P76" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>340000</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
       </c>
       <c r="S76">
         <f t="shared" si="2"/>
-        <v>0.32877364882854404</v>
+        <v>4.5126933037210971E-2</v>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
@@ -5210,369 +5206,363 @@
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78">
+      <c r="A78" s="4">
         <v>77</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="5">
         <v>1.159783590634661</v>
       </c>
-      <c r="C78" s="14">
-        <v>843.139892578125</v>
-      </c>
-      <c r="D78">
-        <v>1.1640465259552</v>
-      </c>
-      <c r="E78">
-        <f t="shared" si="3"/>
-        <v>1.817261754709901E-5</v>
-      </c>
-      <c r="F78">
-        <v>1.4033177867531781E-3</v>
-      </c>
-      <c r="G78" t="b">
-        <v>1</v>
-      </c>
-      <c r="H78">
-        <v>818.75</v>
-      </c>
-      <c r="I78">
-        <v>856.25</v>
-      </c>
-      <c r="J78">
-        <v>0.54476481676101685</v>
-      </c>
-      <c r="K78">
-        <v>0.29676872491836548</v>
-      </c>
-      <c r="L78">
-        <v>3.85206896083562E-3</v>
-      </c>
-      <c r="M78">
-        <v>7.7041378244757652E-3</v>
-      </c>
-      <c r="N78">
-        <v>4.2629353205390075E-3</v>
-      </c>
-      <c r="O78">
-        <v>20894.60665468204</v>
-      </c>
-      <c r="P78">
-        <v>70</v>
-      </c>
-      <c r="Q78">
-        <v>20000</v>
+      <c r="C78" s="5">
+        <v>842.70001220703125</v>
+      </c>
+      <c r="D78" s="5">
+        <v>1.1590327024459841</v>
+      </c>
+      <c r="E78" s="5">
+        <v>4.723009396911948E-7</v>
+      </c>
+      <c r="F78" s="5">
+        <v>1.4161261497065421E-3</v>
+      </c>
+      <c r="G78" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" s="5">
+        <v>750</v>
+      </c>
+      <c r="I78" s="5">
+        <v>950</v>
+      </c>
+      <c r="J78" s="5">
+        <v>0.543232262134552</v>
+      </c>
+      <c r="K78" s="5">
+        <v>0.29510128498077393</v>
+      </c>
+      <c r="L78" s="5">
+        <v>9.9180187978551207E-4</v>
+      </c>
+      <c r="M78" s="5">
+        <v>1.983603928238153E-3</v>
+      </c>
+      <c r="N78" s="5">
+        <v>7.5088818867707907E-4</v>
+      </c>
+      <c r="O78" s="5">
+        <v>62331.2918851137</v>
+      </c>
+      <c r="P78" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q78" s="6">
+        <v>300000</v>
       </c>
       <c r="R78" t="b">
         <v>1</v>
       </c>
       <c r="S78">
         <f t="shared" si="2"/>
-        <v>0.36756299666269882</v>
+        <v>6.4743818996971264E-2</v>
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A79">
+      <c r="A79" s="4">
         <v>78</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="5">
         <v>1.113833533176569</v>
       </c>
-      <c r="C79" s="14">
-        <v>878.2418212890625</v>
-      </c>
-      <c r="D79">
-        <v>1.112043499946594</v>
-      </c>
-      <c r="E79">
-        <f t="shared" si="3"/>
-        <v>3.2042189644145599E-6</v>
-      </c>
-      <c r="F79">
-        <v>1.2902793241664769E-3</v>
-      </c>
-      <c r="G79" t="b">
-        <v>1</v>
-      </c>
-      <c r="H79">
-        <v>868.75</v>
-      </c>
-      <c r="I79">
-        <v>906.25</v>
-      </c>
-      <c r="J79">
-        <v>0.54646950960159302</v>
-      </c>
-      <c r="K79">
-        <v>0.29862892627716059</v>
-      </c>
-      <c r="L79">
-        <v>3.8641229595097349E-3</v>
-      </c>
-      <c r="M79">
-        <v>7.7282460406422624E-3</v>
-      </c>
-      <c r="N79">
-        <v>1.790033229975174E-3</v>
-      </c>
-      <c r="O79">
-        <v>19711.05278115426</v>
-      </c>
-      <c r="P79">
-        <v>80</v>
-      </c>
-      <c r="Q79">
-        <v>20000</v>
+      <c r="C79" s="5">
+        <v>877.9000244140625</v>
+      </c>
+      <c r="D79" s="5">
+        <v>1.114607572555542</v>
+      </c>
+      <c r="E79" s="5">
+        <v>1.0738363016571381E-5</v>
+      </c>
+      <c r="F79" s="5">
+        <v>1.2568847741931679E-3</v>
+      </c>
+      <c r="G79" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" s="5">
+        <v>750</v>
+      </c>
+      <c r="I79" s="5">
+        <v>950</v>
+      </c>
+      <c r="J79" s="5">
+        <v>0.54423987865447998</v>
+      </c>
+      <c r="K79" s="5">
+        <v>0.29619705677032471</v>
+      </c>
+      <c r="L79" s="5">
+        <v>1.1603233199842561E-3</v>
+      </c>
+      <c r="M79" s="5">
+        <v>2.3206467740237709E-3</v>
+      </c>
+      <c r="N79" s="5">
+        <v>7.7403937897257968E-4</v>
+      </c>
+      <c r="O79" s="5">
+        <v>118688.9646890117</v>
+      </c>
+      <c r="P79" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q79" s="6">
+        <v>220000</v>
       </c>
       <c r="R79" t="b">
         <v>1</v>
       </c>
       <c r="S79">
         <f t="shared" si="2"/>
-        <v>0.16070922419350533</v>
+        <v>6.9493273089478461E-2</v>
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A80">
+      <c r="A80" s="4">
         <v>79</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="5">
         <v>1.0804088945786661</v>
       </c>
-      <c r="C80" s="14">
-        <v>905.79388427734375</v>
-      </c>
-      <c r="D80">
-        <v>1.079329252243042</v>
-      </c>
-      <c r="E80">
-        <f t="shared" si="3"/>
-        <v>1.1656275728718097E-6</v>
-      </c>
-      <c r="F80">
-        <v>1.1961624259129171E-3</v>
-      </c>
-      <c r="G80" t="b">
-        <v>1</v>
-      </c>
-      <c r="H80">
-        <v>893.75</v>
-      </c>
-      <c r="I80">
-        <v>931.25</v>
-      </c>
-      <c r="J80">
-        <v>0.54633551836013794</v>
-      </c>
-      <c r="K80">
-        <v>0.29848247766494751</v>
-      </c>
-      <c r="L80">
-        <v>3.8631754983552112E-3</v>
-      </c>
-      <c r="M80">
-        <v>7.726350799202919E-3</v>
-      </c>
-      <c r="N80">
-        <v>2.7448769013589391E-3</v>
-      </c>
-      <c r="O80">
-        <v>669.90731859745927</v>
-      </c>
-      <c r="P80">
-        <v>70</v>
-      </c>
-      <c r="Q80">
-        <v>20000</v>
+      <c r="C80" s="5">
+        <v>907</v>
+      </c>
+      <c r="D80" s="5">
+        <v>1.0803041458129881</v>
+      </c>
+      <c r="E80" s="5">
+        <v>8.1581902122707106E-8</v>
+      </c>
+      <c r="F80" s="5">
+        <v>1.2549993116408591E-3</v>
+      </c>
+      <c r="G80" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" s="5">
+        <v>850</v>
+      </c>
+      <c r="I80" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J80" s="5">
+        <v>0.54448181390762329</v>
+      </c>
+      <c r="K80" s="5">
+        <v>0.29646044969558721</v>
+      </c>
+      <c r="L80" s="5">
+        <v>9.6251695711708064E-4</v>
+      </c>
+      <c r="M80" s="5">
+        <v>1.925033866427839E-3</v>
+      </c>
+      <c r="N80" s="5">
+        <v>1.0474876567778681E-4</v>
+      </c>
+      <c r="O80" s="5">
+        <v>79363.90668303534</v>
+      </c>
+      <c r="P80" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q80" s="6">
+        <v>320000</v>
       </c>
       <c r="R80" t="b">
         <v>1</v>
       </c>
       <c r="S80">
         <f t="shared" si="2"/>
-        <v>0.25405908032896901</v>
+        <v>9.695289089473513E-3</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A81">
+      <c r="A81" s="4">
         <v>80</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="5">
         <v>1.059669741704262</v>
       </c>
-      <c r="C81" s="14">
-        <v>924.84893798828125</v>
-      </c>
-      <c r="D81">
-        <v>1.0567318201065059</v>
-      </c>
-      <c r="E81">
-        <f t="shared" si="3"/>
-        <v>8.6313833145616196E-6</v>
-      </c>
-      <c r="F81">
-        <v>1.0263194562867279E-3</v>
-      </c>
-      <c r="G81" t="b">
-        <v>1</v>
-      </c>
-      <c r="H81">
-        <v>918.75</v>
-      </c>
-      <c r="I81">
-        <v>956.25</v>
-      </c>
-      <c r="J81">
-        <v>0.54913276433944702</v>
-      </c>
-      <c r="K81">
-        <v>0.30154681205749512</v>
-      </c>
-      <c r="L81">
-        <v>3.8829550143613732E-3</v>
-      </c>
-      <c r="M81">
-        <v>7.7659101225435734E-3</v>
-      </c>
-      <c r="N81">
-        <v>2.9379215977560769E-3</v>
-      </c>
-      <c r="O81">
-        <v>34223.192511983551</v>
-      </c>
-      <c r="P81">
-        <v>70</v>
-      </c>
-      <c r="Q81">
-        <v>20000</v>
+      <c r="C81" s="5">
+        <v>924.20001220703125</v>
+      </c>
+      <c r="D81" s="5">
+        <v>1.0601015090942381</v>
+      </c>
+      <c r="E81" s="5">
+        <v>1.864305545495881E-7</v>
+      </c>
+      <c r="F81" s="5">
+        <v>1.152220065705478E-3</v>
+      </c>
+      <c r="G81" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" s="5">
+        <v>850</v>
+      </c>
+      <c r="I81" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J81" s="5">
+        <v>0.54567134380340576</v>
+      </c>
+      <c r="K81" s="5">
+        <v>0.29775723814964289</v>
+      </c>
+      <c r="L81" s="5">
+        <v>9.6461976875641042E-4</v>
+      </c>
+      <c r="M81" s="5">
+        <v>1.9292394863441591E-3</v>
+      </c>
+      <c r="N81" s="5">
+        <v>4.3176738997630082E-4</v>
+      </c>
+      <c r="O81" s="5">
+        <v>94154.080137295168</v>
+      </c>
+      <c r="P81" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q81" s="6">
+        <v>320000</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
       </c>
       <c r="S81">
         <f t="shared" si="2"/>
-        <v>0.2772487957456472</v>
+        <v>4.0745467477621027E-2</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A82">
+      <c r="A82" s="4">
         <v>81</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="5">
         <v>1.051786933968325</v>
       </c>
-      <c r="C82" s="14">
-        <v>930.06939697265625</v>
-      </c>
-      <c r="D82">
-        <v>1.050126314163208</v>
-      </c>
-      <c r="E82">
-        <f t="shared" si="3"/>
-        <v>2.7576581371468327E-6</v>
-      </c>
-      <c r="F82">
-        <v>1.12149165943265E-3</v>
-      </c>
-      <c r="G82" t="b">
-        <v>1</v>
-      </c>
-      <c r="H82">
-        <v>918.75</v>
-      </c>
-      <c r="I82">
-        <v>956.25</v>
-      </c>
-      <c r="J82">
-        <v>0.54532283544540405</v>
-      </c>
-      <c r="K82">
-        <v>0.29737699031829828</v>
-      </c>
-      <c r="L82">
-        <v>3.8560147487932098E-3</v>
-      </c>
-      <c r="M82">
-        <v>7.7120293863117686E-3</v>
-      </c>
-      <c r="N82">
-        <v>1.660619805117225E-3</v>
-      </c>
-      <c r="O82">
-        <v>39737.685786778638</v>
-      </c>
-      <c r="P82">
-        <v>60</v>
-      </c>
-      <c r="Q82">
-        <v>20000</v>
+      <c r="C82" s="5">
+        <v>931.4000244140625</v>
+      </c>
+      <c r="D82" s="5">
+        <v>1.052038192749023</v>
+      </c>
+      <c r="E82" s="5">
+        <v>7.7919403338455595E-6</v>
+      </c>
+      <c r="F82" s="5">
+        <v>1.122568035498261E-3</v>
+      </c>
+      <c r="G82" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" s="5">
+        <v>850</v>
+      </c>
+      <c r="I82" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J82" s="5">
+        <v>0.54423952102661133</v>
+      </c>
+      <c r="K82" s="5">
+        <v>0.29619666934013372</v>
+      </c>
+      <c r="L82" s="5">
+        <v>8.204719487854581E-4</v>
+      </c>
+      <c r="M82" s="5">
+        <v>1.640943926759064E-3</v>
+      </c>
+      <c r="N82" s="5">
+        <v>2.5125878069820468E-4</v>
+      </c>
+      <c r="O82" s="5">
+        <v>74395.374252285023</v>
+      </c>
+      <c r="P82" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q82" s="6">
+        <v>440000</v>
       </c>
       <c r="R82" t="b">
         <v>1</v>
       </c>
       <c r="S82">
         <f t="shared" si="2"/>
-        <v>0.1578855708781067</v>
+        <v>2.3888752805686728E-2</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A83">
+      <c r="A83" s="4">
         <v>82</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="5">
         <v>1.056956812851094</v>
       </c>
-      <c r="C83" s="14">
-        <v>925.05218505859375</v>
-      </c>
-      <c r="D83">
-        <v>1.057095050811768</v>
-      </c>
-      <c r="E83">
-        <f t="shared" si="3"/>
-        <v>1.910973377131351E-8</v>
-      </c>
-      <c r="F83">
-        <v>1.2383922003209591E-3</v>
-      </c>
-      <c r="G83" t="b">
-        <v>1</v>
-      </c>
-      <c r="H83">
-        <v>918.75</v>
-      </c>
-      <c r="I83">
-        <v>956.25</v>
-      </c>
-      <c r="J83">
-        <v>0.54484963417053223</v>
-      </c>
-      <c r="K83">
-        <v>0.29686114192008972</v>
-      </c>
-      <c r="L83">
-        <v>3.85266871048993E-3</v>
-      </c>
-      <c r="M83">
-        <v>7.70533736795187E-3</v>
-      </c>
-      <c r="N83">
-        <v>1.3823796067335969E-4</v>
-      </c>
-      <c r="O83">
-        <v>35635.38615767243</v>
-      </c>
-      <c r="P83">
-        <v>60</v>
-      </c>
-      <c r="Q83">
-        <v>20000</v>
+      <c r="C83" s="5">
+        <v>926.29998779296875</v>
+      </c>
+      <c r="D83" s="5">
+        <v>1.056923031806946</v>
+      </c>
+      <c r="E83" s="5">
+        <v>3.1936065170157239E-6</v>
+      </c>
+      <c r="F83" s="5">
+        <v>1.1722173076122999E-3</v>
+      </c>
+      <c r="G83" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" s="5">
+        <v>850</v>
+      </c>
+      <c r="I83" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J83" s="5">
+        <v>0.5441935658454895</v>
+      </c>
+      <c r="K83" s="5">
+        <v>0.29614666104316711</v>
+      </c>
+      <c r="L83" s="5">
+        <v>2.2216609293785479E-3</v>
+      </c>
+      <c r="M83" s="5">
+        <v>4.443321842700243E-3</v>
+      </c>
+      <c r="N83" s="5">
+        <v>3.3781044148417649E-5</v>
+      </c>
+      <c r="O83" s="5">
+        <v>17056.70060169026</v>
+      </c>
+      <c r="P83" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="6">
+        <v>60000</v>
       </c>
       <c r="R83" t="b">
         <v>1</v>
       </c>
       <c r="S83">
         <f t="shared" si="2"/>
-        <v>1.3078865568827636E-2</v>
+        <v>3.19606664507841E-3</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
@@ -5637,308 +5627,303 @@
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A85">
+      <c r="A85" s="4">
         <v>84</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="5">
         <v>1.107425917291978</v>
       </c>
-      <c r="C85" s="14">
-        <v>883.05816650390625</v>
-      </c>
-      <c r="D85">
-        <v>1.109120845794678</v>
-      </c>
-      <c r="E85">
-        <f t="shared" si="3"/>
-        <v>2.8727826292645985E-6</v>
-      </c>
-      <c r="F85">
-        <v>1.340210204944015E-3</v>
-      </c>
-      <c r="G85" t="b">
-        <v>1</v>
-      </c>
-      <c r="H85">
-        <v>868.75</v>
-      </c>
-      <c r="I85">
-        <v>906.25</v>
-      </c>
-      <c r="J85">
-        <v>0.54369378089904785</v>
-      </c>
-      <c r="K85">
-        <v>0.295602947473526</v>
-      </c>
-      <c r="L85">
-        <v>3.8444955936266971E-3</v>
-      </c>
-      <c r="M85">
-        <v>7.6889912597835064E-3</v>
-      </c>
-      <c r="N85">
-        <v>1.6949285026999217E-3</v>
-      </c>
-      <c r="O85">
-        <v>29995.207830151801</v>
-      </c>
-      <c r="P85">
-        <v>60</v>
-      </c>
-      <c r="Q85">
-        <v>20000</v>
+      <c r="C85" s="5">
+        <v>883.79998779296875</v>
+      </c>
+      <c r="D85" s="5">
+        <v>1.107108592987061</v>
+      </c>
+      <c r="E85" s="5">
+        <v>9.9818325907108374E-6</v>
+      </c>
+      <c r="F85" s="5">
+        <v>1.278836745768785E-3</v>
+      </c>
+      <c r="G85" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" s="5">
+        <v>750</v>
+      </c>
+      <c r="I85" s="5">
+        <v>950</v>
+      </c>
+      <c r="J85" s="5">
+        <v>0.54434406757354736</v>
+      </c>
+      <c r="K85" s="5">
+        <v>0.29631048440933228</v>
+      </c>
+      <c r="L85" s="5">
+        <v>9.9383174951382766E-4</v>
+      </c>
+      <c r="M85" s="5">
+        <v>1.9876635633409019E-3</v>
+      </c>
+      <c r="N85" s="5">
+        <v>3.1732430491704378E-4</v>
+      </c>
+      <c r="O85" s="5">
+        <v>152865.61057322571</v>
+      </c>
+      <c r="P85" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q85" s="6">
+        <v>300000</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
       </c>
       <c r="S85">
         <f t="shared" si="2"/>
-        <v>0.15305118619984814</v>
+        <v>2.8654224175374769E-2</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A86">
+      <c r="A86" s="4">
         <v>85</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="5">
         <v>1.153316940821536</v>
       </c>
-      <c r="C86" s="14">
-        <v>848.11285400390625</v>
-      </c>
-      <c r="D86">
-        <v>1.1526093482971189</v>
-      </c>
-      <c r="E86">
-        <f t="shared" si="3"/>
-        <v>5.0068718061096424E-7</v>
-      </c>
-      <c r="F86">
-        <v>1.31747021805495E-3</v>
-      </c>
-      <c r="G86" t="b">
-        <v>1</v>
-      </c>
-      <c r="H86">
-        <v>818.75</v>
-      </c>
-      <c r="I86">
-        <v>856.25</v>
-      </c>
-      <c r="J86">
-        <v>0.54546272754669189</v>
-      </c>
-      <c r="K86">
-        <v>0.29752957820892328</v>
-      </c>
-      <c r="L86">
-        <v>3.85700393532776E-3</v>
-      </c>
-      <c r="M86">
-        <v>7.7140079811215401E-3</v>
-      </c>
-      <c r="N86">
-        <v>7.0759252441709997E-4</v>
-      </c>
-      <c r="O86">
-        <v>22506.398279807439</v>
-      </c>
-      <c r="P86">
-        <v>70</v>
-      </c>
-      <c r="Q86">
-        <v>20000</v>
+      <c r="C86" s="5">
+        <v>848.5999755859375</v>
+      </c>
+      <c r="D86" s="5">
+        <v>1.15399181842804</v>
+      </c>
+      <c r="E86" s="5">
+        <v>6.370066330418922E-6</v>
+      </c>
+      <c r="F86" s="5">
+        <v>1.344336313195527E-3</v>
+      </c>
+      <c r="G86" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" s="5">
+        <v>750</v>
+      </c>
+      <c r="I86" s="5">
+        <v>950</v>
+      </c>
+      <c r="J86" s="5">
+        <v>0.54306060075759888</v>
+      </c>
+      <c r="K86" s="5">
+        <v>0.29491481184959412</v>
+      </c>
+      <c r="L86" s="5">
+        <v>1.065029461664007E-3</v>
+      </c>
+      <c r="M86" s="5">
+        <v>2.1300588268786669E-3</v>
+      </c>
+      <c r="N86" s="5">
+        <v>6.7487760650331019E-4</v>
+      </c>
+      <c r="O86" s="5">
+        <v>103749.3566108013</v>
+      </c>
+      <c r="P86" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q86" s="6">
+        <v>260000</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
       </c>
       <c r="S86">
         <f t="shared" si="2"/>
-        <v>6.1352825001691591E-2</v>
+        <v>5.8516231108387107E-2</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A87">
+      <c r="A87" s="4">
         <v>86</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="5">
         <v>1.2134415787506809</v>
       </c>
-      <c r="C87" s="14">
-        <v>805.17840576171875</v>
-      </c>
-      <c r="D87">
-        <v>1.2129890918731689</v>
-      </c>
-      <c r="E87">
-        <f t="shared" si="3"/>
-        <v>2.0474437432054313E-7</v>
-      </c>
-      <c r="F87">
-        <v>1.515534124337137E-3</v>
-      </c>
-      <c r="G87" t="b">
-        <v>1</v>
-      </c>
-      <c r="H87">
-        <v>787.5</v>
-      </c>
-      <c r="I87">
-        <v>862.5</v>
-      </c>
-      <c r="J87">
-        <v>0.5471457839012146</v>
-      </c>
-      <c r="K87">
-        <v>0.29936850070953369</v>
-      </c>
-      <c r="L87">
-        <v>3.8689049409417809E-3</v>
-      </c>
-      <c r="M87">
-        <v>7.7378097921609879E-3</v>
-      </c>
-      <c r="N87">
-        <v>2.3888665389311114E-3</v>
-      </c>
-      <c r="O87">
-        <v>17674.23746215256</v>
-      </c>
-      <c r="P87">
-        <v>70</v>
-      </c>
-      <c r="Q87">
-        <v>20000</v>
+      <c r="C87" s="5">
+        <v>805.79998779296875</v>
+      </c>
+      <c r="D87" s="5">
+        <v>1.2130575180053711</v>
+      </c>
+      <c r="E87" s="5">
+        <v>8.8881806732388213E-6</v>
+      </c>
+      <c r="F87" s="5">
+        <v>1.5202244976535439E-3</v>
+      </c>
+      <c r="G87" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H87" s="5">
+        <v>750</v>
+      </c>
+      <c r="I87" s="5">
+        <v>950</v>
+      </c>
+      <c r="J87" s="5">
+        <v>0.54280632734298706</v>
+      </c>
+      <c r="K87" s="5">
+        <v>0.29463869333267212</v>
+      </c>
+      <c r="L87" s="5">
+        <v>1.0258075373013309E-3</v>
+      </c>
+      <c r="M87" s="5">
+        <v>2.0516151562333111E-3</v>
+      </c>
+      <c r="N87" s="5">
+        <v>3.8406074530961121E-4</v>
+      </c>
+      <c r="O87" s="5">
+        <v>81130.811259404625</v>
+      </c>
+      <c r="P87" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q87" s="6">
+        <v>280000</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
       </c>
       <c r="S87">
         <f t="shared" si="2"/>
-        <v>0.19686704170715899</v>
+        <v>3.1650534482675907E-2</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A88">
+      <c r="A88" s="4">
         <v>87</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="5">
         <v>1.288186717062378</v>
       </c>
-      <c r="C88" s="14">
-        <v>759.5911865234375</v>
-      </c>
-      <c r="D88">
-        <v>1.28356409072876</v>
-      </c>
-      <c r="E88">
-        <f t="shared" si="3"/>
-        <v>2.1368674220258456E-5</v>
-      </c>
-      <c r="F88">
-        <v>1.6302834264934061E-3</v>
-      </c>
-      <c r="G88" t="b">
-        <v>1</v>
-      </c>
-      <c r="H88">
-        <v>743.75</v>
-      </c>
-      <c r="I88">
-        <v>781.25</v>
-      </c>
-      <c r="J88">
-        <v>0.54227781295776367</v>
-      </c>
-      <c r="K88">
-        <v>0.2940652072429657</v>
-      </c>
-      <c r="L88">
-        <v>3.8344831882944491E-3</v>
-      </c>
-      <c r="M88">
-        <v>7.6689664274454117E-3</v>
-      </c>
-      <c r="N88">
-        <v>4.6226263336184292E-3</v>
-      </c>
-      <c r="O88">
-        <v>14578.854524978389</v>
-      </c>
-      <c r="P88">
-        <v>70</v>
-      </c>
-      <c r="Q88">
-        <v>20000</v>
+      <c r="C88" s="5">
+        <v>757.70001220703125</v>
+      </c>
+      <c r="D88" s="5">
+        <v>1.288069009780884</v>
+      </c>
+      <c r="E88" s="5">
+        <v>3.0374906145880232E-8</v>
+      </c>
+      <c r="F88" s="5">
+        <v>1.669995253905654E-3</v>
+      </c>
+      <c r="G88" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H88" s="5">
+        <v>650</v>
+      </c>
+      <c r="I88" s="5">
+        <v>850</v>
+      </c>
+      <c r="J88" s="5">
+        <v>0.54237622022628784</v>
+      </c>
+      <c r="K88" s="5">
+        <v>0.29417195916175842</v>
+      </c>
+      <c r="L88" s="5">
+        <v>7.5214048946854988E-4</v>
+      </c>
+      <c r="M88" s="5">
+        <v>1.50428107008338E-3</v>
+      </c>
+      <c r="N88" s="5">
+        <v>1.177072814944058E-4</v>
+      </c>
+      <c r="O88" s="5">
+        <v>44820.793322168021</v>
+      </c>
+      <c r="P88" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q88" s="6">
+        <v>520000</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
       </c>
       <c r="S88">
         <f t="shared" si="2"/>
-        <v>0.35884753913314782</v>
+        <v>9.1374394670695903E-3</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A89">
+      <c r="A89" s="4">
         <v>88</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="5">
         <v>1.3779544541977089</v>
       </c>
-      <c r="C89" s="14">
-        <v>709.41546630859375</v>
-      </c>
-      <c r="D89">
-        <v>1.375151634216309</v>
-      </c>
-      <c r="E89">
-        <f t="shared" si="3"/>
-        <v>7.8557998481343247E-6</v>
-      </c>
-      <c r="F89">
-        <v>1.691667246632278E-3</v>
-      </c>
-      <c r="G89" t="b">
-        <v>0</v>
-      </c>
-      <c r="H89">
-        <v>693.75</v>
-      </c>
-      <c r="I89">
-        <v>731.25</v>
-      </c>
-      <c r="J89">
-        <v>0.53854817152023315</v>
-      </c>
-      <c r="K89">
-        <v>0.29003411531448359</v>
-      </c>
-      <c r="L89">
-        <v>3.808110640775728E-3</v>
-      </c>
-      <c r="M89">
-        <v>7.6162214390933514E-3</v>
-      </c>
-      <c r="N89">
-        <v>2.80281998140075E-3</v>
-      </c>
-      <c r="O89">
-        <v>6.7883416950050961</v>
-      </c>
-      <c r="P89">
-        <v>70</v>
-      </c>
-      <c r="Q89">
-        <v>20000</v>
+      <c r="C89" s="5">
+        <v>708.5999755859375</v>
+      </c>
+      <c r="D89" s="5">
+        <v>1.3774845600128169</v>
+      </c>
+      <c r="E89" s="5">
+        <v>2.7964256332779769E-7</v>
+      </c>
+      <c r="F89" s="5">
+        <v>1.9382953178137541E-3</v>
+      </c>
+      <c r="G89" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H89" s="5">
+        <v>650</v>
+      </c>
+      <c r="I89" s="5">
+        <v>850</v>
+      </c>
+      <c r="J89" s="5">
+        <v>0.54114800691604614</v>
+      </c>
+      <c r="K89" s="5">
+        <v>0.29284116625785828</v>
+      </c>
+      <c r="L89" s="5">
+        <v>1.104613743557013E-3</v>
+      </c>
+      <c r="M89" s="5">
+        <v>2.2092275321483612E-3</v>
+      </c>
+      <c r="N89" s="5">
+        <v>4.6989418489196128E-4</v>
+      </c>
+      <c r="O89" s="5">
+        <v>49906.990151633072</v>
+      </c>
+      <c r="P89" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>240000</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
       </c>
       <c r="S89">
         <f t="shared" si="2"/>
-        <v>0.20340439938797872</v>
+        <v>3.4100850246574325E-2</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.25">
@@ -6003,741 +5988,729 @@
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A91">
+      <c r="A91" s="4">
         <v>90</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="5">
         <v>1.60411161733039</v>
       </c>
-      <c r="C91" s="14">
-        <v>609.16339111328125</v>
-      </c>
-      <c r="D91">
-        <v>1.605581402778625</v>
-      </c>
-      <c r="E91">
-        <f t="shared" si="3"/>
-        <v>2.1602692638435405E-6</v>
-      </c>
-      <c r="F91">
-        <v>2.586782211437821E-3</v>
-      </c>
-      <c r="G91" t="b">
-        <v>1</v>
-      </c>
-      <c r="H91">
-        <v>600</v>
-      </c>
-      <c r="I91">
-        <v>631.25</v>
-      </c>
-      <c r="J91">
-        <v>0.54172325134277344</v>
-      </c>
-      <c r="K91">
-        <v>0.29346409440040588</v>
-      </c>
-      <c r="L91">
-        <v>3.8305618455089958E-3</v>
-      </c>
-      <c r="M91">
-        <v>7.6611237600445747E-3</v>
-      </c>
-      <c r="N91">
-        <v>1.469785448235061E-3</v>
-      </c>
-      <c r="O91">
-        <v>5925.3651017309621</v>
-      </c>
-      <c r="P91">
-        <v>70</v>
-      </c>
-      <c r="Q91">
-        <v>20000</v>
+      <c r="C91" s="5">
+        <v>609.79998779296875</v>
+      </c>
+      <c r="D91" s="5">
+        <v>1.604020357131958</v>
+      </c>
+      <c r="E91" s="5">
+        <v>2.517539599011798E-8</v>
+      </c>
+      <c r="F91" s="5">
+        <v>2.622093772515655E-3</v>
+      </c>
+      <c r="G91" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" s="5">
+        <v>550</v>
+      </c>
+      <c r="I91" s="5">
+        <v>750</v>
+      </c>
+      <c r="J91" s="5">
+        <v>0.53919690847396851</v>
+      </c>
+      <c r="K91" s="5">
+        <v>0.29073333740234381</v>
+      </c>
+      <c r="L91" s="5">
+        <v>6.0284047030276298E-4</v>
+      </c>
+      <c r="M91" s="5">
+        <v>1.2056808918714519E-3</v>
+      </c>
+      <c r="N91" s="5">
+        <v>9.126019843241906E-5</v>
+      </c>
+      <c r="O91" s="5">
+        <v>18180.824512185522</v>
+      </c>
+      <c r="P91" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q91" s="6">
+        <v>800000</v>
       </c>
       <c r="R91" t="b">
         <v>1</v>
       </c>
       <c r="S91">
         <f t="shared" si="2"/>
-        <v>9.1626133266282397E-2</v>
+        <v>5.6891426660382266E-3</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A92">
+      <c r="A92" s="4">
         <v>91</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="5">
         <v>1.741164351173744</v>
       </c>
-      <c r="C92" s="14">
-        <v>561.83294677734375</v>
-      </c>
-      <c r="D92">
-        <v>1.7451074123382571</v>
-      </c>
-      <c r="E92">
-        <f t="shared" si="3"/>
-        <v>1.5547731347090929E-5</v>
-      </c>
-      <c r="F92">
-        <v>3.1471722759306431E-3</v>
-      </c>
-      <c r="G92" t="b">
-        <v>1</v>
-      </c>
-      <c r="H92">
-        <v>543.75</v>
-      </c>
-      <c r="I92">
-        <v>581.25</v>
-      </c>
-      <c r="J92">
-        <v>0.53951317071914673</v>
-      </c>
-      <c r="K92">
-        <v>0.29107445478439331</v>
-      </c>
-      <c r="L92">
-        <v>3.8149342155496409E-3</v>
-      </c>
-      <c r="M92">
-        <v>7.6298685744404793E-3</v>
-      </c>
-      <c r="N92">
-        <v>3.9430611645130398E-3</v>
-      </c>
-      <c r="O92">
-        <v>4133.7489623763877</v>
-      </c>
-      <c r="P92">
-        <v>70</v>
-      </c>
-      <c r="Q92">
-        <v>20000</v>
+      <c r="C92" s="5">
+        <v>562.20001220703125</v>
+      </c>
+      <c r="D92" s="5">
+        <v>1.740996718406677</v>
+      </c>
+      <c r="E92" s="5">
+        <v>1.181162048169426E-7</v>
+      </c>
+      <c r="F92" s="5">
+        <v>3.0820043757557869E-3</v>
+      </c>
+      <c r="G92" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H92" s="5">
+        <v>450</v>
+      </c>
+      <c r="I92" s="5">
+        <v>650</v>
+      </c>
+      <c r="J92" s="5">
+        <v>0.53832542896270752</v>
+      </c>
+      <c r="K92" s="5">
+        <v>0.28979423642158508</v>
+      </c>
+      <c r="L92" s="5">
+        <v>1.055743025747712E-3</v>
+      </c>
+      <c r="M92" s="5">
+        <v>2.1114861592650409E-3</v>
+      </c>
+      <c r="N92" s="5">
+        <v>1.676327670667721E-4</v>
+      </c>
+      <c r="O92" s="5">
+        <v>13159.62491975308</v>
+      </c>
+      <c r="P92" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q92" s="6">
+        <v>260000</v>
       </c>
       <c r="R92" t="b">
         <v>1</v>
       </c>
       <c r="S92">
         <f t="shared" si="2"/>
-        <v>0.22646117018505263</v>
+        <v>9.627624580859839E-3</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A93">
+      <c r="A93" s="4">
         <v>92</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="5">
         <v>1.8944949560389981</v>
       </c>
-      <c r="C93" s="14">
-        <v>517.19720458984375</v>
-      </c>
-      <c r="D93">
-        <v>1.89471447467804</v>
-      </c>
-      <c r="E93">
-        <f t="shared" si="3"/>
-        <v>4.8188432886810005E-8</v>
-      </c>
-      <c r="F93">
-        <v>3.6374018527567391E-3</v>
-      </c>
-      <c r="G93" t="b">
-        <v>1</v>
-      </c>
-      <c r="H93">
-        <v>493.75</v>
-      </c>
-      <c r="I93">
-        <v>531.25</v>
-      </c>
-      <c r="J93">
-        <v>0.54436945915222168</v>
-      </c>
-      <c r="K93">
-        <v>0.29633811116218572</v>
-      </c>
-      <c r="L93">
-        <v>3.849273360373892E-3</v>
-      </c>
-      <c r="M93">
-        <v>7.6985466293990612E-3</v>
-      </c>
-      <c r="N93">
-        <v>2.1951863904190461E-4</v>
-      </c>
-      <c r="O93">
-        <v>3021.105968767085</v>
-      </c>
-      <c r="P93">
-        <v>70</v>
-      </c>
-      <c r="Q93">
-        <v>20000</v>
+      <c r="C93" s="5">
+        <v>517.469970703125</v>
+      </c>
+      <c r="D93" s="5">
+        <v>1.894332647323608</v>
+      </c>
+      <c r="E93" s="5">
+        <v>1.8221340724267069E-5</v>
+      </c>
+      <c r="F93" s="5">
+        <v>3.5621318966150279E-3</v>
+      </c>
+      <c r="G93" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H93" s="5">
+        <v>450</v>
+      </c>
+      <c r="I93" s="5">
+        <v>600</v>
+      </c>
+      <c r="J93" s="5">
+        <v>0.53948569297790527</v>
+      </c>
+      <c r="K93" s="5">
+        <v>0.29104483127593989</v>
+      </c>
+      <c r="L93" s="5">
+        <v>1.907369959289003E-3</v>
+      </c>
+      <c r="M93" s="5">
+        <v>3.8147398736327891E-3</v>
+      </c>
+      <c r="N93" s="5">
+        <v>1.6230871538924771E-4</v>
+      </c>
+      <c r="O93" s="5">
+        <v>19702.440117026021</v>
+      </c>
+      <c r="P93" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q93" s="6">
+        <v>80000</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
       </c>
       <c r="S93">
         <f t="shared" si="2"/>
-        <v>1.1587185193719029E-2</v>
+        <v>8.5673870427505419E-3</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A94">
+      <c r="A94" s="4">
         <v>93</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="5">
         <v>2.0641515592264712</v>
       </c>
-      <c r="C94" s="14">
-        <v>475.73391723632813</v>
-      </c>
-      <c r="D94">
-        <v>2.0646834373474121</v>
-      </c>
-      <c r="E94">
-        <f t="shared" si="3"/>
-        <v>2.8289433553563284E-7</v>
-      </c>
-      <c r="F94">
-        <v>4.2521283030509949E-3</v>
-      </c>
-      <c r="G94" t="b">
-        <v>1</v>
-      </c>
-      <c r="H94">
-        <v>468.75</v>
-      </c>
-      <c r="I94">
-        <v>506.25</v>
-      </c>
-      <c r="J94">
-        <v>0.54014480113983154</v>
-      </c>
-      <c r="K94">
-        <v>0.29175639152526861</v>
-      </c>
-      <c r="L94">
-        <v>3.8194005170863409E-3</v>
-      </c>
-      <c r="M94">
-        <v>7.6388008892536163E-3</v>
-      </c>
-      <c r="N94">
-        <v>5.3187812094135367E-4</v>
-      </c>
-      <c r="O94">
-        <v>2176.9809311967551</v>
-      </c>
-      <c r="P94">
-        <v>70</v>
-      </c>
-      <c r="Q94">
-        <v>20000</v>
+      <c r="C94" s="5">
+        <v>475.44000244140619</v>
+      </c>
+      <c r="D94" s="5">
+        <v>2.0638003349304199</v>
+      </c>
+      <c r="E94" s="5">
+        <v>2.372558469687647E-7</v>
+      </c>
+      <c r="F94" s="5">
+        <v>4.3005542829632759E-3</v>
+      </c>
+      <c r="G94" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" s="5">
+        <v>350</v>
+      </c>
+      <c r="I94" s="5">
+        <v>550</v>
+      </c>
+      <c r="J94" s="5">
+        <v>0.5380215048789978</v>
+      </c>
+      <c r="K94" s="5">
+        <v>0.28946712613105768</v>
+      </c>
+      <c r="L94" s="5">
+        <v>1.5531343033584851E-3</v>
+      </c>
+      <c r="M94" s="5">
+        <v>3.1062685884535308E-3</v>
+      </c>
+      <c r="N94" s="5">
+        <v>3.5122429605083377E-4</v>
+      </c>
+      <c r="O94" s="5">
+        <v>422.41678094999202</v>
+      </c>
+      <c r="P94" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q94" s="6">
+        <v>120000</v>
       </c>
       <c r="R94" t="b">
         <v>1</v>
       </c>
       <c r="S94">
         <f t="shared" si="2"/>
-        <v>2.5767396709022273E-2</v>
+        <v>1.7015431569494494E-2</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A95">
+      <c r="A95" s="4">
         <v>94</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="5">
         <v>2.2499874789877352</v>
       </c>
-      <c r="C95" s="14">
-        <v>437.32403564453119</v>
-      </c>
-      <c r="D95">
-        <v>2.2502238750457759</v>
-      </c>
-      <c r="E95">
-        <f t="shared" si="3"/>
-        <v>5.5883096257187184E-8</v>
-      </c>
-      <c r="F95">
-        <v>5.0141783431172371E-3</v>
-      </c>
-      <c r="G95" t="b">
-        <v>1</v>
-      </c>
-      <c r="H95">
-        <v>418.75</v>
-      </c>
-      <c r="I95">
-        <v>456.25</v>
-      </c>
-      <c r="J95">
-        <v>0.54189616441726685</v>
-      </c>
-      <c r="K95">
-        <v>0.29365143179893488</v>
-      </c>
-      <c r="L95">
-        <v>3.831784525584297E-3</v>
-      </c>
-      <c r="M95">
-        <v>7.6635689474642277E-3</v>
-      </c>
-      <c r="N95">
-        <v>2.3639605804115499E-4</v>
-      </c>
-      <c r="O95">
-        <v>1553.760833953382</v>
-      </c>
-      <c r="P95">
-        <v>70</v>
-      </c>
-      <c r="Q95">
-        <v>20000</v>
+      <c r="C95" s="5">
+        <v>437.20999145507813</v>
+      </c>
+      <c r="D95" s="5">
+        <v>2.2498457431793208</v>
+      </c>
+      <c r="E95" s="5">
+        <v>1.224155039381003E-5</v>
+      </c>
+      <c r="F95" s="5">
+        <v>5.0168195739388466E-3</v>
+      </c>
+      <c r="G95" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H95" s="5">
+        <v>350</v>
+      </c>
+      <c r="I95" s="5">
+        <v>550</v>
+      </c>
+      <c r="J95" s="5">
+        <v>0.54204505681991577</v>
+      </c>
+      <c r="K95" s="5">
+        <v>0.29381284117698669</v>
+      </c>
+      <c r="L95" s="5">
+        <v>1.2776124512867001E-3</v>
+      </c>
+      <c r="M95" s="5">
+        <v>2.5552248116582632E-3</v>
+      </c>
+      <c r="N95" s="5">
+        <v>1.4173580841392311E-4</v>
+      </c>
+      <c r="O95" s="5">
+        <v>310.40811455219898</v>
+      </c>
+      <c r="P95" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q95" s="6">
+        <v>180000</v>
       </c>
       <c r="R95" t="b">
         <v>1</v>
       </c>
       <c r="S95">
         <f t="shared" si="2"/>
-        <v>1.0506549936336051E-2</v>
+        <v>6.2994043183604628E-3</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A96">
+      <c r="A96" s="4">
         <v>95</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="5">
         <v>2.451611489865392</v>
       </c>
-      <c r="C96" s="14">
-        <v>402.53265380859381</v>
-      </c>
-      <c r="D96">
-        <v>2.4533123970031738</v>
-      </c>
-      <c r="E96">
-        <f t="shared" si="3"/>
-        <v>2.893085091357127E-6</v>
-      </c>
-      <c r="F96">
-        <v>6.1460942961275578E-3</v>
-      </c>
-      <c r="G96" t="b">
-        <v>1</v>
-      </c>
-      <c r="H96">
-        <v>393.75</v>
-      </c>
-      <c r="I96">
-        <v>431.25</v>
-      </c>
-      <c r="J96">
-        <v>0.54150855541229248</v>
-      </c>
-      <c r="K96">
-        <v>0.2932315468788147</v>
-      </c>
-      <c r="L96">
-        <v>3.8290437160256332E-3</v>
-      </c>
-      <c r="M96">
-        <v>7.6580876484513283E-3</v>
-      </c>
-      <c r="N96">
-        <v>1.700907137781815E-3</v>
-      </c>
-      <c r="O96">
-        <v>1067.681294348195</v>
-      </c>
-      <c r="P96">
-        <v>70</v>
-      </c>
-      <c r="Q96">
-        <v>20000</v>
+      <c r="C96" s="5">
+        <v>402.47000122070313</v>
+      </c>
+      <c r="D96" s="5">
+        <v>2.451360940933228</v>
+      </c>
+      <c r="E96" s="5">
+        <v>9.8749660537578166E-7</v>
+      </c>
+      <c r="F96" s="5">
+        <v>5.8587524108588704E-3</v>
+      </c>
+      <c r="G96" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H96" s="5">
+        <v>350</v>
+      </c>
+      <c r="I96" s="5">
+        <v>550</v>
+      </c>
+      <c r="J96" s="5">
+        <v>0.54326903820037842</v>
+      </c>
+      <c r="K96" s="5">
+        <v>0.29514124989509583</v>
+      </c>
+      <c r="L96" s="5">
+        <v>1.4519475784200151E-3</v>
+      </c>
+      <c r="M96" s="5">
+        <v>2.9038952197879549E-3</v>
+      </c>
+      <c r="N96" s="5">
+        <v>2.5054893216447383E-4</v>
+      </c>
+      <c r="O96" s="5">
+        <v>113.80196059615569</v>
+      </c>
+      <c r="P96" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q96" s="6">
+        <v>140000</v>
       </c>
       <c r="R96" t="b">
         <v>1</v>
       </c>
       <c r="S96">
         <f t="shared" si="2"/>
-        <v>6.9379146933073191E-2</v>
+        <v>1.0219764966847599E-2</v>
       </c>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A97">
+      <c r="A97" s="4">
         <v>96</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="5">
         <v>2.668338221910707</v>
       </c>
-      <c r="C97" s="14">
-        <v>370.69317626953119</v>
-      </c>
-      <c r="D97">
-        <v>2.6640868186950679</v>
-      </c>
-      <c r="E97">
-        <f t="shared" si="3"/>
-        <v>1.8074429301946517E-5</v>
-      </c>
-      <c r="F97">
-        <v>7.0380507968366146E-3</v>
-      </c>
-      <c r="G97" t="b">
-        <v>1</v>
-      </c>
-      <c r="H97">
-        <v>350</v>
-      </c>
-      <c r="I97">
-        <v>381.25</v>
-      </c>
-      <c r="J97">
-        <v>0.55232340097427368</v>
-      </c>
-      <c r="K97">
-        <v>0.30506113171577448</v>
-      </c>
-      <c r="L97">
-        <v>3.9055162223692549E-3</v>
-      </c>
-      <c r="M97">
-        <v>7.811032235622406E-3</v>
-      </c>
-      <c r="N97">
-        <v>4.2514032156386614E-3</v>
-      </c>
-      <c r="O97">
-        <v>787.06390842971723</v>
-      </c>
-      <c r="P97">
-        <v>70</v>
-      </c>
-      <c r="Q97">
-        <v>20000</v>
+      <c r="C97" s="5">
+        <v>370.6400146484375</v>
+      </c>
+      <c r="D97" s="5">
+        <v>2.6677896976470952</v>
+      </c>
+      <c r="E97" s="5">
+        <v>1.853204230428673E-5</v>
+      </c>
+      <c r="F97" s="5">
+        <v>7.0040496066212654E-3</v>
+      </c>
+      <c r="G97" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H97" s="5">
+        <v>250</v>
+      </c>
+      <c r="I97" s="5">
+        <v>450</v>
+      </c>
+      <c r="J97" s="5">
+        <v>0.54896694421768188</v>
+      </c>
+      <c r="K97" s="5">
+        <v>0.30136469006538391</v>
+      </c>
+      <c r="L97" s="5">
+        <v>1.5847310651014241E-3</v>
+      </c>
+      <c r="M97" s="5">
+        <v>3.1694620847702031E-3</v>
+      </c>
+      <c r="N97" s="5">
+        <v>5.4852426361229334E-4</v>
+      </c>
+      <c r="O97" s="5">
+        <v>2548.071359190028</v>
+      </c>
+      <c r="P97" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q97" s="6">
+        <v>120000</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
       </c>
       <c r="S97">
         <f t="shared" si="2"/>
-        <v>0.15932774866127636</v>
+        <v>2.0556774216557661E-2</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A98">
+      <c r="A98" s="4">
         <v>97</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="5">
         <v>2.8991416438778361</v>
       </c>
-      <c r="C98" s="14">
-        <v>342.44683837890619</v>
-      </c>
-      <c r="D98">
-        <v>2.8974988460540771</v>
-      </c>
-      <c r="E98">
-        <f t="shared" si="3"/>
-        <v>2.6987846897472378E-6</v>
-      </c>
-      <c r="F98">
-        <v>8.0352509394288063E-3</v>
-      </c>
-      <c r="G98" t="b">
-        <v>1</v>
-      </c>
-      <c r="H98">
-        <v>318.75</v>
-      </c>
-      <c r="I98">
-        <v>356.25</v>
-      </c>
-      <c r="J98">
-        <v>0.55505967140197754</v>
-      </c>
-      <c r="K98">
-        <v>0.30809125304222112</v>
-      </c>
-      <c r="L98">
-        <v>3.9248645761151514E-3</v>
-      </c>
-      <c r="M98">
-        <v>7.8497286885976791E-3</v>
-      </c>
-      <c r="N98">
-        <v>1.642797823758535E-3</v>
-      </c>
-      <c r="O98">
-        <v>583.99057278602959</v>
-      </c>
-      <c r="P98">
-        <v>70</v>
-      </c>
-      <c r="Q98">
-        <v>20000</v>
+      <c r="C98" s="5">
+        <v>342.67001342773438</v>
+      </c>
+      <c r="D98" s="5">
+        <v>2.8987081050872798</v>
+      </c>
+      <c r="E98" s="5">
+        <v>4.6545892473659478E-6</v>
+      </c>
+      <c r="F98" s="5">
+        <v>8.1189507618546486E-3</v>
+      </c>
+      <c r="G98" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H98" s="5">
+        <v>250</v>
+      </c>
+      <c r="I98" s="5">
+        <v>450</v>
+      </c>
+      <c r="J98" s="5">
+        <v>0.55779224634170532</v>
+      </c>
+      <c r="K98" s="5">
+        <v>0.31113219261169428</v>
+      </c>
+      <c r="L98" s="5">
+        <v>1.7638939596215119E-3</v>
+      </c>
+      <c r="M98" s="5">
+        <v>3.5277879796922211E-3</v>
+      </c>
+      <c r="N98" s="5">
+        <v>4.3353879055541E-4</v>
+      </c>
+      <c r="O98" s="5">
+        <v>59.259805196770728</v>
+      </c>
+      <c r="P98" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q98" s="6">
+        <v>100000</v>
       </c>
       <c r="R98" t="b">
         <v>1</v>
       </c>
       <c r="S98">
         <f t="shared" si="2"/>
-        <v>5.6664972793849432E-2</v>
+        <v>1.4954039636901523E-2</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A99">
+      <c r="A99" s="4">
         <v>98</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="5">
         <v>3.1426150900261072</v>
       </c>
-      <c r="C99" s="14">
-        <v>317.7115478515625</v>
-      </c>
-      <c r="D99">
-        <v>3.148351669311523</v>
-      </c>
-      <c r="E99">
-        <f t="shared" si="3"/>
-        <v>3.29083418978619E-5</v>
-      </c>
-      <c r="F99">
-        <v>9.2890560626983643E-3</v>
-      </c>
-      <c r="G99" t="b">
-        <v>1</v>
-      </c>
-      <c r="H99">
-        <v>293.75</v>
-      </c>
-      <c r="I99">
-        <v>331.25</v>
-      </c>
-      <c r="J99">
-        <v>0.56511878967285156</v>
-      </c>
-      <c r="K99">
-        <v>0.31935924291610718</v>
-      </c>
-      <c r="L99">
-        <v>3.9959932835360763E-3</v>
-      </c>
-      <c r="M99">
-        <v>7.9919863492250443E-3</v>
-      </c>
-      <c r="N99">
-        <v>5.7365792854162656E-3</v>
-      </c>
-      <c r="O99">
-        <v>429.92250757184502</v>
-      </c>
-      <c r="P99">
-        <v>70</v>
-      </c>
-      <c r="Q99">
-        <v>20000</v>
+      <c r="C99" s="5">
+        <v>317.3800048828125</v>
+      </c>
+      <c r="D99" s="5">
+        <v>3.1429083347320561</v>
+      </c>
+      <c r="E99" s="5">
+        <v>4.9800291890278459E-8</v>
+      </c>
+      <c r="F99" s="5">
+        <v>9.1174338012933731E-3</v>
+      </c>
+      <c r="G99" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H99" s="5">
+        <v>250</v>
+      </c>
+      <c r="I99" s="5">
+        <v>450</v>
+      </c>
+      <c r="J99" s="5">
+        <v>0.55955517292022705</v>
+      </c>
+      <c r="K99" s="5">
+        <v>0.31310197710990911</v>
+      </c>
+      <c r="L99" s="5">
+        <v>1.6152966485597029E-3</v>
+      </c>
+      <c r="M99" s="5">
+        <v>3.2305934000760321E-3</v>
+      </c>
+      <c r="N99" s="5">
+        <v>2.9324470594849222E-4</v>
+      </c>
+      <c r="O99" s="5">
+        <v>375.92809524698453</v>
+      </c>
+      <c r="P99" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q99" s="6">
+        <v>120000</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
       </c>
       <c r="S99">
         <f t="shared" si="2"/>
-        <v>0.18254158148806601</v>
+        <v>9.3312320328117586E-3</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A100">
+      <c r="A100" s="4">
         <v>99</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="5">
         <v>3.396941596840962</v>
       </c>
-      <c r="C100" s="14">
-        <v>295.99356079101563</v>
-      </c>
-      <c r="D100">
-        <v>3.395908117294312</v>
-      </c>
-      <c r="E100">
-        <f t="shared" si="3"/>
-        <v>1.0680799733439037E-6</v>
-      </c>
-      <c r="F100">
-        <v>1.046575699001551E-2</v>
-      </c>
-      <c r="G100" t="b">
-        <v>1</v>
-      </c>
-      <c r="H100">
-        <v>268.75</v>
-      </c>
-      <c r="I100">
-        <v>306.25</v>
-      </c>
-      <c r="J100">
-        <v>0.56142938137054443</v>
-      </c>
-      <c r="K100">
-        <v>0.31520295143127441</v>
-      </c>
-      <c r="L100">
-        <v>3.969905227244803E-3</v>
-      </c>
-      <c r="M100">
-        <v>7.9398108646273613E-3</v>
-      </c>
-      <c r="N100">
-        <v>1.0334795466500069E-3</v>
-      </c>
-      <c r="O100">
-        <v>326.58583376427657</v>
-      </c>
-      <c r="P100">
-        <v>70</v>
-      </c>
-      <c r="Q100">
-        <v>20000</v>
+      <c r="C100" s="5">
+        <v>295.73001098632813</v>
+      </c>
+      <c r="D100" s="5">
+        <v>3.3973333835601811</v>
+      </c>
+      <c r="E100" s="5">
+        <v>4.9972328497460694E-7</v>
+      </c>
+      <c r="F100" s="5">
+        <v>1.108350791037083E-2</v>
+      </c>
+      <c r="G100" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H100" s="5">
+        <v>150</v>
+      </c>
+      <c r="I100" s="5">
+        <v>350</v>
+      </c>
+      <c r="J100" s="5">
+        <v>0.55725306272506714</v>
+      </c>
+      <c r="K100" s="5">
+        <v>0.31053099036216741</v>
+      </c>
+      <c r="L100" s="5">
+        <v>1.3134580649662251E-3</v>
+      </c>
+      <c r="M100" s="5">
+        <v>2.6269161608070139E-3</v>
+      </c>
+      <c r="N100" s="5">
+        <v>3.9178671921868968E-4</v>
+      </c>
+      <c r="O100" s="5">
+        <v>1017.549492123794</v>
+      </c>
+      <c r="P100" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q100" s="6">
+        <v>180000</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100">
         <f t="shared" si="2"/>
-        <v>3.0423824407552577E-2</v>
+        <v>1.1533513545921359E-2</v>
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>100</v>
-      </c>
-      <c r="B101">
-        <v>3.65987831595602</v>
-      </c>
-      <c r="C101" s="14">
-        <v>277.44094848632813</v>
-      </c>
-      <c r="D101">
-        <v>3.663387537002563</v>
-      </c>
-      <c r="E101">
-        <f t="shared" si="3"/>
-        <v>1.2314632353500727E-5</v>
-      </c>
-      <c r="F101">
-        <v>1.132305338978767E-2</v>
-      </c>
-      <c r="G101" t="b">
-        <v>1</v>
-      </c>
-      <c r="H101">
-        <v>268.75</v>
-      </c>
-      <c r="I101">
-        <v>306.25</v>
-      </c>
-      <c r="J101">
-        <v>0.55844169855117798</v>
-      </c>
-      <c r="K101">
-        <v>0.31185716390609741</v>
-      </c>
-      <c r="L101">
-        <v>3.9487791194287173E-3</v>
-      </c>
-      <c r="M101">
-        <v>7.8975586220622063E-3</v>
-      </c>
-      <c r="N101">
-        <v>3.5092210465386131E-3</v>
-      </c>
-      <c r="O101">
-        <v>260.04427790048851</v>
-      </c>
-      <c r="P101">
-        <v>70</v>
-      </c>
-      <c r="Q101">
-        <v>20000</v>
+      <c r="A101" s="4">
+        <v>100</v>
+      </c>
+      <c r="B101" s="5">
+        <v>3.6598783159560249</v>
+      </c>
+      <c r="C101" s="5">
+        <v>277.39999389648438</v>
+      </c>
+      <c r="D101" s="5">
+        <v>3.6595418453216548</v>
+      </c>
+      <c r="E101" s="5">
+        <v>6.4497444327571429E-6</v>
+      </c>
+      <c r="F101" s="5">
+        <v>1.2519466690719129E-2</v>
+      </c>
+      <c r="G101" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H101" s="5">
+        <v>150</v>
+      </c>
+      <c r="I101" s="5">
+        <v>350</v>
+      </c>
+      <c r="J101" s="5">
+        <v>0.5600782036781311</v>
+      </c>
+      <c r="K101" s="5">
+        <v>0.31368759274482733</v>
+      </c>
+      <c r="L101" s="5">
+        <v>9.0856682145031096E-4</v>
+      </c>
+      <c r="M101" s="5">
+        <v>1.8171336269006131E-3</v>
+      </c>
+      <c r="N101" s="5">
+        <v>3.3647063436959002E-4</v>
+      </c>
+      <c r="O101" s="5">
+        <v>1595.028144457008</v>
+      </c>
+      <c r="P101" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q101" s="6">
+        <v>380000</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>
       </c>
       <c r="S101">
         <f t="shared" si="2"/>
-        <v>9.5883544303629317E-2</v>
+        <v>9.1934923875111926E-3</v>
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A102">
+      <c r="A102" s="4">
         <v>101</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="5">
         <v>3.9287583783681899</v>
       </c>
-      <c r="C102" s="14">
-        <v>262.08700561523438</v>
-      </c>
-      <c r="D102">
-        <v>3.9297914505004878</v>
-      </c>
-      <c r="E102">
-        <f t="shared" si="3"/>
-        <v>1.0672380305306829E-6</v>
-      </c>
-      <c r="F102">
-        <v>1.2498758733272551E-2</v>
-      </c>
-      <c r="G102" t="b">
-        <v>1</v>
-      </c>
-      <c r="H102">
-        <v>243.75</v>
-      </c>
-      <c r="I102">
-        <v>281.25</v>
-      </c>
-      <c r="J102">
-        <v>0.56631797552108765</v>
-      </c>
-      <c r="K102">
-        <v>0.32071602344512939</v>
-      </c>
-      <c r="L102">
-        <v>4.0044728079879832E-3</v>
-      </c>
-      <c r="M102">
-        <v>8.0089457333087921E-3</v>
-      </c>
-      <c r="N102">
-        <v>1.0330721322979741E-3</v>
-      </c>
-      <c r="O102">
-        <v>204.44035388056281</v>
-      </c>
-      <c r="P102">
-        <v>70</v>
-      </c>
-      <c r="Q102">
-        <v>20000</v>
+      <c r="C102" s="5">
+        <v>261.91000366210938</v>
+      </c>
+      <c r="D102" s="5">
+        <v>3.9291176795959468</v>
+      </c>
+      <c r="E102" s="5">
+        <v>2.3479929041059222E-6</v>
+      </c>
+      <c r="F102" s="5">
+        <v>1.3725630007684231E-2</v>
+      </c>
+      <c r="G102" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H102" s="5">
+        <v>150</v>
+      </c>
+      <c r="I102" s="5">
+        <v>350</v>
+      </c>
+      <c r="J102" s="5">
+        <v>0.56195908784866333</v>
+      </c>
+      <c r="K102" s="5">
+        <v>0.31579798460006708</v>
+      </c>
+      <c r="L102" s="5">
+        <v>1.6222361532149121E-3</v>
+      </c>
+      <c r="M102" s="5">
+        <v>3.2444724347442389E-3</v>
+      </c>
+      <c r="N102" s="5">
+        <v>3.5930122775740259E-4</v>
+      </c>
+      <c r="O102" s="5">
+        <v>82.93836134603221</v>
+      </c>
+      <c r="P102" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>120000</v>
       </c>
       <c r="R102" t="b">
         <v>0</v>
       </c>
       <c r="S102">
         <f t="shared" si="2"/>
-        <v>2.6295130237229319E-2</v>
+        <v>9.1454142289767986E-3</v>
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="S103">
         <f>AVERAGE(S2:S102)</f>
-        <v>8.9664837333458189E-2</v>
+        <v>5.8089134391854452E-2</v>
       </c>
     </row>
   </sheetData>

--- a/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix.xlsx
+++ b/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D4D485-FD28-483A-8954-B4ED99DFD04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29E70C88-3ADC-4D3C-AFCC-CA6965696291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,8 +115,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -126,6 +133,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -226,11 +238,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -252,9 +265,11 @@
     <xf numFmtId="2" fontId="2" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2980,57 +2995,56 @@
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A41">
+      <c r="A41" s="4">
         <v>40</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="5">
         <v>3.4019493212427241</v>
       </c>
-      <c r="C41" s="14">
-        <v>295.44149780273438</v>
-      </c>
-      <c r="D41">
+      <c r="C41" s="5">
+        <v>295.42999267578119</v>
+      </c>
+      <c r="D41" s="15">
         <v>3.4018938541412349</v>
       </c>
-      <c r="E41">
-        <f t="shared" si="1"/>
-        <v>3.0765993476111782E-9</v>
-      </c>
-      <c r="F41">
-        <v>1.076914463192225E-2</v>
-      </c>
-      <c r="G41" t="b">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <v>237.5</v>
-      </c>
-      <c r="I41">
-        <v>312.5</v>
-      </c>
-      <c r="J41">
-        <v>0.55975854396820068</v>
-      </c>
-      <c r="K41">
-        <v>0.31332963705062872</v>
-      </c>
-      <c r="L41">
-        <v>3.9580906226702288E-3</v>
-      </c>
-      <c r="M41">
-        <v>7.9161813482642174E-3</v>
-      </c>
-      <c r="N41">
+      <c r="E41" s="5">
+        <v>2.2232891296880548E-6</v>
+      </c>
+      <c r="F41" s="5">
+        <v>1.109889522194862E-2</v>
+      </c>
+      <c r="G41" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" s="5">
+        <v>150</v>
+      </c>
+      <c r="I41" s="5">
+        <v>350</v>
+      </c>
+      <c r="J41" s="5">
+        <v>0.55928552150726318</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0.31280028820037842</v>
+      </c>
+      <c r="L41" s="5">
+        <v>1.7686161103180401E-3</v>
+      </c>
+      <c r="M41" s="5">
+        <v>3.537232289090753E-3</v>
+      </c>
+      <c r="N41" s="15">
         <v>5.5467101489181658E-5</v>
       </c>
-      <c r="O41">
-        <v>386.16426949736461</v>
-      </c>
-      <c r="P41">
-        <v>70</v>
-      </c>
-      <c r="Q41">
-        <v>20000</v>
+      <c r="O41" s="5">
+        <v>47.565469816714263</v>
+      </c>
+      <c r="P41" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>100000</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
@@ -3041,57 +3055,56 @@
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="A42" s="4">
         <v>41</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="5">
         <v>3.540332478193541</v>
       </c>
-      <c r="C42" s="14">
-        <v>285.37942504882813</v>
-      </c>
-      <c r="D42">
+      <c r="C42" s="5">
+        <v>285.42999267578119</v>
+      </c>
+      <c r="D42" s="15">
         <v>3.5418522357940669</v>
       </c>
-      <c r="E42">
-        <f t="shared" si="1"/>
-        <v>2.3096631643562933E-6</v>
-      </c>
-      <c r="F42">
-        <v>1.1191254481673241E-2</v>
-      </c>
-      <c r="G42" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42">
-        <v>237.5</v>
-      </c>
-      <c r="I42">
-        <v>312.5</v>
-      </c>
-      <c r="J42">
-        <v>0.55980002880096436</v>
-      </c>
-      <c r="K42">
-        <v>0.3133760392665863</v>
-      </c>
-      <c r="L42">
-        <v>3.9583839647358652E-3</v>
-      </c>
-      <c r="M42">
-        <v>7.9167680814862251E-3</v>
-      </c>
-      <c r="N42">
+      <c r="E42" s="5">
+        <v>3.3257492759730671E-6</v>
+      </c>
+      <c r="F42" s="5">
+        <v>1.184104289859533E-2</v>
+      </c>
+      <c r="G42" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" s="5">
+        <v>150</v>
+      </c>
+      <c r="I42" s="5">
+        <v>350</v>
+      </c>
+      <c r="J42" s="5">
+        <v>0.55870705842971802</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0.31215357780456537</v>
+      </c>
+      <c r="L42" s="5">
+        <v>1.020054863131045E-3</v>
+      </c>
+      <c r="M42" s="5">
+        <v>2.0401098299771552E-3</v>
+      </c>
+      <c r="N42" s="15">
         <v>2.1688224736493567E-4</v>
       </c>
-      <c r="O42">
-        <v>268.24070534576867</v>
-      </c>
-      <c r="P42">
-        <v>70</v>
-      </c>
-      <c r="Q42">
-        <v>20000</v>
+      <c r="O42" s="5">
+        <v>334.31924065187769</v>
+      </c>
+      <c r="P42" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>300000</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
@@ -3402,64 +3415,63 @@
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48">
+      <c r="A48" s="4">
         <v>47</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="5">
         <v>4.097070649025869</v>
       </c>
-      <c r="C48" s="14">
-        <v>253.69715881347659</v>
-      </c>
-      <c r="D48">
-        <v>4.1021084785461426</v>
-      </c>
-      <c r="E48">
-        <f t="shared" si="1"/>
-        <v>2.5379726275339526E-5</v>
-      </c>
-      <c r="F48">
-        <v>1.2739351019263269E-2</v>
-      </c>
-      <c r="G48" t="b">
-        <v>1</v>
-      </c>
-      <c r="H48">
-        <v>243.75</v>
-      </c>
-      <c r="I48">
-        <v>281.25</v>
-      </c>
-      <c r="J48">
-        <v>0.57192689180374146</v>
-      </c>
-      <c r="K48">
-        <v>0.32710033655166632</v>
-      </c>
-      <c r="L48">
-        <v>4.0441338353737043E-3</v>
-      </c>
-      <c r="M48">
-        <v>8.088267408311367E-3</v>
-      </c>
-      <c r="N48">
-        <v>2.6707375245127452E-4</v>
-      </c>
-      <c r="O48">
-        <v>184.4378025094268</v>
-      </c>
-      <c r="P48">
-        <v>70</v>
-      </c>
-      <c r="Q48">
-        <v>20000</v>
+      <c r="C48" s="5">
+        <v>253.69000244140619</v>
+      </c>
+      <c r="D48" s="5">
+        <v>4.0969843864440918</v>
+      </c>
+      <c r="E48" s="5">
+        <v>7.7230856732057873E-7</v>
+      </c>
+      <c r="F48" s="5">
+        <v>1.439468935132027E-2</v>
+      </c>
+      <c r="G48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" s="5">
+        <v>150</v>
+      </c>
+      <c r="I48" s="5">
+        <v>350</v>
+      </c>
+      <c r="J48" s="5">
+        <v>0.56472033262252808</v>
+      </c>
+      <c r="K48" s="5">
+        <v>0.31890907883644098</v>
+      </c>
+      <c r="L48" s="5">
+        <v>1.1075076906787999E-3</v>
+      </c>
+      <c r="M48" s="5">
+        <v>2.2150154691189532E-3</v>
+      </c>
+      <c r="N48" s="5">
+        <v>8.626258177724111E-5</v>
+      </c>
+      <c r="O48" s="5">
+        <v>603.26123548689441</v>
+      </c>
+      <c r="P48" s="5">
+        <v>125</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>260000</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48">
         <f t="shared" si="0"/>
-        <v>6.5186513811953603E-3</v>
+        <v>2.1054697164607388E-3</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
@@ -4916,7 +4928,7 @@
         <v>1.5696079730987551</v>
       </c>
       <c r="E73">
-        <f t="shared" ref="E73:E102" si="3">(B73-D73)^2</f>
+        <f t="shared" ref="E73:E90" si="3">(B73-D73)^2</f>
         <v>1.4956413051673382E-7</v>
       </c>
       <c r="F73">
@@ -6710,7 +6722,7 @@
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="S103">
         <f>AVERAGE(S2:S102)</f>
-        <v>5.8089134391854452E-2</v>
+        <v>5.8045439523886785E-2</v>
       </c>
     </row>
   </sheetData>

--- a/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix.xlsx
+++ b/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29E70C88-3ADC-4D3C-AFCC-CA6965696291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46523B9-AECF-49A8-BD45-B8669571DF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,8 +30,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>deme_index</t>
   </si>
@@ -89,12 +111,27 @@
   <si>
     <t>max_n_samples_final</t>
   </si>
+  <si>
+    <t>Mean Abs Percent Error</t>
+  </si>
+  <si>
+    <t>Median absolute percent error</t>
+  </si>
+  <si>
+    <t>95th percentile</t>
+  </si>
+  <si>
+    <t>Maximum absolute percent error</t>
+  </si>
+  <si>
+    <t>Standard Deviation of absolute percent error</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,6 +155,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -243,7 +288,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -266,6 +311,7 @@
     <xf numFmtId="2" fontId="2" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -570,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S103"/>
+  <dimension ref="A1:S107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -588,7 +634,7 @@
     <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.7109375" customWidth="1"/>
-    <col min="18" max="18" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2166,7 +2212,7 @@
         <v>1.242001533508301</v>
       </c>
       <c r="E27">
-        <f t="shared" ref="E27:E48" si="1">(B27-D27)^2</f>
+        <f t="shared" ref="E27:E29" si="1">(B27-D27)^2</f>
         <v>1.867646055540535E-9</v>
       </c>
       <c r="F27">
@@ -6720,9 +6766,48 @@
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R103" s="16" t="s">
+        <v>19</v>
+      </c>
       <c r="S103">
         <f>AVERAGE(S2:S102)</f>
         <v>5.8045439523886785E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R104" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="S104" cm="1">
+        <f t="array" ref="S104">MEDIAN(ABS(S2:S102))</f>
+        <v>1.7015431569494494E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R105" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="S105">
+        <f>_xlfn.STDEV.S(S2:S102)</f>
+        <v>0.10767796076091427</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R106" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="S106">
+        <f>_xlfn.PERCENTILE.INC(S2:S102,0.95)</f>
+        <v>0.29131995435649394</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R107" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="S107">
+        <f>MAX(S2:S102)</f>
+        <v>0.60810119606681023</v>
       </c>
     </row>
   </sheetData>
